--- a/tool/track-aggregator/template/統合結果.xlsx
+++ b/tool/track-aggregator/template/統合結果.xlsx
@@ -8,21 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ishid\Desktop\project_management\tool\track-aggregator\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C8D52FB-F071-4CEB-AB9E-4CCFF283E7BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DA94DA7-27EE-4A1C-B46F-1FF37C3F79E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="実施状況" sheetId="33" r:id="rId1"/>
-    <sheet name="経年比較" sheetId="31" r:id="rId2"/>
-    <sheet name="経年比較（前年同じFMT）" sheetId="22" state="hidden" r:id="rId3"/>
-    <sheet name="サマリ" sheetId="32" r:id="rId4"/>
+    <sheet name="サマリ" sheetId="32" r:id="rId2"/>
+    <sheet name="経年比較" sheetId="31" r:id="rId3"/>
+    <sheet name="経年比較（前年同じFMT）" sheetId="22" state="hidden" r:id="rId4"/>
     <sheet name="ビジネス基礎（Day5)" sheetId="13" state="hidden" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">サマリ!$B$2:$O$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">経年比較!$B$2:$Q$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'経年比較（前年同じFMT）'!$B$2:$Q$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">サマリ!$B$2:$O$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">経年比較!$B$2:$Q$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'経年比較（前年同じFMT）'!$B$2:$Q$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">実施状況!$A$2:$F$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -2387,6 +2387,66 @@
     <xf numFmtId="0" fontId="10" fillId="9" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="40" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="179" fontId="10" fillId="8" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2396,64 +2456,13 @@
     <xf numFmtId="179" fontId="10" fillId="8" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="40" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2473,15 +2482,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
@@ -3218,6 +3218,280 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACF7CB32-E2DC-41F1-851C-45AF01A8E0CE}">
+  <sheetPr>
+    <tabColor rgb="FFFFFF00"/>
+  </sheetPr>
+  <dimension ref="A1:AA9"/>
+  <sheetFormatPr defaultColWidth="8.19921875" defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="2.59765625" style="94" customWidth="1"/>
+    <col min="2" max="2" width="40.69921875" style="94" customWidth="1"/>
+    <col min="3" max="4" width="13.69921875" style="95" customWidth="1"/>
+    <col min="5" max="15" width="13.69921875" style="94" customWidth="1"/>
+    <col min="16" max="16384" width="8.19921875" style="94"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="A1" s="94" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B2" s="246" t="s">
+        <v>156</v>
+      </c>
+      <c r="C2" s="247" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" s="247"/>
+      <c r="E2" s="247"/>
+      <c r="F2" s="249" t="s">
+        <v>56</v>
+      </c>
+      <c r="G2" s="250"/>
+      <c r="H2" s="250"/>
+      <c r="I2" s="250"/>
+      <c r="J2" s="250"/>
+      <c r="K2" s="250"/>
+      <c r="L2" s="250"/>
+      <c r="M2" s="250"/>
+      <c r="N2" s="250"/>
+      <c r="O2" s="251"/>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="B3" s="246"/>
+      <c r="C3" s="247" t="s">
+        <v>97</v>
+      </c>
+      <c r="D3" s="247"/>
+      <c r="E3" s="247"/>
+      <c r="F3" s="252"/>
+      <c r="G3" s="253"/>
+      <c r="H3" s="253"/>
+      <c r="I3" s="253"/>
+      <c r="J3" s="253"/>
+      <c r="K3" s="253"/>
+      <c r="L3" s="253"/>
+      <c r="M3" s="253"/>
+      <c r="N3" s="253"/>
+      <c r="O3" s="254"/>
+    </row>
+    <row r="4" spans="1:27" ht="36" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B4" s="246"/>
+      <c r="C4" s="97" t="s">
+        <v>141</v>
+      </c>
+      <c r="D4" s="97" t="s">
+        <v>149</v>
+      </c>
+      <c r="E4" s="96" t="s">
+        <v>57</v>
+      </c>
+      <c r="F4" s="93" t="s">
+        <v>58</v>
+      </c>
+      <c r="G4" s="93" t="s">
+        <v>59</v>
+      </c>
+      <c r="H4" s="93" t="s">
+        <v>60</v>
+      </c>
+      <c r="I4" s="93" t="s">
+        <v>140</v>
+      </c>
+      <c r="J4" s="93" t="s">
+        <v>61</v>
+      </c>
+      <c r="K4" s="93" t="s">
+        <v>62</v>
+      </c>
+      <c r="L4" s="93" t="s">
+        <v>63</v>
+      </c>
+      <c r="M4" s="93" t="s">
+        <v>64</v>
+      </c>
+      <c r="N4" s="93" t="s">
+        <v>65</v>
+      </c>
+      <c r="O4" s="93" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="B5" s="98" t="s">
+        <v>151</v>
+      </c>
+      <c r="C5" s="99"/>
+      <c r="D5" s="99"/>
+      <c r="E5" s="100"/>
+      <c r="F5" s="99"/>
+      <c r="G5" s="99"/>
+      <c r="H5" s="99"/>
+      <c r="I5" s="99"/>
+      <c r="J5" s="99"/>
+      <c r="K5" s="99"/>
+      <c r="L5" s="99"/>
+      <c r="M5" s="99"/>
+      <c r="N5" s="99"/>
+      <c r="O5" s="99"/>
+      <c r="Q5" s="101"/>
+    </row>
+    <row r="6" spans="1:27" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B6" s="248" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" s="102"/>
+      <c r="D6" s="102"/>
+      <c r="E6" s="103"/>
+      <c r="F6" s="102"/>
+      <c r="G6" s="102"/>
+      <c r="H6" s="102"/>
+      <c r="I6" s="102"/>
+      <c r="J6" s="102"/>
+      <c r="K6" s="102"/>
+      <c r="L6" s="102"/>
+      <c r="M6" s="102"/>
+      <c r="N6" s="102"/>
+      <c r="O6" s="104"/>
+    </row>
+    <row r="7" spans="1:27" ht="18.600000000000001" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B7" s="205"/>
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="107"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="107"/>
+      <c r="K7" s="107"/>
+      <c r="L7" s="107"/>
+      <c r="M7" s="107"/>
+      <c r="N7" s="107"/>
+      <c r="O7" s="107"/>
+      <c r="P7" s="108"/>
+      <c r="Q7" s="108"/>
+      <c r="R7" s="108"/>
+      <c r="S7" s="108"/>
+      <c r="T7" s="108"/>
+      <c r="U7" s="108"/>
+      <c r="V7" s="108"/>
+      <c r="W7" s="108"/>
+      <c r="X7" s="108"/>
+      <c r="Y7" s="108"/>
+      <c r="Z7" s="108"/>
+      <c r="AA7" s="108"/>
+    </row>
+    <row r="8" spans="1:27" ht="18.600000000000001" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B8" s="204"/>
+      <c r="C8" s="109"/>
+      <c r="D8" s="109"/>
+      <c r="E8" s="110"/>
+      <c r="F8" s="111"/>
+      <c r="G8" s="111"/>
+      <c r="H8" s="111"/>
+      <c r="I8" s="111"/>
+      <c r="J8" s="111"/>
+      <c r="K8" s="111"/>
+      <c r="L8" s="111"/>
+      <c r="M8" s="111"/>
+      <c r="N8" s="111"/>
+      <c r="O8" s="112"/>
+      <c r="P8" s="108"/>
+      <c r="Q8" s="108"/>
+      <c r="R8" s="108"/>
+      <c r="S8" s="108"/>
+      <c r="T8" s="108"/>
+      <c r="U8" s="108"/>
+      <c r="V8" s="108"/>
+      <c r="W8" s="108"/>
+      <c r="X8" s="108"/>
+      <c r="Y8" s="108"/>
+      <c r="Z8" s="108"/>
+      <c r="AA8" s="108"/>
+    </row>
+    <row r="9" spans="1:27" ht="18.600000000000001" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B9" s="113" t="s">
+        <v>92</v>
+      </c>
+      <c r="C9" s="114" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9" s="114"/>
+      <c r="E9" s="115"/>
+      <c r="F9" s="116"/>
+      <c r="G9" s="117"/>
+      <c r="H9" s="116"/>
+      <c r="I9" s="117"/>
+      <c r="J9" s="116"/>
+      <c r="K9" s="117"/>
+      <c r="L9" s="116"/>
+      <c r="M9" s="117"/>
+      <c r="N9" s="116"/>
+      <c r="O9" s="118"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="F2:O3"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <conditionalFormatting sqref="C5:E5">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+      <formula>""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5:O6">
+    <cfRule type="cellIs" dxfId="2" priority="8" operator="lessThanOrEqual">
+      <formula>3.4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7:O7">
+    <cfRule type="cellIs" dxfId="1" priority="13" operator="lessThanOrEqual">
+      <formula>3.4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8:O8">
+    <cfRule type="cellIs" dxfId="0" priority="14" operator="lessThanOrEqual">
+      <formula>3.4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="31" id="{929A1E3A-38D3-44BC-9132-468325377686}">
+            <x14:iconSet iconSet="3Arrows" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>-0.25</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0.25</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Arrows" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Arrows" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>F9:N9</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{738A7942-48C0-418C-A267-8ECE9048A1F1}">
   <sheetPr>
     <tabColor theme="7" tint="0.39997558519241921"/>
@@ -3242,11 +3516,11 @@
       </c>
     </row>
     <row r="2" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="205" t="s">
+      <c r="B2" s="206" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="206"/>
-      <c r="D2" s="211" t="s">
+      <c r="C2" s="207"/>
+      <c r="D2" s="212" t="s">
         <v>54</v>
       </c>
       <c r="E2" s="191" t="s">
@@ -3254,23 +3528,23 @@
       </c>
       <c r="F2" s="192"/>
       <c r="G2" s="193"/>
-      <c r="H2" s="213" t="s">
+      <c r="H2" s="194" t="s">
         <v>56</v>
       </c>
-      <c r="I2" s="214"/>
-      <c r="J2" s="214"/>
-      <c r="K2" s="214"/>
-      <c r="L2" s="214"/>
-      <c r="M2" s="214"/>
-      <c r="N2" s="214"/>
-      <c r="O2" s="214"/>
-      <c r="P2" s="214"/>
-      <c r="Q2" s="215"/>
+      <c r="I2" s="195"/>
+      <c r="J2" s="195"/>
+      <c r="K2" s="195"/>
+      <c r="L2" s="195"/>
+      <c r="M2" s="195"/>
+      <c r="N2" s="195"/>
+      <c r="O2" s="195"/>
+      <c r="P2" s="195"/>
+      <c r="Q2" s="196"/>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="B3" s="207"/>
-      <c r="C3" s="208"/>
-      <c r="D3" s="212"/>
+      <c r="B3" s="208"/>
+      <c r="C3" s="209"/>
+      <c r="D3" s="213"/>
       <c r="E3" s="197" t="s">
         <v>97</v>
       </c>
@@ -3288,9 +3562,9 @@
       <c r="Q3" s="170"/>
     </row>
     <row r="4" spans="1:29" ht="36.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B4" s="209"/>
-      <c r="C4" s="210"/>
-      <c r="D4" s="212"/>
+      <c r="B4" s="210"/>
+      <c r="C4" s="211"/>
+      <c r="D4" s="213"/>
       <c r="E4" s="171" t="s">
         <v>141</v>
       </c>
@@ -3518,7 +3792,7 @@
     </row>
     <row r="9" spans="1:29" ht="18.600000000000001" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B9" s="201"/>
-      <c r="C9" s="216"/>
+      <c r="C9" s="205"/>
       <c r="D9" s="131" t="s">
         <v>103</v>
       </c>
@@ -3827,11 +4101,11 @@
       <c r="Q15" s="95"/>
     </row>
     <row r="16" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="B16" s="205" t="s">
+      <c r="B16" s="206" t="s">
         <v>53</v>
       </c>
-      <c r="C16" s="206"/>
-      <c r="D16" s="211" t="s">
+      <c r="C16" s="207"/>
+      <c r="D16" s="212" t="s">
         <v>54</v>
       </c>
       <c r="E16" s="191" t="s">
@@ -3839,23 +4113,23 @@
       </c>
       <c r="F16" s="192"/>
       <c r="G16" s="193"/>
-      <c r="H16" s="194" t="s">
+      <c r="H16" s="214" t="s">
         <v>56</v>
       </c>
-      <c r="I16" s="195"/>
-      <c r="J16" s="195"/>
-      <c r="K16" s="195"/>
-      <c r="L16" s="195"/>
-      <c r="M16" s="195"/>
-      <c r="N16" s="195"/>
-      <c r="O16" s="195"/>
-      <c r="P16" s="195"/>
-      <c r="Q16" s="196"/>
+      <c r="I16" s="215"/>
+      <c r="J16" s="215"/>
+      <c r="K16" s="215"/>
+      <c r="L16" s="215"/>
+      <c r="M16" s="215"/>
+      <c r="N16" s="215"/>
+      <c r="O16" s="215"/>
+      <c r="P16" s="215"/>
+      <c r="Q16" s="216"/>
     </row>
     <row r="17" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B17" s="207"/>
-      <c r="C17" s="208"/>
-      <c r="D17" s="212"/>
+      <c r="B17" s="208"/>
+      <c r="C17" s="209"/>
+      <c r="D17" s="213"/>
       <c r="E17" s="197" t="s">
         <v>97</v>
       </c>
@@ -3873,9 +4147,9 @@
       <c r="Q17" s="179"/>
     </row>
     <row r="18" spans="2:28" ht="36.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B18" s="209"/>
-      <c r="C18" s="210"/>
-      <c r="D18" s="212"/>
+      <c r="B18" s="210"/>
+      <c r="C18" s="211"/>
+      <c r="D18" s="213"/>
       <c r="E18" s="171" t="s">
         <v>141</v>
       </c>
@@ -4384,11 +4658,11 @@
       <c r="Q28" s="95"/>
     </row>
     <row r="29" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B29" s="205" t="s">
+      <c r="B29" s="206" t="s">
         <v>53</v>
       </c>
-      <c r="C29" s="206"/>
-      <c r="D29" s="211" t="s">
+      <c r="C29" s="207"/>
+      <c r="D29" s="212" t="s">
         <v>54</v>
       </c>
       <c r="E29" s="191" t="s">
@@ -4396,23 +4670,23 @@
       </c>
       <c r="F29" s="192"/>
       <c r="G29" s="193"/>
-      <c r="H29" s="194" t="s">
+      <c r="H29" s="214" t="s">
         <v>56</v>
       </c>
-      <c r="I29" s="195"/>
-      <c r="J29" s="195"/>
-      <c r="K29" s="195"/>
-      <c r="L29" s="195"/>
-      <c r="M29" s="195"/>
-      <c r="N29" s="195"/>
-      <c r="O29" s="195"/>
-      <c r="P29" s="195"/>
-      <c r="Q29" s="196"/>
+      <c r="I29" s="215"/>
+      <c r="J29" s="215"/>
+      <c r="K29" s="215"/>
+      <c r="L29" s="215"/>
+      <c r="M29" s="215"/>
+      <c r="N29" s="215"/>
+      <c r="O29" s="215"/>
+      <c r="P29" s="215"/>
+      <c r="Q29" s="216"/>
     </row>
     <row r="30" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B30" s="207"/>
-      <c r="C30" s="208"/>
-      <c r="D30" s="212"/>
+      <c r="B30" s="208"/>
+      <c r="C30" s="209"/>
+      <c r="D30" s="213"/>
       <c r="E30" s="197" t="s">
         <v>97</v>
       </c>
@@ -4430,9 +4704,9 @@
       <c r="Q30" s="179"/>
     </row>
     <row r="31" spans="2:28" ht="36.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B31" s="209"/>
-      <c r="C31" s="210"/>
-      <c r="D31" s="212"/>
+      <c r="B31" s="210"/>
+      <c r="C31" s="211"/>
+      <c r="D31" s="213"/>
       <c r="E31" s="171" t="s">
         <v>141</v>
       </c>
@@ -5346,18 +5620,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:Q2"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="B5:B14"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="B2:C4"/>
-    <mergeCell ref="B16:C18"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="D16:D18"/>
     <mergeCell ref="E16:G16"/>
     <mergeCell ref="H16:Q16"/>
     <mergeCell ref="E17:G17"/>
@@ -5374,6 +5636,18 @@
     <mergeCell ref="B19:B27"/>
     <mergeCell ref="C19:C20"/>
     <mergeCell ref="C22:C23"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="B2:C4"/>
+    <mergeCell ref="B16:C18"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:Q2"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="B5:B14"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="C12:C13"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="H5:Q6">
@@ -5471,7 +5745,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5C06947-9AD3-4764-A00F-59E09793C545}">
   <sheetPr>
     <tabColor theme="8" tint="0.39997558519241921"/>
@@ -5492,10 +5766,10 @@
   <sheetData>
     <row r="1" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="2" spans="2:29" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="217" t="s">
+      <c r="B2" s="220" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="218"/>
+      <c r="C2" s="221"/>
       <c r="D2" s="229" t="s">
         <v>54</v>
       </c>
@@ -5518,8 +5792,8 @@
       <c r="Q2" s="233"/>
     </row>
     <row r="3" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B3" s="219"/>
-      <c r="C3" s="220"/>
+      <c r="B3" s="222"/>
+      <c r="C3" s="223"/>
       <c r="D3" s="230"/>
       <c r="E3" s="234" t="s">
         <v>97</v>
@@ -5538,8 +5812,8 @@
       <c r="Q3" s="20"/>
     </row>
     <row r="4" spans="2:29" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B4" s="221"/>
-      <c r="C4" s="222"/>
+      <c r="B4" s="224"/>
+      <c r="C4" s="225"/>
       <c r="D4" s="230"/>
       <c r="E4" s="85" t="s">
         <v>141</v>
@@ -5585,7 +5859,7 @@
       <c r="B5" s="226" t="s">
         <v>90</v>
       </c>
-      <c r="C5" s="223" t="s">
+      <c r="C5" s="217" t="s">
         <v>138</v>
       </c>
       <c r="D5" s="33" t="s">
@@ -5640,7 +5914,7 @@
     </row>
     <row r="6" spans="2:29" x14ac:dyDescent="0.45">
       <c r="B6" s="227"/>
-      <c r="C6" s="224"/>
+      <c r="C6" s="218"/>
       <c r="D6" s="26" t="s">
         <v>103</v>
       </c>
@@ -5694,7 +5968,7 @@
     </row>
     <row r="7" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B7" s="227"/>
-      <c r="C7" s="225"/>
+      <c r="C7" s="219"/>
       <c r="D7" s="83" t="s">
         <v>71</v>
       </c>
@@ -5800,7 +6074,7 @@
     </row>
     <row r="9" spans="2:29" hidden="1" x14ac:dyDescent="0.45">
       <c r="B9" s="227"/>
-      <c r="C9" s="223" t="s">
+      <c r="C9" s="217" t="s">
         <v>102</v>
       </c>
       <c r="D9" s="33" t="s">
@@ -5852,7 +6126,7 @@
     </row>
     <row r="10" spans="2:29" hidden="1" x14ac:dyDescent="0.45">
       <c r="B10" s="227"/>
-      <c r="C10" s="224"/>
+      <c r="C10" s="218"/>
       <c r="D10" s="26" t="s">
         <v>103</v>
       </c>
@@ -5904,7 +6178,7 @@
     </row>
     <row r="11" spans="2:29" ht="15.6" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B11" s="227"/>
-      <c r="C11" s="225"/>
+      <c r="C11" s="219"/>
       <c r="D11" s="34" t="s">
         <v>71</v>
       </c>
@@ -6010,7 +6284,7 @@
     </row>
     <row r="13" spans="2:29" x14ac:dyDescent="0.45">
       <c r="B13" s="227"/>
-      <c r="C13" s="223" t="s">
+      <c r="C13" s="217" t="s">
         <v>143</v>
       </c>
       <c r="D13" s="33" t="s">
@@ -6062,7 +6336,7 @@
     </row>
     <row r="14" spans="2:29" x14ac:dyDescent="0.45">
       <c r="B14" s="227"/>
-      <c r="C14" s="224"/>
+      <c r="C14" s="218"/>
       <c r="D14" s="26" t="s">
         <v>103</v>
       </c>
@@ -6114,7 +6388,7 @@
     </row>
     <row r="15" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B15" s="227"/>
-      <c r="C15" s="225"/>
+      <c r="C15" s="219"/>
       <c r="D15" s="83" t="s">
         <v>71</v>
       </c>
@@ -6231,10 +6505,10 @@
       <c r="Q17" s="12"/>
     </row>
     <row r="18" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B18" s="217" t="s">
+      <c r="B18" s="220" t="s">
         <v>53</v>
       </c>
-      <c r="C18" s="218"/>
+      <c r="C18" s="221"/>
       <c r="D18" s="229" t="s">
         <v>54</v>
       </c>
@@ -6257,8 +6531,8 @@
       <c r="Q18" s="245"/>
     </row>
     <row r="19" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B19" s="219"/>
-      <c r="C19" s="220"/>
+      <c r="B19" s="222"/>
+      <c r="C19" s="223"/>
       <c r="D19" s="230"/>
       <c r="E19" s="234" t="s">
         <v>97</v>
@@ -6277,8 +6551,8 @@
       <c r="Q19" s="69"/>
     </row>
     <row r="20" spans="2:28" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B20" s="221"/>
-      <c r="C20" s="222"/>
+      <c r="B20" s="224"/>
+      <c r="C20" s="225"/>
       <c r="D20" s="230"/>
       <c r="E20" s="85" t="s">
         <v>141</v>
@@ -6324,7 +6598,7 @@
       <c r="B21" s="226" t="s">
         <v>101</v>
       </c>
-      <c r="C21" s="223" t="s">
+      <c r="C21" s="217" t="s">
         <v>100</v>
       </c>
       <c r="D21" s="33" t="s">
@@ -6385,7 +6659,7 @@
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B22" s="227"/>
-      <c r="C22" s="224"/>
+      <c r="C22" s="218"/>
       <c r="D22" s="26" t="s">
         <v>103</v>
       </c>
@@ -6440,7 +6714,7 @@
     </row>
     <row r="23" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B23" s="227"/>
-      <c r="C23" s="225"/>
+      <c r="C23" s="219"/>
       <c r="D23" s="83" t="s">
         <v>71</v>
       </c>
@@ -6551,7 +6825,7 @@
     </row>
     <row r="25" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B25" s="227"/>
-      <c r="C25" s="223" t="s">
+      <c r="C25" s="217" t="s">
         <v>99</v>
       </c>
       <c r="D25" s="33" t="s">
@@ -6612,7 +6886,7 @@
     </row>
     <row r="26" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B26" s="227"/>
-      <c r="C26" s="224"/>
+      <c r="C26" s="218"/>
       <c r="D26" s="26" t="s">
         <v>103</v>
       </c>
@@ -6667,7 +6941,7 @@
     </row>
     <row r="27" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B27" s="227"/>
-      <c r="C27" s="225"/>
+      <c r="C27" s="219"/>
       <c r="D27" s="83" t="s">
         <v>71</v>
       </c>
@@ -6778,7 +7052,7 @@
     </row>
     <row r="29" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B29" s="227"/>
-      <c r="C29" s="223" t="s">
+      <c r="C29" s="217" t="s">
         <v>98</v>
       </c>
       <c r="D29" s="33" t="s">
@@ -6839,7 +7113,7 @@
     </row>
     <row r="30" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B30" s="227"/>
-      <c r="C30" s="224"/>
+      <c r="C30" s="218"/>
       <c r="D30" s="26" t="s">
         <v>103</v>
       </c>
@@ -6894,7 +7168,7 @@
     </row>
     <row r="31" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B31" s="227"/>
-      <c r="C31" s="225"/>
+      <c r="C31" s="219"/>
       <c r="D31" s="83" t="s">
         <v>71</v>
       </c>
@@ -7016,10 +7290,10 @@
       <c r="Q33" s="12"/>
     </row>
     <row r="34" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B34" s="217" t="s">
+      <c r="B34" s="220" t="s">
         <v>53</v>
       </c>
-      <c r="C34" s="218"/>
+      <c r="C34" s="221"/>
       <c r="D34" s="229" t="s">
         <v>54</v>
       </c>
@@ -7042,8 +7316,8 @@
       <c r="Q34" s="245"/>
     </row>
     <row r="35" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B35" s="219"/>
-      <c r="C35" s="220"/>
+      <c r="B35" s="222"/>
+      <c r="C35" s="223"/>
       <c r="D35" s="230"/>
       <c r="E35" s="234" t="s">
         <v>97</v>
@@ -7062,8 +7336,8 @@
       <c r="Q35" s="69"/>
     </row>
     <row r="36" spans="2:28" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B36" s="221"/>
-      <c r="C36" s="222"/>
+      <c r="B36" s="224"/>
+      <c r="C36" s="225"/>
       <c r="D36" s="230"/>
       <c r="E36" s="85" t="s">
         <v>141</v>
@@ -7109,7 +7383,7 @@
       <c r="B37" s="226" t="s">
         <v>96</v>
       </c>
-      <c r="C37" s="223" t="s">
+      <c r="C37" s="217" t="s">
         <v>95</v>
       </c>
       <c r="D37" s="33" t="s">
@@ -7170,7 +7444,7 @@
     </row>
     <row r="38" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B38" s="227"/>
-      <c r="C38" s="224"/>
+      <c r="C38" s="218"/>
       <c r="D38" s="26" t="s">
         <v>103</v>
       </c>
@@ -7225,7 +7499,7 @@
     </row>
     <row r="39" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B39" s="227"/>
-      <c r="C39" s="225"/>
+      <c r="C39" s="219"/>
       <c r="D39" s="83" t="s">
         <v>71</v>
       </c>
@@ -7336,7 +7610,7 @@
     </row>
     <row r="41" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B41" s="227"/>
-      <c r="C41" s="223" t="s">
+      <c r="C41" s="217" t="s">
         <v>80</v>
       </c>
       <c r="D41" s="33" t="s">
@@ -7397,7 +7671,7 @@
     </row>
     <row r="42" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B42" s="227"/>
-      <c r="C42" s="224"/>
+      <c r="C42" s="218"/>
       <c r="D42" s="26" t="s">
         <v>103</v>
       </c>
@@ -7452,7 +7726,7 @@
     </row>
     <row r="43" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B43" s="227"/>
-      <c r="C43" s="225"/>
+      <c r="C43" s="219"/>
       <c r="D43" s="83" t="s">
         <v>71</v>
       </c>
@@ -7563,7 +7837,7 @@
     </row>
     <row r="45" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B45" s="227"/>
-      <c r="C45" s="223" t="s">
+      <c r="C45" s="217" t="s">
         <v>94</v>
       </c>
       <c r="D45" s="33" t="s">
@@ -7624,7 +7898,7 @@
     </row>
     <row r="46" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B46" s="227"/>
-      <c r="C46" s="224"/>
+      <c r="C46" s="218"/>
       <c r="D46" s="26" t="s">
         <v>103</v>
       </c>
@@ -7679,7 +7953,7 @@
     </row>
     <row r="47" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B47" s="227"/>
-      <c r="C47" s="225"/>
+      <c r="C47" s="219"/>
       <c r="D47" s="83" t="s">
         <v>71</v>
       </c>
@@ -7790,7 +8064,7 @@
     </row>
     <row r="49" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B49" s="227"/>
-      <c r="C49" s="223" t="s">
+      <c r="C49" s="217" t="s">
         <v>93</v>
       </c>
       <c r="D49" s="33" t="s">
@@ -7842,7 +8116,7 @@
     </row>
     <row r="50" spans="2:28" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B50" s="227"/>
-      <c r="C50" s="224"/>
+      <c r="C50" s="218"/>
       <c r="D50" s="26" t="s">
         <v>103</v>
       </c>
@@ -7893,7 +8167,7 @@
     </row>
     <row r="51" spans="2:28" ht="18.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B51" s="227"/>
-      <c r="C51" s="225"/>
+      <c r="C51" s="219"/>
       <c r="D51" s="83" t="s">
         <v>71</v>
       </c>
@@ -8395,12 +8669,16 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="C41:C43"/>
-    <mergeCell ref="C45:C47"/>
-    <mergeCell ref="C49:C51"/>
-    <mergeCell ref="B34:C36"/>
-    <mergeCell ref="B37:B52"/>
-    <mergeCell ref="C37:C39"/>
+    <mergeCell ref="B2:C4"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="B18:C20"/>
+    <mergeCell ref="B5:B16"/>
+    <mergeCell ref="B21:B32"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="C25:C27"/>
     <mergeCell ref="D2:D4"/>
     <mergeCell ref="H2:Q2"/>
     <mergeCell ref="E3:G3"/>
@@ -8414,16 +8692,12 @@
     <mergeCell ref="D18:D20"/>
     <mergeCell ref="E18:G18"/>
     <mergeCell ref="E19:G19"/>
-    <mergeCell ref="B2:C4"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="B18:C20"/>
-    <mergeCell ref="B5:B16"/>
-    <mergeCell ref="B21:B32"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="C29:C31"/>
-    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="C41:C43"/>
+    <mergeCell ref="C45:C47"/>
+    <mergeCell ref="C49:C51"/>
+    <mergeCell ref="B34:C36"/>
+    <mergeCell ref="B37:B52"/>
+    <mergeCell ref="C37:C39"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="H5:Q7">
@@ -8531,280 +8805,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACF7CB32-E2DC-41F1-851C-45AF01A8E0CE}">
-  <sheetPr>
-    <tabColor rgb="FFFFFF00"/>
-  </sheetPr>
-  <dimension ref="A1:AA9"/>
-  <sheetFormatPr defaultColWidth="8.19921875" defaultRowHeight="18" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="2.59765625" style="94" customWidth="1"/>
-    <col min="2" max="2" width="40.69921875" style="94" customWidth="1"/>
-    <col min="3" max="4" width="13.69921875" style="95" customWidth="1"/>
-    <col min="5" max="15" width="13.69921875" style="94" customWidth="1"/>
-    <col min="16" max="16384" width="8.19921875" style="94"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.45">
-      <c r="A1" s="94" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="246" t="s">
-        <v>156</v>
-      </c>
-      <c r="C2" s="247" t="s">
-        <v>55</v>
-      </c>
-      <c r="D2" s="247"/>
-      <c r="E2" s="247"/>
-      <c r="F2" s="249" t="s">
-        <v>56</v>
-      </c>
-      <c r="G2" s="250"/>
-      <c r="H2" s="250"/>
-      <c r="I2" s="250"/>
-      <c r="J2" s="250"/>
-      <c r="K2" s="250"/>
-      <c r="L2" s="250"/>
-      <c r="M2" s="250"/>
-      <c r="N2" s="250"/>
-      <c r="O2" s="251"/>
-    </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.45">
-      <c r="B3" s="246"/>
-      <c r="C3" s="247" t="s">
-        <v>97</v>
-      </c>
-      <c r="D3" s="247"/>
-      <c r="E3" s="247"/>
-      <c r="F3" s="252"/>
-      <c r="G3" s="253"/>
-      <c r="H3" s="253"/>
-      <c r="I3" s="253"/>
-      <c r="J3" s="253"/>
-      <c r="K3" s="253"/>
-      <c r="L3" s="253"/>
-      <c r="M3" s="253"/>
-      <c r="N3" s="253"/>
-      <c r="O3" s="254"/>
-    </row>
-    <row r="4" spans="1:27" ht="36" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B4" s="246"/>
-      <c r="C4" s="97" t="s">
-        <v>141</v>
-      </c>
-      <c r="D4" s="97" t="s">
-        <v>149</v>
-      </c>
-      <c r="E4" s="96" t="s">
-        <v>57</v>
-      </c>
-      <c r="F4" s="93" t="s">
-        <v>58</v>
-      </c>
-      <c r="G4" s="93" t="s">
-        <v>59</v>
-      </c>
-      <c r="H4" s="93" t="s">
-        <v>60</v>
-      </c>
-      <c r="I4" s="93" t="s">
-        <v>140</v>
-      </c>
-      <c r="J4" s="93" t="s">
-        <v>61</v>
-      </c>
-      <c r="K4" s="93" t="s">
-        <v>62</v>
-      </c>
-      <c r="L4" s="93" t="s">
-        <v>63</v>
-      </c>
-      <c r="M4" s="93" t="s">
-        <v>64</v>
-      </c>
-      <c r="N4" s="93" t="s">
-        <v>65</v>
-      </c>
-      <c r="O4" s="93" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.45">
-      <c r="B5" s="98" t="s">
-        <v>151</v>
-      </c>
-      <c r="C5" s="99"/>
-      <c r="D5" s="99"/>
-      <c r="E5" s="100"/>
-      <c r="F5" s="99"/>
-      <c r="G5" s="99"/>
-      <c r="H5" s="99"/>
-      <c r="I5" s="99"/>
-      <c r="J5" s="99"/>
-      <c r="K5" s="99"/>
-      <c r="L5" s="99"/>
-      <c r="M5" s="99"/>
-      <c r="N5" s="99"/>
-      <c r="O5" s="99"/>
-      <c r="Q5" s="101"/>
-    </row>
-    <row r="6" spans="1:27" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B6" s="248" t="s">
-        <v>102</v>
-      </c>
-      <c r="C6" s="102"/>
-      <c r="D6" s="102"/>
-      <c r="E6" s="103"/>
-      <c r="F6" s="102"/>
-      <c r="G6" s="102"/>
-      <c r="H6" s="102"/>
-      <c r="I6" s="102"/>
-      <c r="J6" s="102"/>
-      <c r="K6" s="102"/>
-      <c r="L6" s="102"/>
-      <c r="M6" s="102"/>
-      <c r="N6" s="102"/>
-      <c r="O6" s="104"/>
-    </row>
-    <row r="7" spans="1:27" ht="18.600000000000001" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B7" s="216"/>
-      <c r="C7" s="105"/>
-      <c r="D7" s="105"/>
-      <c r="E7" s="106"/>
-      <c r="F7" s="107"/>
-      <c r="G7" s="107"/>
-      <c r="H7" s="107"/>
-      <c r="I7" s="107"/>
-      <c r="J7" s="107"/>
-      <c r="K7" s="107"/>
-      <c r="L7" s="107"/>
-      <c r="M7" s="107"/>
-      <c r="N7" s="107"/>
-      <c r="O7" s="107"/>
-      <c r="P7" s="108"/>
-      <c r="Q7" s="108"/>
-      <c r="R7" s="108"/>
-      <c r="S7" s="108"/>
-      <c r="T7" s="108"/>
-      <c r="U7" s="108"/>
-      <c r="V7" s="108"/>
-      <c r="W7" s="108"/>
-      <c r="X7" s="108"/>
-      <c r="Y7" s="108"/>
-      <c r="Z7" s="108"/>
-      <c r="AA7" s="108"/>
-    </row>
-    <row r="8" spans="1:27" ht="18.600000000000001" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B8" s="204"/>
-      <c r="C8" s="109"/>
-      <c r="D8" s="109"/>
-      <c r="E8" s="110"/>
-      <c r="F8" s="111"/>
-      <c r="G8" s="111"/>
-      <c r="H8" s="111"/>
-      <c r="I8" s="111"/>
-      <c r="J8" s="111"/>
-      <c r="K8" s="111"/>
-      <c r="L8" s="111"/>
-      <c r="M8" s="111"/>
-      <c r="N8" s="111"/>
-      <c r="O8" s="112"/>
-      <c r="P8" s="108"/>
-      <c r="Q8" s="108"/>
-      <c r="R8" s="108"/>
-      <c r="S8" s="108"/>
-      <c r="T8" s="108"/>
-      <c r="U8" s="108"/>
-      <c r="V8" s="108"/>
-      <c r="W8" s="108"/>
-      <c r="X8" s="108"/>
-      <c r="Y8" s="108"/>
-      <c r="Z8" s="108"/>
-      <c r="AA8" s="108"/>
-    </row>
-    <row r="9" spans="1:27" ht="18.600000000000001" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B9" s="113" t="s">
-        <v>92</v>
-      </c>
-      <c r="C9" s="114" t="s">
-        <v>70</v>
-      </c>
-      <c r="D9" s="114"/>
-      <c r="E9" s="115"/>
-      <c r="F9" s="116"/>
-      <c r="G9" s="117"/>
-      <c r="H9" s="116"/>
-      <c r="I9" s="117"/>
-      <c r="J9" s="116"/>
-      <c r="K9" s="117"/>
-      <c r="L9" s="116"/>
-      <c r="M9" s="117"/>
-      <c r="N9" s="116"/>
-      <c r="O9" s="118"/>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="B6:B8"/>
-    <mergeCell ref="F2:O3"/>
-  </mergeCells>
-  <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="C5:E5">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
-      <formula>""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5:O6">
-    <cfRule type="cellIs" dxfId="2" priority="8" operator="lessThanOrEqual">
-      <formula>3.4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7:O7">
-    <cfRule type="cellIs" dxfId="1" priority="13" operator="lessThanOrEqual">
-      <formula>3.4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F8:O8">
-    <cfRule type="cellIs" dxfId="0" priority="14" operator="lessThanOrEqual">
-      <formula>3.4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
-      <x14:conditionalFormattings>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="31" id="{929A1E3A-38D3-44BC-9132-468325377686}">
-            <x14:iconSet iconSet="3Arrows" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>-0.25</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>0.25</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="3Arrows" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Arrows" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>F9:N9</xm:sqref>
-        </x14:conditionalFormatting>
-      </x14:conditionalFormattings>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>

--- a/tool/track-aggregator/template/統合結果.xlsx
+++ b/tool/track-aggregator/template/統合結果.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ishid\Desktop\project_management\tool\track-aggregator\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DA94DA7-27EE-4A1C-B46F-1FF37C3F79E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CF0E662-3C7A-4957-952B-ADBBBE58DC3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">サマリ!$B$2:$O$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">経年比較!$B$2:$Q$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'経年比較（前年同じFMT）'!$B$2:$Q$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">実施状況!$A$2:$F$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">実施状況!$A$3:$F$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="167">
   <si>
     <t>目的達成</t>
     <rPh sb="0" eb="2">
@@ -953,10 +953,18 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>テスト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アンケート</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>{実施データ}</t>
-    <rPh sb="1" eb="3">
-      <t>ジッシ</t>
-    </rPh>
+  </si>
+  <si>
+    <t>{コースデータ}</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1139,7 +1147,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="53">
+  <borders count="54">
     <border>
       <left/>
       <right/>
@@ -1791,6 +1799,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1804,7 +1825,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="255">
+  <cellXfs count="258">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2372,12 +2393,39 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="44" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="47" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="48" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="49" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="50" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="51" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="9" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2387,13 +2435,13 @@
     <xf numFmtId="0" fontId="10" fillId="9" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="10" fillId="8" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="10" fillId="8" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="10" fillId="8" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="9" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2417,12 +2465,6 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2447,13 +2489,31 @@
     <xf numFmtId="0" fontId="10" fillId="7" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="10" fillId="8" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="8" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="8" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2465,24 +2525,6 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -2543,31 +2585,19 @@
     <xf numFmtId="179" fontId="5" fillId="8" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="44" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="47" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="48" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="49" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="50" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="51" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2578,38 +2608,6 @@
     <cellStyle name="標準 2" xfId="2" xr:uid="{35DECEAB-A874-4A31-B6F5-75B712B64A43}"/>
   </cellStyles>
   <dxfs count="32">
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -2873,6 +2871,38 @@
       <font>
         <color rgb="FFFF0000"/>
       </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="6" tint="0.79998168889431442"/>
@@ -3163,52 +3193,70 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3C1958A-33FA-4C4A-B3B4-B13C570E4EA1}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="19.296875" style="186" customWidth="1"/>
     <col min="2" max="2" width="30.69921875" style="186" customWidth="1"/>
     <col min="3" max="3" width="40.69921875" style="186" customWidth="1"/>
     <col min="4" max="5" width="15.69921875" style="186" customWidth="1"/>
-    <col min="6" max="6" width="20.5" style="186" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" style="186" customWidth="1"/>
+    <col min="7" max="7" width="20.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="185"/>
       <c r="B1" s="185"/>
       <c r="C1" s="185"/>
       <c r="D1" s="185"/>
       <c r="E1" s="185"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A2" s="187" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A2" s="185"/>
+      <c r="B2" s="185"/>
+      <c r="C2" s="185"/>
+      <c r="D2" s="185"/>
+      <c r="E2" s="185"/>
+      <c r="F2" s="255" t="s">
+        <v>166</v>
+      </c>
+      <c r="G2" s="254"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A3" s="187" t="s">
         <v>157</v>
       </c>
-      <c r="B2" s="187" t="s">
+      <c r="B3" s="187" t="s">
         <v>158</v>
       </c>
-      <c r="C2" s="187" t="s">
+      <c r="C3" s="187" t="s">
         <v>159</v>
       </c>
-      <c r="D2" s="187" t="s">
+      <c r="D3" s="187" t="s">
         <v>160</v>
       </c>
-      <c r="E2" s="187" t="s">
+      <c r="E3" s="187" t="s">
         <v>161</v>
       </c>
-      <c r="F2" s="190" t="s">
+      <c r="F3" s="253" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A3" s="188" t="s">
+      <c r="G3" s="253" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A4" s="188" t="s">
         <v>162</v>
       </c>
-      <c r="B3" s="188"/>
-      <c r="C3" s="188"/>
-      <c r="D3" s="188"/>
-      <c r="E3" s="188"/>
-      <c r="F3" s="189"/>
+      <c r="B4" s="188"/>
+      <c r="C4" s="188"/>
+      <c r="D4" s="188"/>
+      <c r="E4" s="188"/>
+      <c r="F4" s="256" t="s">
+        <v>165</v>
+      </c>
+      <c r="G4" s="257"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -3238,47 +3286,47 @@
       </c>
     </row>
     <row r="2" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="246" t="s">
+      <c r="B2" s="189" t="s">
         <v>156</v>
       </c>
-      <c r="C2" s="247" t="s">
+      <c r="C2" s="190" t="s">
         <v>55</v>
       </c>
-      <c r="D2" s="247"/>
-      <c r="E2" s="247"/>
-      <c r="F2" s="249" t="s">
+      <c r="D2" s="190"/>
+      <c r="E2" s="190"/>
+      <c r="F2" s="194" t="s">
         <v>56</v>
       </c>
-      <c r="G2" s="250"/>
-      <c r="H2" s="250"/>
-      <c r="I2" s="250"/>
-      <c r="J2" s="250"/>
-      <c r="K2" s="250"/>
-      <c r="L2" s="250"/>
-      <c r="M2" s="250"/>
-      <c r="N2" s="250"/>
-      <c r="O2" s="251"/>
+      <c r="G2" s="195"/>
+      <c r="H2" s="195"/>
+      <c r="I2" s="195"/>
+      <c r="J2" s="195"/>
+      <c r="K2" s="195"/>
+      <c r="L2" s="195"/>
+      <c r="M2" s="195"/>
+      <c r="N2" s="195"/>
+      <c r="O2" s="196"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.45">
-      <c r="B3" s="246"/>
-      <c r="C3" s="247" t="s">
+      <c r="B3" s="189"/>
+      <c r="C3" s="190" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="247"/>
-      <c r="E3" s="247"/>
-      <c r="F3" s="252"/>
-      <c r="G3" s="253"/>
-      <c r="H3" s="253"/>
-      <c r="I3" s="253"/>
-      <c r="J3" s="253"/>
-      <c r="K3" s="253"/>
-      <c r="L3" s="253"/>
-      <c r="M3" s="253"/>
-      <c r="N3" s="253"/>
-      <c r="O3" s="254"/>
+      <c r="D3" s="190"/>
+      <c r="E3" s="190"/>
+      <c r="F3" s="197"/>
+      <c r="G3" s="198"/>
+      <c r="H3" s="198"/>
+      <c r="I3" s="198"/>
+      <c r="J3" s="198"/>
+      <c r="K3" s="198"/>
+      <c r="L3" s="198"/>
+      <c r="M3" s="198"/>
+      <c r="N3" s="198"/>
+      <c r="O3" s="199"/>
     </row>
     <row r="4" spans="1:27" ht="36" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B4" s="246"/>
+      <c r="B4" s="189"/>
       <c r="C4" s="97" t="s">
         <v>141</v>
       </c>
@@ -3339,7 +3387,7 @@
       <c r="Q5" s="101"/>
     </row>
     <row r="6" spans="1:27" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B6" s="248" t="s">
+      <c r="B6" s="191" t="s">
         <v>102</v>
       </c>
       <c r="C6" s="102"/>
@@ -3357,7 +3405,7 @@
       <c r="O6" s="104"/>
     </row>
     <row r="7" spans="1:27" ht="18.600000000000001" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B7" s="205"/>
+      <c r="B7" s="192"/>
       <c r="C7" s="105"/>
       <c r="D7" s="105"/>
       <c r="E7" s="106"/>
@@ -3385,7 +3433,7 @@
       <c r="AA7" s="108"/>
     </row>
     <row r="8" spans="1:27" ht="18.600000000000001" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B8" s="204"/>
+      <c r="B8" s="193"/>
       <c r="C8" s="109"/>
       <c r="D8" s="109"/>
       <c r="E8" s="110"/>
@@ -3442,22 +3490,22 @@
   </mergeCells>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="C5:E5">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="1" operator="equal">
       <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:O6">
-    <cfRule type="cellIs" dxfId="2" priority="8" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="30" priority="8" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7:O7">
-    <cfRule type="cellIs" dxfId="1" priority="13" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="29" priority="13" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8:O8">
-    <cfRule type="cellIs" dxfId="0" priority="14" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="28" priority="14" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3516,40 +3564,40 @@
       </c>
     </row>
     <row r="2" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="206" t="s">
+      <c r="B2" s="213" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="207"/>
-      <c r="D2" s="212" t="s">
+      <c r="C2" s="214"/>
+      <c r="D2" s="219" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="191" t="s">
+      <c r="E2" s="200" t="s">
         <v>55</v>
       </c>
-      <c r="F2" s="192"/>
-      <c r="G2" s="193"/>
-      <c r="H2" s="194" t="s">
+      <c r="F2" s="201"/>
+      <c r="G2" s="202"/>
+      <c r="H2" s="221" t="s">
         <v>56</v>
       </c>
-      <c r="I2" s="195"/>
-      <c r="J2" s="195"/>
-      <c r="K2" s="195"/>
-      <c r="L2" s="195"/>
-      <c r="M2" s="195"/>
-      <c r="N2" s="195"/>
-      <c r="O2" s="195"/>
-      <c r="P2" s="195"/>
-      <c r="Q2" s="196"/>
+      <c r="I2" s="222"/>
+      <c r="J2" s="222"/>
+      <c r="K2" s="222"/>
+      <c r="L2" s="222"/>
+      <c r="M2" s="222"/>
+      <c r="N2" s="222"/>
+      <c r="O2" s="222"/>
+      <c r="P2" s="222"/>
+      <c r="Q2" s="223"/>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="B3" s="208"/>
-      <c r="C3" s="209"/>
-      <c r="D3" s="213"/>
-      <c r="E3" s="197" t="s">
+      <c r="B3" s="215"/>
+      <c r="C3" s="216"/>
+      <c r="D3" s="220"/>
+      <c r="E3" s="206" t="s">
         <v>97</v>
       </c>
-      <c r="F3" s="198"/>
-      <c r="G3" s="199"/>
+      <c r="F3" s="207"/>
+      <c r="G3" s="208"/>
       <c r="H3" s="168"/>
       <c r="I3" s="169"/>
       <c r="J3" s="169"/>
@@ -3562,9 +3610,9 @@
       <c r="Q3" s="170"/>
     </row>
     <row r="4" spans="1:29" ht="36.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B4" s="210"/>
-      <c r="C4" s="211"/>
-      <c r="D4" s="213"/>
+      <c r="B4" s="217"/>
+      <c r="C4" s="218"/>
+      <c r="D4" s="220"/>
       <c r="E4" s="171" t="s">
         <v>141</v>
       </c>
@@ -3606,10 +3654,10 @@
       </c>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="B5" s="200" t="s">
+      <c r="B5" s="209" t="s">
         <v>90</v>
       </c>
-      <c r="C5" s="203" t="s">
+      <c r="C5" s="212" t="s">
         <v>89</v>
       </c>
       <c r="D5" s="119" t="s">
@@ -3661,8 +3709,8 @@
       <c r="S5" s="101"/>
     </row>
     <row r="6" spans="1:29" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B6" s="201"/>
-      <c r="C6" s="204"/>
+      <c r="B6" s="210"/>
+      <c r="C6" s="193"/>
       <c r="D6" s="124" t="s">
         <v>145</v>
       </c>
@@ -3693,7 +3741,7 @@
       <c r="AC6" s="108"/>
     </row>
     <row r="7" spans="1:29" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B7" s="201"/>
+      <c r="B7" s="210"/>
       <c r="C7" s="184" t="s">
         <v>92</v>
       </c>
@@ -3749,8 +3797,8 @@
       </c>
     </row>
     <row r="8" spans="1:29" ht="18.600000000000001" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B8" s="201"/>
-      <c r="C8" s="203" t="s">
+      <c r="B8" s="210"/>
+      <c r="C8" s="212" t="s">
         <v>102</v>
       </c>
       <c r="D8" s="119" t="s">
@@ -3791,8 +3839,8 @@
       </c>
     </row>
     <row r="9" spans="1:29" ht="18.600000000000001" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B9" s="201"/>
-      <c r="C9" s="205"/>
+      <c r="B9" s="210"/>
+      <c r="C9" s="192"/>
       <c r="D9" s="131" t="s">
         <v>103</v>
       </c>
@@ -3843,8 +3891,8 @@
       <c r="AC9" s="108"/>
     </row>
     <row r="10" spans="1:29" ht="18.600000000000001" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B10" s="201"/>
-      <c r="C10" s="204"/>
+      <c r="B10" s="210"/>
+      <c r="C10" s="193"/>
       <c r="D10" s="134" t="s">
         <v>71</v>
       </c>
@@ -3895,7 +3943,7 @@
       <c r="AC10" s="108"/>
     </row>
     <row r="11" spans="1:29" ht="18.600000000000001" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B11" s="201"/>
+      <c r="B11" s="210"/>
       <c r="C11" s="113" t="s">
         <v>92</v>
       </c>
@@ -3949,8 +3997,8 @@
       </c>
     </row>
     <row r="12" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="B12" s="201"/>
-      <c r="C12" s="203" t="s">
+      <c r="B12" s="210"/>
+      <c r="C12" s="212" t="s">
         <v>88</v>
       </c>
       <c r="D12" s="119" t="s">
@@ -4001,8 +4049,8 @@
       </c>
     </row>
     <row r="13" spans="1:29" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B13" s="201"/>
-      <c r="C13" s="204"/>
+      <c r="B13" s="210"/>
+      <c r="C13" s="193"/>
       <c r="D13" s="124" t="s">
         <v>145</v>
       </c>
@@ -4033,7 +4081,7 @@
       <c r="AC13" s="108"/>
     </row>
     <row r="14" spans="1:29" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B14" s="202"/>
+      <c r="B14" s="211"/>
       <c r="C14" s="183" t="s">
         <v>92</v>
       </c>
@@ -4101,40 +4149,40 @@
       <c r="Q15" s="95"/>
     </row>
     <row r="16" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="B16" s="206" t="s">
+      <c r="B16" s="213" t="s">
         <v>53</v>
       </c>
-      <c r="C16" s="207"/>
-      <c r="D16" s="212" t="s">
+      <c r="C16" s="214"/>
+      <c r="D16" s="219" t="s">
         <v>54</v>
       </c>
-      <c r="E16" s="191" t="s">
+      <c r="E16" s="200" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="192"/>
-      <c r="G16" s="193"/>
-      <c r="H16" s="214" t="s">
+      <c r="F16" s="201"/>
+      <c r="G16" s="202"/>
+      <c r="H16" s="203" t="s">
         <v>56</v>
       </c>
-      <c r="I16" s="215"/>
-      <c r="J16" s="215"/>
-      <c r="K16" s="215"/>
-      <c r="L16" s="215"/>
-      <c r="M16" s="215"/>
-      <c r="N16" s="215"/>
-      <c r="O16" s="215"/>
-      <c r="P16" s="215"/>
-      <c r="Q16" s="216"/>
+      <c r="I16" s="204"/>
+      <c r="J16" s="204"/>
+      <c r="K16" s="204"/>
+      <c r="L16" s="204"/>
+      <c r="M16" s="204"/>
+      <c r="N16" s="204"/>
+      <c r="O16" s="204"/>
+      <c r="P16" s="204"/>
+      <c r="Q16" s="205"/>
     </row>
     <row r="17" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B17" s="208"/>
-      <c r="C17" s="209"/>
-      <c r="D17" s="213"/>
-      <c r="E17" s="197" t="s">
+      <c r="B17" s="215"/>
+      <c r="C17" s="216"/>
+      <c r="D17" s="220"/>
+      <c r="E17" s="206" t="s">
         <v>97</v>
       </c>
-      <c r="F17" s="198"/>
-      <c r="G17" s="199"/>
+      <c r="F17" s="207"/>
+      <c r="G17" s="208"/>
       <c r="H17" s="177"/>
       <c r="I17" s="178"/>
       <c r="J17" s="178"/>
@@ -4147,9 +4195,9 @@
       <c r="Q17" s="179"/>
     </row>
     <row r="18" spans="2:28" ht="36.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B18" s="210"/>
-      <c r="C18" s="211"/>
-      <c r="D18" s="213"/>
+      <c r="B18" s="217"/>
+      <c r="C18" s="218"/>
+      <c r="D18" s="220"/>
       <c r="E18" s="171" t="s">
         <v>141</v>
       </c>
@@ -4191,10 +4239,10 @@
       </c>
     </row>
     <row r="19" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B19" s="200" t="s">
+      <c r="B19" s="209" t="s">
         <v>101</v>
       </c>
-      <c r="C19" s="203" t="s">
+      <c r="C19" s="212" t="s">
         <v>147</v>
       </c>
       <c r="D19" s="119" t="s">
@@ -4254,8 +4302,8 @@
       </c>
     </row>
     <row r="20" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B20" s="201"/>
-      <c r="C20" s="204"/>
+      <c r="B20" s="210"/>
+      <c r="C20" s="193"/>
       <c r="D20" s="124" t="s">
         <v>145</v>
       </c>
@@ -4285,7 +4333,7 @@
       <c r="AB20" s="108"/>
     </row>
     <row r="21" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B21" s="201"/>
+      <c r="B21" s="210"/>
       <c r="C21" s="184" t="s">
         <v>92</v>
       </c>
@@ -4344,8 +4392,8 @@
       </c>
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B22" s="201"/>
-      <c r="C22" s="203" t="s">
+      <c r="B22" s="210"/>
+      <c r="C22" s="212" t="s">
         <v>152</v>
       </c>
       <c r="D22" s="119" t="s">
@@ -4405,8 +4453,8 @@
       </c>
     </row>
     <row r="23" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B23" s="201"/>
-      <c r="C23" s="204"/>
+      <c r="B23" s="210"/>
+      <c r="C23" s="193"/>
       <c r="D23" s="124" t="s">
         <v>145</v>
       </c>
@@ -4436,7 +4484,7 @@
       <c r="AB23" s="108"/>
     </row>
     <row r="24" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B24" s="201"/>
+      <c r="B24" s="210"/>
       <c r="C24" s="184" t="s">
         <v>92</v>
       </c>
@@ -4495,8 +4543,8 @@
       </c>
     </row>
     <row r="25" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B25" s="201"/>
-      <c r="C25" s="203" t="s">
+      <c r="B25" s="210"/>
+      <c r="C25" s="212" t="s">
         <v>153</v>
       </c>
       <c r="D25" s="119" t="s">
@@ -4556,8 +4604,8 @@
       </c>
     </row>
     <row r="26" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B26" s="201"/>
-      <c r="C26" s="204"/>
+      <c r="B26" s="210"/>
+      <c r="C26" s="193"/>
       <c r="D26" s="124" t="s">
         <v>145</v>
       </c>
@@ -4587,7 +4635,7 @@
       <c r="AB26" s="108"/>
     </row>
     <row r="27" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B27" s="202"/>
+      <c r="B27" s="211"/>
       <c r="C27" s="183" t="s">
         <v>92</v>
       </c>
@@ -4658,40 +4706,40 @@
       <c r="Q28" s="95"/>
     </row>
     <row r="29" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B29" s="206" t="s">
+      <c r="B29" s="213" t="s">
         <v>53</v>
       </c>
-      <c r="C29" s="207"/>
-      <c r="D29" s="212" t="s">
+      <c r="C29" s="214"/>
+      <c r="D29" s="219" t="s">
         <v>54</v>
       </c>
-      <c r="E29" s="191" t="s">
+      <c r="E29" s="200" t="s">
         <v>55</v>
       </c>
-      <c r="F29" s="192"/>
-      <c r="G29" s="193"/>
-      <c r="H29" s="214" t="s">
+      <c r="F29" s="201"/>
+      <c r="G29" s="202"/>
+      <c r="H29" s="203" t="s">
         <v>56</v>
       </c>
-      <c r="I29" s="215"/>
-      <c r="J29" s="215"/>
-      <c r="K29" s="215"/>
-      <c r="L29" s="215"/>
-      <c r="M29" s="215"/>
-      <c r="N29" s="215"/>
-      <c r="O29" s="215"/>
-      <c r="P29" s="215"/>
-      <c r="Q29" s="216"/>
+      <c r="I29" s="204"/>
+      <c r="J29" s="204"/>
+      <c r="K29" s="204"/>
+      <c r="L29" s="204"/>
+      <c r="M29" s="204"/>
+      <c r="N29" s="204"/>
+      <c r="O29" s="204"/>
+      <c r="P29" s="204"/>
+      <c r="Q29" s="205"/>
     </row>
     <row r="30" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B30" s="208"/>
-      <c r="C30" s="209"/>
-      <c r="D30" s="213"/>
-      <c r="E30" s="197" t="s">
+      <c r="B30" s="215"/>
+      <c r="C30" s="216"/>
+      <c r="D30" s="220"/>
+      <c r="E30" s="206" t="s">
         <v>97</v>
       </c>
-      <c r="F30" s="198"/>
-      <c r="G30" s="199"/>
+      <c r="F30" s="207"/>
+      <c r="G30" s="208"/>
       <c r="H30" s="177"/>
       <c r="I30" s="178"/>
       <c r="J30" s="178"/>
@@ -4704,9 +4752,9 @@
       <c r="Q30" s="179"/>
     </row>
     <row r="31" spans="2:28" ht="36.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B31" s="210"/>
-      <c r="C31" s="211"/>
-      <c r="D31" s="213"/>
+      <c r="B31" s="217"/>
+      <c r="C31" s="218"/>
+      <c r="D31" s="220"/>
       <c r="E31" s="171" t="s">
         <v>141</v>
       </c>
@@ -4748,10 +4796,10 @@
       </c>
     </row>
     <row r="32" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B32" s="200" t="s">
+      <c r="B32" s="209" t="s">
         <v>96</v>
       </c>
-      <c r="C32" s="203" t="s">
+      <c r="C32" s="212" t="s">
         <v>81</v>
       </c>
       <c r="D32" s="119" t="s">
@@ -4811,8 +4859,8 @@
       </c>
     </row>
     <row r="33" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B33" s="201"/>
-      <c r="C33" s="204"/>
+      <c r="B33" s="210"/>
+      <c r="C33" s="193"/>
       <c r="D33" s="124" t="s">
         <v>145</v>
       </c>
@@ -4842,7 +4890,7 @@
       <c r="AB33" s="108"/>
     </row>
     <row r="34" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B34" s="201"/>
+      <c r="B34" s="210"/>
       <c r="C34" s="184" t="s">
         <v>92</v>
       </c>
@@ -4901,8 +4949,8 @@
       </c>
     </row>
     <row r="35" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B35" s="201"/>
-      <c r="C35" s="203" t="s">
+      <c r="B35" s="210"/>
+      <c r="C35" s="212" t="s">
         <v>80</v>
       </c>
       <c r="D35" s="119" t="s">
@@ -4962,8 +5010,8 @@
       </c>
     </row>
     <row r="36" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B36" s="201"/>
-      <c r="C36" s="204"/>
+      <c r="B36" s="210"/>
+      <c r="C36" s="193"/>
       <c r="D36" s="124" t="s">
         <v>145</v>
       </c>
@@ -4993,7 +5041,7 @@
       <c r="AB36" s="108"/>
     </row>
     <row r="37" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B37" s="201"/>
+      <c r="B37" s="210"/>
       <c r="C37" s="184" t="s">
         <v>92</v>
       </c>
@@ -5052,8 +5100,8 @@
       </c>
     </row>
     <row r="38" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B38" s="201"/>
-      <c r="C38" s="203" t="s">
+      <c r="B38" s="210"/>
+      <c r="C38" s="212" t="s">
         <v>94</v>
       </c>
       <c r="D38" s="119" t="s">
@@ -5113,8 +5161,8 @@
       </c>
     </row>
     <row r="39" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B39" s="201"/>
-      <c r="C39" s="204"/>
+      <c r="B39" s="210"/>
+      <c r="C39" s="193"/>
       <c r="D39" s="124" t="s">
         <v>145</v>
       </c>
@@ -5144,7 +5192,7 @@
       <c r="AB39" s="108"/>
     </row>
     <row r="40" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B40" s="201"/>
+      <c r="B40" s="210"/>
       <c r="C40" s="184" t="s">
         <v>92</v>
       </c>
@@ -5203,8 +5251,8 @@
       </c>
     </row>
     <row r="41" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B41" s="201"/>
-      <c r="C41" s="203" t="s">
+      <c r="B41" s="210"/>
+      <c r="C41" s="212" t="s">
         <v>154</v>
       </c>
       <c r="D41" s="119" t="s">
@@ -5255,8 +5303,8 @@
       </c>
     </row>
     <row r="42" spans="2:28" ht="18.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B42" s="201"/>
-      <c r="C42" s="204"/>
+      <c r="B42" s="210"/>
+      <c r="C42" s="193"/>
       <c r="D42" s="124" t="s">
         <v>145</v>
       </c>
@@ -5286,7 +5334,7 @@
       <c r="AB42" s="108"/>
     </row>
     <row r="43" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B43" s="202"/>
+      <c r="B43" s="211"/>
       <c r="C43" s="183" t="s">
         <v>92</v>
       </c>
@@ -5620,6 +5668,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:Q2"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="B5:B14"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="B2:C4"/>
+    <mergeCell ref="B16:C18"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="D16:D18"/>
     <mergeCell ref="E16:G16"/>
     <mergeCell ref="H16:Q16"/>
     <mergeCell ref="E17:G17"/>
@@ -5636,82 +5696,70 @@
     <mergeCell ref="B19:B27"/>
     <mergeCell ref="C19:C20"/>
     <mergeCell ref="C22:C23"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="B2:C4"/>
-    <mergeCell ref="B16:C18"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:Q2"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="B5:B14"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="C12:C13"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="H5:Q6">
-    <cfRule type="cellIs" dxfId="31" priority="1" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="27" priority="1" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H8:Q8">
-    <cfRule type="cellIs" dxfId="30" priority="18" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="26" priority="18" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H9:Q9">
-    <cfRule type="cellIs" dxfId="29" priority="19" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="25" priority="19" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H10:Q10">
-    <cfRule type="cellIs" dxfId="28" priority="20" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="24" priority="20" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12:Q13">
-    <cfRule type="cellIs" dxfId="27" priority="4" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="23" priority="4" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H19:Q20">
-    <cfRule type="cellIs" dxfId="26" priority="16" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="22" priority="16" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H22:Q22">
-    <cfRule type="cellIs" dxfId="25" priority="10" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="21" priority="10" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H23:Q23 H39:Q39 H42:Q42">
-    <cfRule type="cellIs" dxfId="24" priority="21" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="20" priority="21" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H25:Q26">
-    <cfRule type="cellIs" dxfId="23" priority="9" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="19" priority="9" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H32:Q33">
-    <cfRule type="cellIs" dxfId="22" priority="8" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="18" priority="8" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H35:Q36">
-    <cfRule type="cellIs" dxfId="21" priority="7" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="17" priority="7" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H38:Q38">
-    <cfRule type="cellIs" dxfId="20" priority="6" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="16" priority="6" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H41:Q41">
-    <cfRule type="cellIs" dxfId="19" priority="3" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="15" priority="3" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5766,40 +5814,40 @@
   <sheetData>
     <row r="1" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="2" spans="2:29" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="220" t="s">
+      <c r="B2" s="224" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="221"/>
-      <c r="D2" s="229" t="s">
+      <c r="C2" s="225"/>
+      <c r="D2" s="236" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="237" t="s">
+      <c r="E2" s="244" t="s">
         <v>55</v>
       </c>
-      <c r="F2" s="238"/>
-      <c r="G2" s="239"/>
-      <c r="H2" s="231" t="s">
+      <c r="F2" s="245"/>
+      <c r="G2" s="246"/>
+      <c r="H2" s="238" t="s">
         <v>56</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
-      <c r="M2" s="232"/>
-      <c r="N2" s="232"/>
-      <c r="O2" s="232"/>
-      <c r="P2" s="232"/>
-      <c r="Q2" s="233"/>
+      <c r="I2" s="239"/>
+      <c r="J2" s="239"/>
+      <c r="K2" s="239"/>
+      <c r="L2" s="239"/>
+      <c r="M2" s="239"/>
+      <c r="N2" s="239"/>
+      <c r="O2" s="239"/>
+      <c r="P2" s="239"/>
+      <c r="Q2" s="240"/>
     </row>
     <row r="3" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B3" s="222"/>
-      <c r="C3" s="223"/>
-      <c r="D3" s="230"/>
-      <c r="E3" s="234" t="s">
+      <c r="B3" s="226"/>
+      <c r="C3" s="227"/>
+      <c r="D3" s="237"/>
+      <c r="E3" s="241" t="s">
         <v>97</v>
       </c>
-      <c r="F3" s="235"/>
-      <c r="G3" s="236"/>
+      <c r="F3" s="242"/>
+      <c r="G3" s="243"/>
       <c r="H3" s="22"/>
       <c r="I3" s="21"/>
       <c r="J3" s="21"/>
@@ -5812,9 +5860,9 @@
       <c r="Q3" s="20"/>
     </row>
     <row r="4" spans="2:29" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B4" s="224"/>
-      <c r="C4" s="225"/>
-      <c r="D4" s="230"/>
+      <c r="B4" s="228"/>
+      <c r="C4" s="229"/>
+      <c r="D4" s="237"/>
       <c r="E4" s="85" t="s">
         <v>141</v>
       </c>
@@ -5856,10 +5904,10 @@
       </c>
     </row>
     <row r="5" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B5" s="226" t="s">
+      <c r="B5" s="233" t="s">
         <v>90</v>
       </c>
-      <c r="C5" s="217" t="s">
+      <c r="C5" s="230" t="s">
         <v>138</v>
       </c>
       <c r="D5" s="33" t="s">
@@ -5913,8 +5961,8 @@
       </c>
     </row>
     <row r="6" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B6" s="227"/>
-      <c r="C6" s="218"/>
+      <c r="B6" s="234"/>
+      <c r="C6" s="231"/>
       <c r="D6" s="26" t="s">
         <v>103</v>
       </c>
@@ -5967,8 +6015,8 @@
       <c r="AC6" s="19"/>
     </row>
     <row r="7" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B7" s="227"/>
-      <c r="C7" s="219"/>
+      <c r="B7" s="234"/>
+      <c r="C7" s="232"/>
       <c r="D7" s="83" t="s">
         <v>71</v>
       </c>
@@ -6019,7 +6067,7 @@
       <c r="AC7" s="19"/>
     </row>
     <row r="8" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B8" s="227"/>
+      <c r="B8" s="234"/>
       <c r="C8" s="36" t="s">
         <v>92</v>
       </c>
@@ -6073,8 +6121,8 @@
       </c>
     </row>
     <row r="9" spans="2:29" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B9" s="227"/>
-      <c r="C9" s="217" t="s">
+      <c r="B9" s="234"/>
+      <c r="C9" s="230" t="s">
         <v>102</v>
       </c>
       <c r="D9" s="33" t="s">
@@ -6125,8 +6173,8 @@
       </c>
     </row>
     <row r="10" spans="2:29" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B10" s="227"/>
-      <c r="C10" s="218"/>
+      <c r="B10" s="234"/>
+      <c r="C10" s="231"/>
       <c r="D10" s="26" t="s">
         <v>103</v>
       </c>
@@ -6177,8 +6225,8 @@
       <c r="AC10" s="19"/>
     </row>
     <row r="11" spans="2:29" ht="15.6" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B11" s="227"/>
-      <c r="C11" s="219"/>
+      <c r="B11" s="234"/>
+      <c r="C11" s="232"/>
       <c r="D11" s="34" t="s">
         <v>71</v>
       </c>
@@ -6229,7 +6277,7 @@
       <c r="AC11" s="19"/>
     </row>
     <row r="12" spans="2:29" ht="15.6" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B12" s="227"/>
+      <c r="B12" s="234"/>
       <c r="C12" s="36" t="s">
         <v>92</v>
       </c>
@@ -6283,8 +6331,8 @@
       </c>
     </row>
     <row r="13" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B13" s="227"/>
-      <c r="C13" s="217" t="s">
+      <c r="B13" s="234"/>
+      <c r="C13" s="230" t="s">
         <v>143</v>
       </c>
       <c r="D13" s="33" t="s">
@@ -6335,8 +6383,8 @@
       </c>
     </row>
     <row r="14" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B14" s="227"/>
-      <c r="C14" s="218"/>
+      <c r="B14" s="234"/>
+      <c r="C14" s="231"/>
       <c r="D14" s="26" t="s">
         <v>103</v>
       </c>
@@ -6387,8 +6435,8 @@
       <c r="AC14" s="19"/>
     </row>
     <row r="15" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B15" s="227"/>
-      <c r="C15" s="219"/>
+      <c r="B15" s="234"/>
+      <c r="C15" s="232"/>
       <c r="D15" s="83" t="s">
         <v>71</v>
       </c>
@@ -6439,7 +6487,7 @@
       <c r="AC15" s="19"/>
     </row>
     <row r="16" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B16" s="228"/>
+      <c r="B16" s="235"/>
       <c r="C16" s="32" t="s">
         <v>92</v>
       </c>
@@ -6505,40 +6553,40 @@
       <c r="Q17" s="12"/>
     </row>
     <row r="18" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B18" s="220" t="s">
+      <c r="B18" s="224" t="s">
         <v>53</v>
       </c>
-      <c r="C18" s="221"/>
-      <c r="D18" s="229" t="s">
+      <c r="C18" s="225"/>
+      <c r="D18" s="236" t="s">
         <v>54</v>
       </c>
-      <c r="E18" s="237" t="s">
+      <c r="E18" s="244" t="s">
         <v>55</v>
       </c>
-      <c r="F18" s="238"/>
-      <c r="G18" s="239"/>
-      <c r="H18" s="243" t="s">
+      <c r="F18" s="245"/>
+      <c r="G18" s="246"/>
+      <c r="H18" s="250" t="s">
         <v>56</v>
       </c>
-      <c r="I18" s="244"/>
-      <c r="J18" s="244"/>
-      <c r="K18" s="244"/>
-      <c r="L18" s="244"/>
-      <c r="M18" s="244"/>
-      <c r="N18" s="244"/>
-      <c r="O18" s="244"/>
-      <c r="P18" s="244"/>
-      <c r="Q18" s="245"/>
+      <c r="I18" s="251"/>
+      <c r="J18" s="251"/>
+      <c r="K18" s="251"/>
+      <c r="L18" s="251"/>
+      <c r="M18" s="251"/>
+      <c r="N18" s="251"/>
+      <c r="O18" s="251"/>
+      <c r="P18" s="251"/>
+      <c r="Q18" s="252"/>
     </row>
     <row r="19" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B19" s="222"/>
-      <c r="C19" s="223"/>
-      <c r="D19" s="230"/>
-      <c r="E19" s="234" t="s">
+      <c r="B19" s="226"/>
+      <c r="C19" s="227"/>
+      <c r="D19" s="237"/>
+      <c r="E19" s="241" t="s">
         <v>97</v>
       </c>
-      <c r="F19" s="235"/>
-      <c r="G19" s="236"/>
+      <c r="F19" s="242"/>
+      <c r="G19" s="243"/>
       <c r="H19" s="67"/>
       <c r="I19" s="68"/>
       <c r="J19" s="68"/>
@@ -6551,9 +6599,9 @@
       <c r="Q19" s="69"/>
     </row>
     <row r="20" spans="2:28" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B20" s="224"/>
-      <c r="C20" s="225"/>
-      <c r="D20" s="230"/>
+      <c r="B20" s="228"/>
+      <c r="C20" s="229"/>
+      <c r="D20" s="237"/>
       <c r="E20" s="85" t="s">
         <v>141</v>
       </c>
@@ -6595,10 +6643,10 @@
       </c>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B21" s="226" t="s">
+      <c r="B21" s="233" t="s">
         <v>101</v>
       </c>
-      <c r="C21" s="217" t="s">
+      <c r="C21" s="230" t="s">
         <v>100</v>
       </c>
       <c r="D21" s="33" t="s">
@@ -6658,8 +6706,8 @@
       </c>
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B22" s="227"/>
-      <c r="C22" s="218"/>
+      <c r="B22" s="234"/>
+      <c r="C22" s="231"/>
       <c r="D22" s="26" t="s">
         <v>103</v>
       </c>
@@ -6713,8 +6761,8 @@
       <c r="AB22" s="19"/>
     </row>
     <row r="23" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B23" s="227"/>
-      <c r="C23" s="219"/>
+      <c r="B23" s="234"/>
+      <c r="C23" s="232"/>
       <c r="D23" s="83" t="s">
         <v>71</v>
       </c>
@@ -6768,7 +6816,7 @@
       <c r="AB23" s="19"/>
     </row>
     <row r="24" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B24" s="227"/>
+      <c r="B24" s="234"/>
       <c r="C24" s="36" t="s">
         <v>92</v>
       </c>
@@ -6824,8 +6872,8 @@
       </c>
     </row>
     <row r="25" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B25" s="227"/>
-      <c r="C25" s="217" t="s">
+      <c r="B25" s="234"/>
+      <c r="C25" s="230" t="s">
         <v>99</v>
       </c>
       <c r="D25" s="33" t="s">
@@ -6885,8 +6933,8 @@
       </c>
     </row>
     <row r="26" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B26" s="227"/>
-      <c r="C26" s="218"/>
+      <c r="B26" s="234"/>
+      <c r="C26" s="231"/>
       <c r="D26" s="26" t="s">
         <v>103</v>
       </c>
@@ -6940,8 +6988,8 @@
       <c r="AB26" s="19"/>
     </row>
     <row r="27" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B27" s="227"/>
-      <c r="C27" s="219"/>
+      <c r="B27" s="234"/>
+      <c r="C27" s="232"/>
       <c r="D27" s="83" t="s">
         <v>71</v>
       </c>
@@ -6995,7 +7043,7 @@
       <c r="AB27" s="19"/>
     </row>
     <row r="28" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B28" s="227"/>
+      <c r="B28" s="234"/>
       <c r="C28" s="36" t="s">
         <v>92</v>
       </c>
@@ -7051,8 +7099,8 @@
       </c>
     </row>
     <row r="29" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B29" s="227"/>
-      <c r="C29" s="217" t="s">
+      <c r="B29" s="234"/>
+      <c r="C29" s="230" t="s">
         <v>98</v>
       </c>
       <c r="D29" s="33" t="s">
@@ -7112,8 +7160,8 @@
       </c>
     </row>
     <row r="30" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B30" s="227"/>
-      <c r="C30" s="218"/>
+      <c r="B30" s="234"/>
+      <c r="C30" s="231"/>
       <c r="D30" s="26" t="s">
         <v>103</v>
       </c>
@@ -7167,8 +7215,8 @@
       <c r="AB30" s="19"/>
     </row>
     <row r="31" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B31" s="227"/>
-      <c r="C31" s="219"/>
+      <c r="B31" s="234"/>
+      <c r="C31" s="232"/>
       <c r="D31" s="83" t="s">
         <v>71</v>
       </c>
@@ -7222,7 +7270,7 @@
       <c r="AB31" s="19"/>
     </row>
     <row r="32" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B32" s="228"/>
+      <c r="B32" s="235"/>
       <c r="C32" s="32" t="s">
         <v>92</v>
       </c>
@@ -7290,40 +7338,40 @@
       <c r="Q33" s="12"/>
     </row>
     <row r="34" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B34" s="220" t="s">
+      <c r="B34" s="224" t="s">
         <v>53</v>
       </c>
-      <c r="C34" s="221"/>
-      <c r="D34" s="229" t="s">
+      <c r="C34" s="225"/>
+      <c r="D34" s="236" t="s">
         <v>54</v>
       </c>
-      <c r="E34" s="237" t="s">
+      <c r="E34" s="244" t="s">
         <v>55</v>
       </c>
-      <c r="F34" s="238"/>
-      <c r="G34" s="239"/>
-      <c r="H34" s="243" t="s">
+      <c r="F34" s="245"/>
+      <c r="G34" s="246"/>
+      <c r="H34" s="250" t="s">
         <v>56</v>
       </c>
-      <c r="I34" s="244"/>
-      <c r="J34" s="244"/>
-      <c r="K34" s="244"/>
-      <c r="L34" s="244"/>
-      <c r="M34" s="244"/>
-      <c r="N34" s="244"/>
-      <c r="O34" s="244"/>
-      <c r="P34" s="244"/>
-      <c r="Q34" s="245"/>
+      <c r="I34" s="251"/>
+      <c r="J34" s="251"/>
+      <c r="K34" s="251"/>
+      <c r="L34" s="251"/>
+      <c r="M34" s="251"/>
+      <c r="N34" s="251"/>
+      <c r="O34" s="251"/>
+      <c r="P34" s="251"/>
+      <c r="Q34" s="252"/>
     </row>
     <row r="35" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B35" s="222"/>
-      <c r="C35" s="223"/>
-      <c r="D35" s="230"/>
-      <c r="E35" s="234" t="s">
+      <c r="B35" s="226"/>
+      <c r="C35" s="227"/>
+      <c r="D35" s="237"/>
+      <c r="E35" s="241" t="s">
         <v>97</v>
       </c>
-      <c r="F35" s="235"/>
-      <c r="G35" s="236"/>
+      <c r="F35" s="242"/>
+      <c r="G35" s="243"/>
       <c r="H35" s="67"/>
       <c r="I35" s="68"/>
       <c r="J35" s="68"/>
@@ -7336,9 +7384,9 @@
       <c r="Q35" s="69"/>
     </row>
     <row r="36" spans="2:28" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B36" s="224"/>
-      <c r="C36" s="225"/>
-      <c r="D36" s="230"/>
+      <c r="B36" s="228"/>
+      <c r="C36" s="229"/>
+      <c r="D36" s="237"/>
       <c r="E36" s="85" t="s">
         <v>141</v>
       </c>
@@ -7380,10 +7428,10 @@
       </c>
     </row>
     <row r="37" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B37" s="226" t="s">
+      <c r="B37" s="233" t="s">
         <v>96</v>
       </c>
-      <c r="C37" s="217" t="s">
+      <c r="C37" s="230" t="s">
         <v>95</v>
       </c>
       <c r="D37" s="33" t="s">
@@ -7443,8 +7491,8 @@
       </c>
     </row>
     <row r="38" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B38" s="227"/>
-      <c r="C38" s="218"/>
+      <c r="B38" s="234"/>
+      <c r="C38" s="231"/>
       <c r="D38" s="26" t="s">
         <v>103</v>
       </c>
@@ -7498,8 +7546,8 @@
       <c r="AB38" s="19"/>
     </row>
     <row r="39" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B39" s="227"/>
-      <c r="C39" s="219"/>
+      <c r="B39" s="234"/>
+      <c r="C39" s="232"/>
       <c r="D39" s="83" t="s">
         <v>71</v>
       </c>
@@ -7553,7 +7601,7 @@
       <c r="AB39" s="19"/>
     </row>
     <row r="40" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B40" s="227"/>
+      <c r="B40" s="234"/>
       <c r="C40" s="36" t="s">
         <v>92</v>
       </c>
@@ -7609,8 +7657,8 @@
       </c>
     </row>
     <row r="41" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B41" s="227"/>
-      <c r="C41" s="217" t="s">
+      <c r="B41" s="234"/>
+      <c r="C41" s="230" t="s">
         <v>80</v>
       </c>
       <c r="D41" s="33" t="s">
@@ -7670,8 +7718,8 @@
       </c>
     </row>
     <row r="42" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B42" s="227"/>
-      <c r="C42" s="218"/>
+      <c r="B42" s="234"/>
+      <c r="C42" s="231"/>
       <c r="D42" s="26" t="s">
         <v>103</v>
       </c>
@@ -7725,8 +7773,8 @@
       <c r="AB42" s="19"/>
     </row>
     <row r="43" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B43" s="227"/>
-      <c r="C43" s="219"/>
+      <c r="B43" s="234"/>
+      <c r="C43" s="232"/>
       <c r="D43" s="83" t="s">
         <v>71</v>
       </c>
@@ -7780,7 +7828,7 @@
       <c r="AB43" s="19"/>
     </row>
     <row r="44" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B44" s="227"/>
+      <c r="B44" s="234"/>
       <c r="C44" s="36" t="s">
         <v>92</v>
       </c>
@@ -7836,8 +7884,8 @@
       </c>
     </row>
     <row r="45" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B45" s="227"/>
-      <c r="C45" s="217" t="s">
+      <c r="B45" s="234"/>
+      <c r="C45" s="230" t="s">
         <v>94</v>
       </c>
       <c r="D45" s="33" t="s">
@@ -7897,8 +7945,8 @@
       </c>
     </row>
     <row r="46" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B46" s="227"/>
-      <c r="C46" s="218"/>
+      <c r="B46" s="234"/>
+      <c r="C46" s="231"/>
       <c r="D46" s="26" t="s">
         <v>103</v>
       </c>
@@ -7952,8 +8000,8 @@
       <c r="AB46" s="19"/>
     </row>
     <row r="47" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B47" s="227"/>
-      <c r="C47" s="219"/>
+      <c r="B47" s="234"/>
+      <c r="C47" s="232"/>
       <c r="D47" s="83" t="s">
         <v>71</v>
       </c>
@@ -8007,7 +8055,7 @@
       <c r="AB47" s="19"/>
     </row>
     <row r="48" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B48" s="227"/>
+      <c r="B48" s="234"/>
       <c r="C48" s="36" t="s">
         <v>92</v>
       </c>
@@ -8063,14 +8111,14 @@
       </c>
     </row>
     <row r="49" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B49" s="227"/>
-      <c r="C49" s="217" t="s">
+      <c r="B49" s="234"/>
+      <c r="C49" s="230" t="s">
         <v>93</v>
       </c>
       <c r="D49" s="33" t="s">
         <v>144</v>
       </c>
-      <c r="E49" s="240"/>
+      <c r="E49" s="247"/>
       <c r="F49" s="87"/>
       <c r="G49" s="31"/>
       <c r="H49" s="64" t="e">
@@ -8115,12 +8163,12 @@
       </c>
     </row>
     <row r="50" spans="2:28" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B50" s="227"/>
-      <c r="C50" s="218"/>
+      <c r="B50" s="234"/>
+      <c r="C50" s="231"/>
       <c r="D50" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="E50" s="241"/>
+      <c r="E50" s="248"/>
       <c r="F50" s="88"/>
       <c r="G50" s="28"/>
       <c r="H50" s="73">
@@ -8166,12 +8214,12 @@
       <c r="AB50" s="19"/>
     </row>
     <row r="51" spans="2:28" ht="18.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B51" s="227"/>
-      <c r="C51" s="219"/>
+      <c r="B51" s="234"/>
+      <c r="C51" s="232"/>
       <c r="D51" s="83" t="s">
         <v>71</v>
       </c>
-      <c r="E51" s="242"/>
+      <c r="E51" s="249"/>
       <c r="F51" s="89"/>
       <c r="G51" s="54"/>
       <c r="H51" s="75">
@@ -8217,7 +8265,7 @@
       <c r="AB51" s="19"/>
     </row>
     <row r="52" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B52" s="228"/>
+      <c r="B52" s="235"/>
       <c r="C52" s="32" t="s">
         <v>92</v>
       </c>
@@ -8669,16 +8717,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B2:C4"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="B18:C20"/>
-    <mergeCell ref="B5:B16"/>
-    <mergeCell ref="B21:B32"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="C29:C31"/>
-    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="C41:C43"/>
+    <mergeCell ref="C45:C47"/>
+    <mergeCell ref="C49:C51"/>
+    <mergeCell ref="B34:C36"/>
+    <mergeCell ref="B37:B52"/>
+    <mergeCell ref="C37:C39"/>
     <mergeCell ref="D2:D4"/>
     <mergeCell ref="H2:Q2"/>
     <mergeCell ref="E3:G3"/>
@@ -8692,86 +8736,90 @@
     <mergeCell ref="D18:D20"/>
     <mergeCell ref="E18:G18"/>
     <mergeCell ref="E19:G19"/>
-    <mergeCell ref="C41:C43"/>
-    <mergeCell ref="C45:C47"/>
-    <mergeCell ref="C49:C51"/>
-    <mergeCell ref="B34:C36"/>
-    <mergeCell ref="B37:B52"/>
-    <mergeCell ref="C37:C39"/>
+    <mergeCell ref="B2:C4"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="B18:C20"/>
+    <mergeCell ref="B5:B16"/>
+    <mergeCell ref="B21:B32"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="C25:C27"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="H5:Q7">
-    <cfRule type="cellIs" dxfId="18" priority="11" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="14" priority="11" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H9:Q9">
-    <cfRule type="cellIs" dxfId="17" priority="10" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="13" priority="10" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H10:Q10">
-    <cfRule type="cellIs" dxfId="16" priority="12" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="12" priority="12" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11:Q11">
-    <cfRule type="cellIs" dxfId="15" priority="14" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="11" priority="14" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13:Q13">
-    <cfRule type="cellIs" dxfId="14" priority="9" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="10" priority="9" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H14:Q14 H22:Q22 H26:Q26 H30:Q30 H38:Q38 H42:Q42 H46:Q46 H50:Q50">
-    <cfRule type="cellIs" dxfId="13" priority="16" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="9" priority="16" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:Q15 H23:Q23 H31:Q31 H39:Q39 H43:Q43">
-    <cfRule type="cellIs" dxfId="12" priority="18" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="8" priority="18" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H21:Q21">
-    <cfRule type="cellIs" dxfId="11" priority="8" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="7" priority="8" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H25:Q25">
-    <cfRule type="cellIs" dxfId="10" priority="7" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="6" priority="7" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27:Q27 H47:Q47 H51:Q51">
-    <cfRule type="cellIs" dxfId="9" priority="15" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="5" priority="15" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H29:Q29">
-    <cfRule type="cellIs" dxfId="8" priority="6" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H37:Q37">
-    <cfRule type="cellIs" dxfId="7" priority="5" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H41:Q41">
-    <cfRule type="cellIs" dxfId="6" priority="4" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H45:Q45">
-    <cfRule type="cellIs" dxfId="5" priority="3" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H49:Q49">
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>

--- a/tool/track-aggregator/template/統合結果.xlsx
+++ b/tool/track-aggregator/template/統合結果.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ishid\Desktop\project_management\tool\track-aggregator\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CF0E662-3C7A-4957-952B-ADBBBE58DC3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB6A903B-5160-4478-8B43-4E7F8C93D379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -953,19 +953,19 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>テスト</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>アンケート</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>{実施データ}</t>
   </si>
   <si>
     <t>{コースデータ}</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アンケート</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>テスト</t>
+    <phoneticPr fontId="3"/>
   </si>
 </sst>
 </file>
@@ -1147,7 +1147,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="54">
+  <borders count="53">
     <border>
       <left/>
       <right/>
@@ -1799,19 +1799,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -2435,13 +2422,13 @@
     <xf numFmtId="0" fontId="10" fillId="9" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="10" fillId="8" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="8" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="8" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="9" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2489,31 +2476,13 @@
     <xf numFmtId="0" fontId="10" fillId="7" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="10" fillId="8" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="10" fillId="8" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="10" fillId="8" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2525,6 +2494,24 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -2585,19 +2572,19 @@
     <xf numFmtId="179" fontId="5" fillId="8" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3217,10 +3204,10 @@
       <c r="C2" s="185"/>
       <c r="D2" s="185"/>
       <c r="E2" s="185"/>
-      <c r="F2" s="255" t="s">
-        <v>166</v>
-      </c>
-      <c r="G2" s="254"/>
+      <c r="F2" s="254" t="s">
+        <v>164</v>
+      </c>
+      <c r="G2" s="255"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" s="187" t="s">
@@ -3235,14 +3222,14 @@
       <c r="D3" s="187" t="s">
         <v>160</v>
       </c>
-      <c r="E3" s="187" t="s">
+      <c r="E3" s="253" t="s">
         <v>161</v>
       </c>
-      <c r="F3" s="253" t="s">
-        <v>163</v>
-      </c>
-      <c r="G3" s="253" t="s">
-        <v>164</v>
+      <c r="F3" s="96" t="s">
+        <v>166</v>
+      </c>
+      <c r="G3" s="93" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
@@ -3254,7 +3241,7 @@
       <c r="D4" s="188"/>
       <c r="E4" s="188"/>
       <c r="F4" s="256" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G4" s="257"/>
     </row>
@@ -3576,18 +3563,18 @@
       </c>
       <c r="F2" s="201"/>
       <c r="G2" s="202"/>
-      <c r="H2" s="221" t="s">
+      <c r="H2" s="203" t="s">
         <v>56</v>
       </c>
-      <c r="I2" s="222"/>
-      <c r="J2" s="222"/>
-      <c r="K2" s="222"/>
-      <c r="L2" s="222"/>
-      <c r="M2" s="222"/>
-      <c r="N2" s="222"/>
-      <c r="O2" s="222"/>
-      <c r="P2" s="222"/>
-      <c r="Q2" s="223"/>
+      <c r="I2" s="204"/>
+      <c r="J2" s="204"/>
+      <c r="K2" s="204"/>
+      <c r="L2" s="204"/>
+      <c r="M2" s="204"/>
+      <c r="N2" s="204"/>
+      <c r="O2" s="204"/>
+      <c r="P2" s="204"/>
+      <c r="Q2" s="205"/>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.45">
       <c r="B3" s="215"/>
@@ -4161,18 +4148,18 @@
       </c>
       <c r="F16" s="201"/>
       <c r="G16" s="202"/>
-      <c r="H16" s="203" t="s">
+      <c r="H16" s="221" t="s">
         <v>56</v>
       </c>
-      <c r="I16" s="204"/>
-      <c r="J16" s="204"/>
-      <c r="K16" s="204"/>
-      <c r="L16" s="204"/>
-      <c r="M16" s="204"/>
-      <c r="N16" s="204"/>
-      <c r="O16" s="204"/>
-      <c r="P16" s="204"/>
-      <c r="Q16" s="205"/>
+      <c r="I16" s="222"/>
+      <c r="J16" s="222"/>
+      <c r="K16" s="222"/>
+      <c r="L16" s="222"/>
+      <c r="M16" s="222"/>
+      <c r="N16" s="222"/>
+      <c r="O16" s="222"/>
+      <c r="P16" s="222"/>
+      <c r="Q16" s="223"/>
     </row>
     <row r="17" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B17" s="215"/>
@@ -4718,18 +4705,18 @@
       </c>
       <c r="F29" s="201"/>
       <c r="G29" s="202"/>
-      <c r="H29" s="203" t="s">
+      <c r="H29" s="221" t="s">
         <v>56</v>
       </c>
-      <c r="I29" s="204"/>
-      <c r="J29" s="204"/>
-      <c r="K29" s="204"/>
-      <c r="L29" s="204"/>
-      <c r="M29" s="204"/>
-      <c r="N29" s="204"/>
-      <c r="O29" s="204"/>
-      <c r="P29" s="204"/>
-      <c r="Q29" s="205"/>
+      <c r="I29" s="222"/>
+      <c r="J29" s="222"/>
+      <c r="K29" s="222"/>
+      <c r="L29" s="222"/>
+      <c r="M29" s="222"/>
+      <c r="N29" s="222"/>
+      <c r="O29" s="222"/>
+      <c r="P29" s="222"/>
+      <c r="Q29" s="223"/>
     </row>
     <row r="30" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B30" s="215"/>
@@ -5668,18 +5655,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:Q2"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="B5:B14"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="B2:C4"/>
-    <mergeCell ref="B16:C18"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="D16:D18"/>
     <mergeCell ref="E16:G16"/>
     <mergeCell ref="H16:Q16"/>
     <mergeCell ref="E17:G17"/>
@@ -5696,6 +5671,18 @@
     <mergeCell ref="B19:B27"/>
     <mergeCell ref="C19:C20"/>
     <mergeCell ref="C22:C23"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="B2:C4"/>
+    <mergeCell ref="B16:C18"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:Q2"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="B5:B14"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="C12:C13"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="H5:Q6">
@@ -5814,10 +5801,10 @@
   <sheetData>
     <row r="1" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="2" spans="2:29" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="224" t="s">
+      <c r="B2" s="227" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="225"/>
+      <c r="C2" s="228"/>
       <c r="D2" s="236" t="s">
         <v>54</v>
       </c>
@@ -5840,8 +5827,8 @@
       <c r="Q2" s="240"/>
     </row>
     <row r="3" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B3" s="226"/>
-      <c r="C3" s="227"/>
+      <c r="B3" s="229"/>
+      <c r="C3" s="230"/>
       <c r="D3" s="237"/>
       <c r="E3" s="241" t="s">
         <v>97</v>
@@ -5860,8 +5847,8 @@
       <c r="Q3" s="20"/>
     </row>
     <row r="4" spans="2:29" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B4" s="228"/>
-      <c r="C4" s="229"/>
+      <c r="B4" s="231"/>
+      <c r="C4" s="232"/>
       <c r="D4" s="237"/>
       <c r="E4" s="85" t="s">
         <v>141</v>
@@ -5907,7 +5894,7 @@
       <c r="B5" s="233" t="s">
         <v>90</v>
       </c>
-      <c r="C5" s="230" t="s">
+      <c r="C5" s="224" t="s">
         <v>138</v>
       </c>
       <c r="D5" s="33" t="s">
@@ -5962,7 +5949,7 @@
     </row>
     <row r="6" spans="2:29" x14ac:dyDescent="0.45">
       <c r="B6" s="234"/>
-      <c r="C6" s="231"/>
+      <c r="C6" s="225"/>
       <c r="D6" s="26" t="s">
         <v>103</v>
       </c>
@@ -6016,7 +6003,7 @@
     </row>
     <row r="7" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B7" s="234"/>
-      <c r="C7" s="232"/>
+      <c r="C7" s="226"/>
       <c r="D7" s="83" t="s">
         <v>71</v>
       </c>
@@ -6122,7 +6109,7 @@
     </row>
     <row r="9" spans="2:29" hidden="1" x14ac:dyDescent="0.45">
       <c r="B9" s="234"/>
-      <c r="C9" s="230" t="s">
+      <c r="C9" s="224" t="s">
         <v>102</v>
       </c>
       <c r="D9" s="33" t="s">
@@ -6174,7 +6161,7 @@
     </row>
     <row r="10" spans="2:29" hidden="1" x14ac:dyDescent="0.45">
       <c r="B10" s="234"/>
-      <c r="C10" s="231"/>
+      <c r="C10" s="225"/>
       <c r="D10" s="26" t="s">
         <v>103</v>
       </c>
@@ -6226,7 +6213,7 @@
     </row>
     <row r="11" spans="2:29" ht="15.6" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B11" s="234"/>
-      <c r="C11" s="232"/>
+      <c r="C11" s="226"/>
       <c r="D11" s="34" t="s">
         <v>71</v>
       </c>
@@ -6332,7 +6319,7 @@
     </row>
     <row r="13" spans="2:29" x14ac:dyDescent="0.45">
       <c r="B13" s="234"/>
-      <c r="C13" s="230" t="s">
+      <c r="C13" s="224" t="s">
         <v>143</v>
       </c>
       <c r="D13" s="33" t="s">
@@ -6384,7 +6371,7 @@
     </row>
     <row r="14" spans="2:29" x14ac:dyDescent="0.45">
       <c r="B14" s="234"/>
-      <c r="C14" s="231"/>
+      <c r="C14" s="225"/>
       <c r="D14" s="26" t="s">
         <v>103</v>
       </c>
@@ -6436,7 +6423,7 @@
     </row>
     <row r="15" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B15" s="234"/>
-      <c r="C15" s="232"/>
+      <c r="C15" s="226"/>
       <c r="D15" s="83" t="s">
         <v>71</v>
       </c>
@@ -6553,10 +6540,10 @@
       <c r="Q17" s="12"/>
     </row>
     <row r="18" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B18" s="224" t="s">
+      <c r="B18" s="227" t="s">
         <v>53</v>
       </c>
-      <c r="C18" s="225"/>
+      <c r="C18" s="228"/>
       <c r="D18" s="236" t="s">
         <v>54</v>
       </c>
@@ -6579,8 +6566,8 @@
       <c r="Q18" s="252"/>
     </row>
     <row r="19" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B19" s="226"/>
-      <c r="C19" s="227"/>
+      <c r="B19" s="229"/>
+      <c r="C19" s="230"/>
       <c r="D19" s="237"/>
       <c r="E19" s="241" t="s">
         <v>97</v>
@@ -6599,8 +6586,8 @@
       <c r="Q19" s="69"/>
     </row>
     <row r="20" spans="2:28" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B20" s="228"/>
-      <c r="C20" s="229"/>
+      <c r="B20" s="231"/>
+      <c r="C20" s="232"/>
       <c r="D20" s="237"/>
       <c r="E20" s="85" t="s">
         <v>141</v>
@@ -6646,7 +6633,7 @@
       <c r="B21" s="233" t="s">
         <v>101</v>
       </c>
-      <c r="C21" s="230" t="s">
+      <c r="C21" s="224" t="s">
         <v>100</v>
       </c>
       <c r="D21" s="33" t="s">
@@ -6707,7 +6694,7 @@
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B22" s="234"/>
-      <c r="C22" s="231"/>
+      <c r="C22" s="225"/>
       <c r="D22" s="26" t="s">
         <v>103</v>
       </c>
@@ -6762,7 +6749,7 @@
     </row>
     <row r="23" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B23" s="234"/>
-      <c r="C23" s="232"/>
+      <c r="C23" s="226"/>
       <c r="D23" s="83" t="s">
         <v>71</v>
       </c>
@@ -6873,7 +6860,7 @@
     </row>
     <row r="25" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B25" s="234"/>
-      <c r="C25" s="230" t="s">
+      <c r="C25" s="224" t="s">
         <v>99</v>
       </c>
       <c r="D25" s="33" t="s">
@@ -6934,7 +6921,7 @@
     </row>
     <row r="26" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B26" s="234"/>
-      <c r="C26" s="231"/>
+      <c r="C26" s="225"/>
       <c r="D26" s="26" t="s">
         <v>103</v>
       </c>
@@ -6989,7 +6976,7 @@
     </row>
     <row r="27" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B27" s="234"/>
-      <c r="C27" s="232"/>
+      <c r="C27" s="226"/>
       <c r="D27" s="83" t="s">
         <v>71</v>
       </c>
@@ -7100,7 +7087,7 @@
     </row>
     <row r="29" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B29" s="234"/>
-      <c r="C29" s="230" t="s">
+      <c r="C29" s="224" t="s">
         <v>98</v>
       </c>
       <c r="D29" s="33" t="s">
@@ -7161,7 +7148,7 @@
     </row>
     <row r="30" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B30" s="234"/>
-      <c r="C30" s="231"/>
+      <c r="C30" s="225"/>
       <c r="D30" s="26" t="s">
         <v>103</v>
       </c>
@@ -7216,7 +7203,7 @@
     </row>
     <row r="31" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B31" s="234"/>
-      <c r="C31" s="232"/>
+      <c r="C31" s="226"/>
       <c r="D31" s="83" t="s">
         <v>71</v>
       </c>
@@ -7338,10 +7325,10 @@
       <c r="Q33" s="12"/>
     </row>
     <row r="34" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B34" s="224" t="s">
+      <c r="B34" s="227" t="s">
         <v>53</v>
       </c>
-      <c r="C34" s="225"/>
+      <c r="C34" s="228"/>
       <c r="D34" s="236" t="s">
         <v>54</v>
       </c>
@@ -7364,8 +7351,8 @@
       <c r="Q34" s="252"/>
     </row>
     <row r="35" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B35" s="226"/>
-      <c r="C35" s="227"/>
+      <c r="B35" s="229"/>
+      <c r="C35" s="230"/>
       <c r="D35" s="237"/>
       <c r="E35" s="241" t="s">
         <v>97</v>
@@ -7384,8 +7371,8 @@
       <c r="Q35" s="69"/>
     </row>
     <row r="36" spans="2:28" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B36" s="228"/>
-      <c r="C36" s="229"/>
+      <c r="B36" s="231"/>
+      <c r="C36" s="232"/>
       <c r="D36" s="237"/>
       <c r="E36" s="85" t="s">
         <v>141</v>
@@ -7431,7 +7418,7 @@
       <c r="B37" s="233" t="s">
         <v>96</v>
       </c>
-      <c r="C37" s="230" t="s">
+      <c r="C37" s="224" t="s">
         <v>95</v>
       </c>
       <c r="D37" s="33" t="s">
@@ -7492,7 +7479,7 @@
     </row>
     <row r="38" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B38" s="234"/>
-      <c r="C38" s="231"/>
+      <c r="C38" s="225"/>
       <c r="D38" s="26" t="s">
         <v>103</v>
       </c>
@@ -7547,7 +7534,7 @@
     </row>
     <row r="39" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B39" s="234"/>
-      <c r="C39" s="232"/>
+      <c r="C39" s="226"/>
       <c r="D39" s="83" t="s">
         <v>71</v>
       </c>
@@ -7658,7 +7645,7 @@
     </row>
     <row r="41" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B41" s="234"/>
-      <c r="C41" s="230" t="s">
+      <c r="C41" s="224" t="s">
         <v>80</v>
       </c>
       <c r="D41" s="33" t="s">
@@ -7719,7 +7706,7 @@
     </row>
     <row r="42" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B42" s="234"/>
-      <c r="C42" s="231"/>
+      <c r="C42" s="225"/>
       <c r="D42" s="26" t="s">
         <v>103</v>
       </c>
@@ -7774,7 +7761,7 @@
     </row>
     <row r="43" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B43" s="234"/>
-      <c r="C43" s="232"/>
+      <c r="C43" s="226"/>
       <c r="D43" s="83" t="s">
         <v>71</v>
       </c>
@@ -7885,7 +7872,7 @@
     </row>
     <row r="45" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B45" s="234"/>
-      <c r="C45" s="230" t="s">
+      <c r="C45" s="224" t="s">
         <v>94</v>
       </c>
       <c r="D45" s="33" t="s">
@@ -7946,7 +7933,7 @@
     </row>
     <row r="46" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B46" s="234"/>
-      <c r="C46" s="231"/>
+      <c r="C46" s="225"/>
       <c r="D46" s="26" t="s">
         <v>103</v>
       </c>
@@ -8001,7 +7988,7 @@
     </row>
     <row r="47" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B47" s="234"/>
-      <c r="C47" s="232"/>
+      <c r="C47" s="226"/>
       <c r="D47" s="83" t="s">
         <v>71</v>
       </c>
@@ -8112,7 +8099,7 @@
     </row>
     <row r="49" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B49" s="234"/>
-      <c r="C49" s="230" t="s">
+      <c r="C49" s="224" t="s">
         <v>93</v>
       </c>
       <c r="D49" s="33" t="s">
@@ -8164,7 +8151,7 @@
     </row>
     <row r="50" spans="2:28" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B50" s="234"/>
-      <c r="C50" s="231"/>
+      <c r="C50" s="225"/>
       <c r="D50" s="26" t="s">
         <v>103</v>
       </c>
@@ -8215,7 +8202,7 @@
     </row>
     <row r="51" spans="2:28" ht="18.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B51" s="234"/>
-      <c r="C51" s="232"/>
+      <c r="C51" s="226"/>
       <c r="D51" s="83" t="s">
         <v>71</v>
       </c>
@@ -8717,12 +8704,16 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="C41:C43"/>
-    <mergeCell ref="C45:C47"/>
-    <mergeCell ref="C49:C51"/>
-    <mergeCell ref="B34:C36"/>
-    <mergeCell ref="B37:B52"/>
-    <mergeCell ref="C37:C39"/>
+    <mergeCell ref="B2:C4"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="B18:C20"/>
+    <mergeCell ref="B5:B16"/>
+    <mergeCell ref="B21:B32"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="C25:C27"/>
     <mergeCell ref="D2:D4"/>
     <mergeCell ref="H2:Q2"/>
     <mergeCell ref="E3:G3"/>
@@ -8736,16 +8727,12 @@
     <mergeCell ref="D18:D20"/>
     <mergeCell ref="E18:G18"/>
     <mergeCell ref="E19:G19"/>
-    <mergeCell ref="B2:C4"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="B18:C20"/>
-    <mergeCell ref="B5:B16"/>
-    <mergeCell ref="B21:B32"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="C29:C31"/>
-    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="C41:C43"/>
+    <mergeCell ref="C45:C47"/>
+    <mergeCell ref="C49:C51"/>
+    <mergeCell ref="B34:C36"/>
+    <mergeCell ref="B37:B52"/>
+    <mergeCell ref="C37:C39"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="H5:Q7">

--- a/tool/track-aggregator/template/統合結果.xlsx
+++ b/tool/track-aggregator/template/統合結果.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ishid\Desktop\project_management\tool\track-aggregator\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB6A903B-5160-4478-8B43-4E7F8C93D379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{539EFA6E-7336-4585-87A8-66293D6FD7C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2380,6 +2380,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2570,21 +2585,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="5" fillId="8" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2594,7 +2594,21 @@
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準 2" xfId="2" xr:uid="{35DECEAB-A874-4A31-B6F5-75B712B64A43}"/>
   </cellStyles>
-  <dxfs count="32">
+  <dxfs count="34">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -3204,10 +3218,10 @@
       <c r="C2" s="185"/>
       <c r="D2" s="185"/>
       <c r="E2" s="185"/>
-      <c r="F2" s="254" t="s">
+      <c r="F2" s="190" t="s">
         <v>164</v>
       </c>
-      <c r="G2" s="255"/>
+      <c r="G2" s="191"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" s="187" t="s">
@@ -3222,7 +3236,7 @@
       <c r="D3" s="187" t="s">
         <v>160</v>
       </c>
-      <c r="E3" s="253" t="s">
+      <c r="E3" s="189" t="s">
         <v>161</v>
       </c>
       <c r="F3" s="96" t="s">
@@ -3240,13 +3254,18 @@
       <c r="C4" s="188"/>
       <c r="D4" s="188"/>
       <c r="E4" s="188"/>
-      <c r="F4" s="256" t="s">
+      <c r="F4" s="192" t="s">
         <v>163</v>
       </c>
-      <c r="G4" s="257"/>
+      <c r="G4" s="193"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
+  <conditionalFormatting sqref="F4:G4">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -3273,47 +3292,47 @@
       </c>
     </row>
     <row r="2" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="189" t="s">
+      <c r="B2" s="194" t="s">
         <v>156</v>
       </c>
-      <c r="C2" s="190" t="s">
+      <c r="C2" s="195" t="s">
         <v>55</v>
       </c>
-      <c r="D2" s="190"/>
-      <c r="E2" s="190"/>
-      <c r="F2" s="194" t="s">
+      <c r="D2" s="195"/>
+      <c r="E2" s="195"/>
+      <c r="F2" s="199" t="s">
         <v>56</v>
       </c>
-      <c r="G2" s="195"/>
-      <c r="H2" s="195"/>
-      <c r="I2" s="195"/>
-      <c r="J2" s="195"/>
-      <c r="K2" s="195"/>
-      <c r="L2" s="195"/>
-      <c r="M2" s="195"/>
-      <c r="N2" s="195"/>
-      <c r="O2" s="196"/>
+      <c r="G2" s="200"/>
+      <c r="H2" s="200"/>
+      <c r="I2" s="200"/>
+      <c r="J2" s="200"/>
+      <c r="K2" s="200"/>
+      <c r="L2" s="200"/>
+      <c r="M2" s="200"/>
+      <c r="N2" s="200"/>
+      <c r="O2" s="201"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.45">
-      <c r="B3" s="189"/>
-      <c r="C3" s="190" t="s">
+      <c r="B3" s="194"/>
+      <c r="C3" s="195" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="190"/>
-      <c r="E3" s="190"/>
-      <c r="F3" s="197"/>
-      <c r="G3" s="198"/>
-      <c r="H3" s="198"/>
-      <c r="I3" s="198"/>
-      <c r="J3" s="198"/>
-      <c r="K3" s="198"/>
-      <c r="L3" s="198"/>
-      <c r="M3" s="198"/>
-      <c r="N3" s="198"/>
-      <c r="O3" s="199"/>
+      <c r="D3" s="195"/>
+      <c r="E3" s="195"/>
+      <c r="F3" s="202"/>
+      <c r="G3" s="203"/>
+      <c r="H3" s="203"/>
+      <c r="I3" s="203"/>
+      <c r="J3" s="203"/>
+      <c r="K3" s="203"/>
+      <c r="L3" s="203"/>
+      <c r="M3" s="203"/>
+      <c r="N3" s="203"/>
+      <c r="O3" s="204"/>
     </row>
     <row r="4" spans="1:27" ht="36" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B4" s="189"/>
+      <c r="B4" s="194"/>
       <c r="C4" s="97" t="s">
         <v>141</v>
       </c>
@@ -3374,7 +3393,7 @@
       <c r="Q5" s="101"/>
     </row>
     <row r="6" spans="1:27" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B6" s="191" t="s">
+      <c r="B6" s="196" t="s">
         <v>102</v>
       </c>
       <c r="C6" s="102"/>
@@ -3392,7 +3411,7 @@
       <c r="O6" s="104"/>
     </row>
     <row r="7" spans="1:27" ht="18.600000000000001" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B7" s="192"/>
+      <c r="B7" s="197"/>
       <c r="C7" s="105"/>
       <c r="D7" s="105"/>
       <c r="E7" s="106"/>
@@ -3420,7 +3439,7 @@
       <c r="AA7" s="108"/>
     </row>
     <row r="8" spans="1:27" ht="18.600000000000001" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B8" s="193"/>
+      <c r="B8" s="198"/>
       <c r="C8" s="109"/>
       <c r="D8" s="109"/>
       <c r="E8" s="110"/>
@@ -3477,22 +3496,22 @@
   </mergeCells>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="C5:E5">
-    <cfRule type="cellIs" dxfId="31" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="1" operator="equal">
       <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:O6">
-    <cfRule type="cellIs" dxfId="30" priority="8" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="32" priority="8" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7:O7">
-    <cfRule type="cellIs" dxfId="29" priority="13" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="31" priority="13" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8:O8">
-    <cfRule type="cellIs" dxfId="28" priority="14" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="30" priority="14" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3551,40 +3570,40 @@
       </c>
     </row>
     <row r="2" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="213" t="s">
+      <c r="B2" s="218" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="214"/>
-      <c r="D2" s="219" t="s">
+      <c r="C2" s="219"/>
+      <c r="D2" s="224" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="200" t="s">
+      <c r="E2" s="205" t="s">
         <v>55</v>
       </c>
-      <c r="F2" s="201"/>
-      <c r="G2" s="202"/>
-      <c r="H2" s="203" t="s">
+      <c r="F2" s="206"/>
+      <c r="G2" s="207"/>
+      <c r="H2" s="208" t="s">
         <v>56</v>
       </c>
-      <c r="I2" s="204"/>
-      <c r="J2" s="204"/>
-      <c r="K2" s="204"/>
-      <c r="L2" s="204"/>
-      <c r="M2" s="204"/>
-      <c r="N2" s="204"/>
-      <c r="O2" s="204"/>
-      <c r="P2" s="204"/>
-      <c r="Q2" s="205"/>
+      <c r="I2" s="209"/>
+      <c r="J2" s="209"/>
+      <c r="K2" s="209"/>
+      <c r="L2" s="209"/>
+      <c r="M2" s="209"/>
+      <c r="N2" s="209"/>
+      <c r="O2" s="209"/>
+      <c r="P2" s="209"/>
+      <c r="Q2" s="210"/>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="B3" s="215"/>
-      <c r="C3" s="216"/>
-      <c r="D3" s="220"/>
-      <c r="E3" s="206" t="s">
+      <c r="B3" s="220"/>
+      <c r="C3" s="221"/>
+      <c r="D3" s="225"/>
+      <c r="E3" s="211" t="s">
         <v>97</v>
       </c>
-      <c r="F3" s="207"/>
-      <c r="G3" s="208"/>
+      <c r="F3" s="212"/>
+      <c r="G3" s="213"/>
       <c r="H3" s="168"/>
       <c r="I3" s="169"/>
       <c r="J3" s="169"/>
@@ -3597,9 +3616,9 @@
       <c r="Q3" s="170"/>
     </row>
     <row r="4" spans="1:29" ht="36.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B4" s="217"/>
-      <c r="C4" s="218"/>
-      <c r="D4" s="220"/>
+      <c r="B4" s="222"/>
+      <c r="C4" s="223"/>
+      <c r="D4" s="225"/>
       <c r="E4" s="171" t="s">
         <v>141</v>
       </c>
@@ -3641,10 +3660,10 @@
       </c>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="B5" s="209" t="s">
+      <c r="B5" s="214" t="s">
         <v>90</v>
       </c>
-      <c r="C5" s="212" t="s">
+      <c r="C5" s="217" t="s">
         <v>89</v>
       </c>
       <c r="D5" s="119" t="s">
@@ -3696,8 +3715,8 @@
       <c r="S5" s="101"/>
     </row>
     <row r="6" spans="1:29" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B6" s="210"/>
-      <c r="C6" s="193"/>
+      <c r="B6" s="215"/>
+      <c r="C6" s="198"/>
       <c r="D6" s="124" t="s">
         <v>145</v>
       </c>
@@ -3728,7 +3747,7 @@
       <c r="AC6" s="108"/>
     </row>
     <row r="7" spans="1:29" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B7" s="210"/>
+      <c r="B7" s="215"/>
       <c r="C7" s="184" t="s">
         <v>92</v>
       </c>
@@ -3784,8 +3803,8 @@
       </c>
     </row>
     <row r="8" spans="1:29" ht="18.600000000000001" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B8" s="210"/>
-      <c r="C8" s="212" t="s">
+      <c r="B8" s="215"/>
+      <c r="C8" s="217" t="s">
         <v>102</v>
       </c>
       <c r="D8" s="119" t="s">
@@ -3826,8 +3845,8 @@
       </c>
     </row>
     <row r="9" spans="1:29" ht="18.600000000000001" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B9" s="210"/>
-      <c r="C9" s="192"/>
+      <c r="B9" s="215"/>
+      <c r="C9" s="197"/>
       <c r="D9" s="131" t="s">
         <v>103</v>
       </c>
@@ -3878,8 +3897,8 @@
       <c r="AC9" s="108"/>
     </row>
     <row r="10" spans="1:29" ht="18.600000000000001" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B10" s="210"/>
-      <c r="C10" s="193"/>
+      <c r="B10" s="215"/>
+      <c r="C10" s="198"/>
       <c r="D10" s="134" t="s">
         <v>71</v>
       </c>
@@ -3930,7 +3949,7 @@
       <c r="AC10" s="108"/>
     </row>
     <row r="11" spans="1:29" ht="18.600000000000001" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B11" s="210"/>
+      <c r="B11" s="215"/>
       <c r="C11" s="113" t="s">
         <v>92</v>
       </c>
@@ -3984,8 +4003,8 @@
       </c>
     </row>
     <row r="12" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="B12" s="210"/>
-      <c r="C12" s="212" t="s">
+      <c r="B12" s="215"/>
+      <c r="C12" s="217" t="s">
         <v>88</v>
       </c>
       <c r="D12" s="119" t="s">
@@ -4036,8 +4055,8 @@
       </c>
     </row>
     <row r="13" spans="1:29" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B13" s="210"/>
-      <c r="C13" s="193"/>
+      <c r="B13" s="215"/>
+      <c r="C13" s="198"/>
       <c r="D13" s="124" t="s">
         <v>145</v>
       </c>
@@ -4068,7 +4087,7 @@
       <c r="AC13" s="108"/>
     </row>
     <row r="14" spans="1:29" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B14" s="211"/>
+      <c r="B14" s="216"/>
       <c r="C14" s="183" t="s">
         <v>92</v>
       </c>
@@ -4136,40 +4155,40 @@
       <c r="Q15" s="95"/>
     </row>
     <row r="16" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="B16" s="213" t="s">
+      <c r="B16" s="218" t="s">
         <v>53</v>
       </c>
-      <c r="C16" s="214"/>
-      <c r="D16" s="219" t="s">
+      <c r="C16" s="219"/>
+      <c r="D16" s="224" t="s">
         <v>54</v>
       </c>
-      <c r="E16" s="200" t="s">
+      <c r="E16" s="205" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="201"/>
-      <c r="G16" s="202"/>
-      <c r="H16" s="221" t="s">
+      <c r="F16" s="206"/>
+      <c r="G16" s="207"/>
+      <c r="H16" s="226" t="s">
         <v>56</v>
       </c>
-      <c r="I16" s="222"/>
-      <c r="J16" s="222"/>
-      <c r="K16" s="222"/>
-      <c r="L16" s="222"/>
-      <c r="M16" s="222"/>
-      <c r="N16" s="222"/>
-      <c r="O16" s="222"/>
-      <c r="P16" s="222"/>
-      <c r="Q16" s="223"/>
+      <c r="I16" s="227"/>
+      <c r="J16" s="227"/>
+      <c r="K16" s="227"/>
+      <c r="L16" s="227"/>
+      <c r="M16" s="227"/>
+      <c r="N16" s="227"/>
+      <c r="O16" s="227"/>
+      <c r="P16" s="227"/>
+      <c r="Q16" s="228"/>
     </row>
     <row r="17" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B17" s="215"/>
-      <c r="C17" s="216"/>
-      <c r="D17" s="220"/>
-      <c r="E17" s="206" t="s">
+      <c r="B17" s="220"/>
+      <c r="C17" s="221"/>
+      <c r="D17" s="225"/>
+      <c r="E17" s="211" t="s">
         <v>97</v>
       </c>
-      <c r="F17" s="207"/>
-      <c r="G17" s="208"/>
+      <c r="F17" s="212"/>
+      <c r="G17" s="213"/>
       <c r="H17" s="177"/>
       <c r="I17" s="178"/>
       <c r="J17" s="178"/>
@@ -4182,9 +4201,9 @@
       <c r="Q17" s="179"/>
     </row>
     <row r="18" spans="2:28" ht="36.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B18" s="217"/>
-      <c r="C18" s="218"/>
-      <c r="D18" s="220"/>
+      <c r="B18" s="222"/>
+      <c r="C18" s="223"/>
+      <c r="D18" s="225"/>
       <c r="E18" s="171" t="s">
         <v>141</v>
       </c>
@@ -4226,10 +4245,10 @@
       </c>
     </row>
     <row r="19" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B19" s="209" t="s">
+      <c r="B19" s="214" t="s">
         <v>101</v>
       </c>
-      <c r="C19" s="212" t="s">
+      <c r="C19" s="217" t="s">
         <v>147</v>
       </c>
       <c r="D19" s="119" t="s">
@@ -4289,8 +4308,8 @@
       </c>
     </row>
     <row r="20" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B20" s="210"/>
-      <c r="C20" s="193"/>
+      <c r="B20" s="215"/>
+      <c r="C20" s="198"/>
       <c r="D20" s="124" t="s">
         <v>145</v>
       </c>
@@ -4320,7 +4339,7 @@
       <c r="AB20" s="108"/>
     </row>
     <row r="21" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B21" s="210"/>
+      <c r="B21" s="215"/>
       <c r="C21" s="184" t="s">
         <v>92</v>
       </c>
@@ -4379,8 +4398,8 @@
       </c>
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B22" s="210"/>
-      <c r="C22" s="212" t="s">
+      <c r="B22" s="215"/>
+      <c r="C22" s="217" t="s">
         <v>152</v>
       </c>
       <c r="D22" s="119" t="s">
@@ -4440,8 +4459,8 @@
       </c>
     </row>
     <row r="23" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B23" s="210"/>
-      <c r="C23" s="193"/>
+      <c r="B23" s="215"/>
+      <c r="C23" s="198"/>
       <c r="D23" s="124" t="s">
         <v>145</v>
       </c>
@@ -4471,7 +4490,7 @@
       <c r="AB23" s="108"/>
     </row>
     <row r="24" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B24" s="210"/>
+      <c r="B24" s="215"/>
       <c r="C24" s="184" t="s">
         <v>92</v>
       </c>
@@ -4530,8 +4549,8 @@
       </c>
     </row>
     <row r="25" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B25" s="210"/>
-      <c r="C25" s="212" t="s">
+      <c r="B25" s="215"/>
+      <c r="C25" s="217" t="s">
         <v>153</v>
       </c>
       <c r="D25" s="119" t="s">
@@ -4591,8 +4610,8 @@
       </c>
     </row>
     <row r="26" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B26" s="210"/>
-      <c r="C26" s="193"/>
+      <c r="B26" s="215"/>
+      <c r="C26" s="198"/>
       <c r="D26" s="124" t="s">
         <v>145</v>
       </c>
@@ -4622,7 +4641,7 @@
       <c r="AB26" s="108"/>
     </row>
     <row r="27" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B27" s="211"/>
+      <c r="B27" s="216"/>
       <c r="C27" s="183" t="s">
         <v>92</v>
       </c>
@@ -4693,40 +4712,40 @@
       <c r="Q28" s="95"/>
     </row>
     <row r="29" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B29" s="213" t="s">
+      <c r="B29" s="218" t="s">
         <v>53</v>
       </c>
-      <c r="C29" s="214"/>
-      <c r="D29" s="219" t="s">
+      <c r="C29" s="219"/>
+      <c r="D29" s="224" t="s">
         <v>54</v>
       </c>
-      <c r="E29" s="200" t="s">
+      <c r="E29" s="205" t="s">
         <v>55</v>
       </c>
-      <c r="F29" s="201"/>
-      <c r="G29" s="202"/>
-      <c r="H29" s="221" t="s">
+      <c r="F29" s="206"/>
+      <c r="G29" s="207"/>
+      <c r="H29" s="226" t="s">
         <v>56</v>
       </c>
-      <c r="I29" s="222"/>
-      <c r="J29" s="222"/>
-      <c r="K29" s="222"/>
-      <c r="L29" s="222"/>
-      <c r="M29" s="222"/>
-      <c r="N29" s="222"/>
-      <c r="O29" s="222"/>
-      <c r="P29" s="222"/>
-      <c r="Q29" s="223"/>
+      <c r="I29" s="227"/>
+      <c r="J29" s="227"/>
+      <c r="K29" s="227"/>
+      <c r="L29" s="227"/>
+      <c r="M29" s="227"/>
+      <c r="N29" s="227"/>
+      <c r="O29" s="227"/>
+      <c r="P29" s="227"/>
+      <c r="Q29" s="228"/>
     </row>
     <row r="30" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B30" s="215"/>
-      <c r="C30" s="216"/>
-      <c r="D30" s="220"/>
-      <c r="E30" s="206" t="s">
+      <c r="B30" s="220"/>
+      <c r="C30" s="221"/>
+      <c r="D30" s="225"/>
+      <c r="E30" s="211" t="s">
         <v>97</v>
       </c>
-      <c r="F30" s="207"/>
-      <c r="G30" s="208"/>
+      <c r="F30" s="212"/>
+      <c r="G30" s="213"/>
       <c r="H30" s="177"/>
       <c r="I30" s="178"/>
       <c r="J30" s="178"/>
@@ -4739,9 +4758,9 @@
       <c r="Q30" s="179"/>
     </row>
     <row r="31" spans="2:28" ht="36.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B31" s="217"/>
-      <c r="C31" s="218"/>
-      <c r="D31" s="220"/>
+      <c r="B31" s="222"/>
+      <c r="C31" s="223"/>
+      <c r="D31" s="225"/>
       <c r="E31" s="171" t="s">
         <v>141</v>
       </c>
@@ -4783,10 +4802,10 @@
       </c>
     </row>
     <row r="32" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B32" s="209" t="s">
+      <c r="B32" s="214" t="s">
         <v>96</v>
       </c>
-      <c r="C32" s="212" t="s">
+      <c r="C32" s="217" t="s">
         <v>81</v>
       </c>
       <c r="D32" s="119" t="s">
@@ -4846,8 +4865,8 @@
       </c>
     </row>
     <row r="33" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B33" s="210"/>
-      <c r="C33" s="193"/>
+      <c r="B33" s="215"/>
+      <c r="C33" s="198"/>
       <c r="D33" s="124" t="s">
         <v>145</v>
       </c>
@@ -4877,7 +4896,7 @@
       <c r="AB33" s="108"/>
     </row>
     <row r="34" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B34" s="210"/>
+      <c r="B34" s="215"/>
       <c r="C34" s="184" t="s">
         <v>92</v>
       </c>
@@ -4936,8 +4955,8 @@
       </c>
     </row>
     <row r="35" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B35" s="210"/>
-      <c r="C35" s="212" t="s">
+      <c r="B35" s="215"/>
+      <c r="C35" s="217" t="s">
         <v>80</v>
       </c>
       <c r="D35" s="119" t="s">
@@ -4997,8 +5016,8 @@
       </c>
     </row>
     <row r="36" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B36" s="210"/>
-      <c r="C36" s="193"/>
+      <c r="B36" s="215"/>
+      <c r="C36" s="198"/>
       <c r="D36" s="124" t="s">
         <v>145</v>
       </c>
@@ -5028,7 +5047,7 @@
       <c r="AB36" s="108"/>
     </row>
     <row r="37" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B37" s="210"/>
+      <c r="B37" s="215"/>
       <c r="C37" s="184" t="s">
         <v>92</v>
       </c>
@@ -5087,8 +5106,8 @@
       </c>
     </row>
     <row r="38" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B38" s="210"/>
-      <c r="C38" s="212" t="s">
+      <c r="B38" s="215"/>
+      <c r="C38" s="217" t="s">
         <v>94</v>
       </c>
       <c r="D38" s="119" t="s">
@@ -5148,8 +5167,8 @@
       </c>
     </row>
     <row r="39" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B39" s="210"/>
-      <c r="C39" s="193"/>
+      <c r="B39" s="215"/>
+      <c r="C39" s="198"/>
       <c r="D39" s="124" t="s">
         <v>145</v>
       </c>
@@ -5179,7 +5198,7 @@
       <c r="AB39" s="108"/>
     </row>
     <row r="40" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B40" s="210"/>
+      <c r="B40" s="215"/>
       <c r="C40" s="184" t="s">
         <v>92</v>
       </c>
@@ -5238,8 +5257,8 @@
       </c>
     </row>
     <row r="41" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B41" s="210"/>
-      <c r="C41" s="212" t="s">
+      <c r="B41" s="215"/>
+      <c r="C41" s="217" t="s">
         <v>154</v>
       </c>
       <c r="D41" s="119" t="s">
@@ -5290,8 +5309,8 @@
       </c>
     </row>
     <row r="42" spans="2:28" ht="18.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B42" s="210"/>
-      <c r="C42" s="193"/>
+      <c r="B42" s="215"/>
+      <c r="C42" s="198"/>
       <c r="D42" s="124" t="s">
         <v>145</v>
       </c>
@@ -5321,7 +5340,7 @@
       <c r="AB42" s="108"/>
     </row>
     <row r="43" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B43" s="211"/>
+      <c r="B43" s="216"/>
       <c r="C43" s="183" t="s">
         <v>92</v>
       </c>
@@ -5686,67 +5705,67 @@
   </mergeCells>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="H5:Q6">
-    <cfRule type="cellIs" dxfId="27" priority="1" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="29" priority="1" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H8:Q8">
-    <cfRule type="cellIs" dxfId="26" priority="18" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="28" priority="18" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H9:Q9">
-    <cfRule type="cellIs" dxfId="25" priority="19" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="27" priority="19" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H10:Q10">
-    <cfRule type="cellIs" dxfId="24" priority="20" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="26" priority="20" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12:Q13">
-    <cfRule type="cellIs" dxfId="23" priority="4" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="25" priority="4" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H19:Q20">
-    <cfRule type="cellIs" dxfId="22" priority="16" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="24" priority="16" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H22:Q22">
-    <cfRule type="cellIs" dxfId="21" priority="10" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="23" priority="10" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H23:Q23 H39:Q39 H42:Q42">
-    <cfRule type="cellIs" dxfId="20" priority="21" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="22" priority="21" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H25:Q26">
-    <cfRule type="cellIs" dxfId="19" priority="9" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="21" priority="9" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H32:Q33">
-    <cfRule type="cellIs" dxfId="18" priority="8" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="20" priority="8" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H35:Q36">
-    <cfRule type="cellIs" dxfId="17" priority="7" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="19" priority="7" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H38:Q38">
-    <cfRule type="cellIs" dxfId="16" priority="6" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="18" priority="6" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H41:Q41">
-    <cfRule type="cellIs" dxfId="15" priority="3" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="17" priority="3" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5801,40 +5820,40 @@
   <sheetData>
     <row r="1" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="2" spans="2:29" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="227" t="s">
+      <c r="B2" s="232" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="228"/>
-      <c r="D2" s="236" t="s">
+      <c r="C2" s="233"/>
+      <c r="D2" s="241" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="244" t="s">
+      <c r="E2" s="249" t="s">
         <v>55</v>
       </c>
-      <c r="F2" s="245"/>
-      <c r="G2" s="246"/>
-      <c r="H2" s="238" t="s">
+      <c r="F2" s="250"/>
+      <c r="G2" s="251"/>
+      <c r="H2" s="243" t="s">
         <v>56</v>
       </c>
-      <c r="I2" s="239"/>
-      <c r="J2" s="239"/>
-      <c r="K2" s="239"/>
-      <c r="L2" s="239"/>
-      <c r="M2" s="239"/>
-      <c r="N2" s="239"/>
-      <c r="O2" s="239"/>
-      <c r="P2" s="239"/>
-      <c r="Q2" s="240"/>
+      <c r="I2" s="244"/>
+      <c r="J2" s="244"/>
+      <c r="K2" s="244"/>
+      <c r="L2" s="244"/>
+      <c r="M2" s="244"/>
+      <c r="N2" s="244"/>
+      <c r="O2" s="244"/>
+      <c r="P2" s="244"/>
+      <c r="Q2" s="245"/>
     </row>
     <row r="3" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B3" s="229"/>
-      <c r="C3" s="230"/>
-      <c r="D3" s="237"/>
-      <c r="E3" s="241" t="s">
+      <c r="B3" s="234"/>
+      <c r="C3" s="235"/>
+      <c r="D3" s="242"/>
+      <c r="E3" s="246" t="s">
         <v>97</v>
       </c>
-      <c r="F3" s="242"/>
-      <c r="G3" s="243"/>
+      <c r="F3" s="247"/>
+      <c r="G3" s="248"/>
       <c r="H3" s="22"/>
       <c r="I3" s="21"/>
       <c r="J3" s="21"/>
@@ -5847,9 +5866,9 @@
       <c r="Q3" s="20"/>
     </row>
     <row r="4" spans="2:29" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B4" s="231"/>
-      <c r="C4" s="232"/>
-      <c r="D4" s="237"/>
+      <c r="B4" s="236"/>
+      <c r="C4" s="237"/>
+      <c r="D4" s="242"/>
       <c r="E4" s="85" t="s">
         <v>141</v>
       </c>
@@ -5891,10 +5910,10 @@
       </c>
     </row>
     <row r="5" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B5" s="233" t="s">
+      <c r="B5" s="238" t="s">
         <v>90</v>
       </c>
-      <c r="C5" s="224" t="s">
+      <c r="C5" s="229" t="s">
         <v>138</v>
       </c>
       <c r="D5" s="33" t="s">
@@ -5948,8 +5967,8 @@
       </c>
     </row>
     <row r="6" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B6" s="234"/>
-      <c r="C6" s="225"/>
+      <c r="B6" s="239"/>
+      <c r="C6" s="230"/>
       <c r="D6" s="26" t="s">
         <v>103</v>
       </c>
@@ -6002,8 +6021,8 @@
       <c r="AC6" s="19"/>
     </row>
     <row r="7" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B7" s="234"/>
-      <c r="C7" s="226"/>
+      <c r="B7" s="239"/>
+      <c r="C7" s="231"/>
       <c r="D7" s="83" t="s">
         <v>71</v>
       </c>
@@ -6054,7 +6073,7 @@
       <c r="AC7" s="19"/>
     </row>
     <row r="8" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B8" s="234"/>
+      <c r="B8" s="239"/>
       <c r="C8" s="36" t="s">
         <v>92</v>
       </c>
@@ -6108,8 +6127,8 @@
       </c>
     </row>
     <row r="9" spans="2:29" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B9" s="234"/>
-      <c r="C9" s="224" t="s">
+      <c r="B9" s="239"/>
+      <c r="C9" s="229" t="s">
         <v>102</v>
       </c>
       <c r="D9" s="33" t="s">
@@ -6160,8 +6179,8 @@
       </c>
     </row>
     <row r="10" spans="2:29" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B10" s="234"/>
-      <c r="C10" s="225"/>
+      <c r="B10" s="239"/>
+      <c r="C10" s="230"/>
       <c r="D10" s="26" t="s">
         <v>103</v>
       </c>
@@ -6212,8 +6231,8 @@
       <c r="AC10" s="19"/>
     </row>
     <row r="11" spans="2:29" ht="15.6" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B11" s="234"/>
-      <c r="C11" s="226"/>
+      <c r="B11" s="239"/>
+      <c r="C11" s="231"/>
       <c r="D11" s="34" t="s">
         <v>71</v>
       </c>
@@ -6264,7 +6283,7 @@
       <c r="AC11" s="19"/>
     </row>
     <row r="12" spans="2:29" ht="15.6" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B12" s="234"/>
+      <c r="B12" s="239"/>
       <c r="C12" s="36" t="s">
         <v>92</v>
       </c>
@@ -6318,8 +6337,8 @@
       </c>
     </row>
     <row r="13" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B13" s="234"/>
-      <c r="C13" s="224" t="s">
+      <c r="B13" s="239"/>
+      <c r="C13" s="229" t="s">
         <v>143</v>
       </c>
       <c r="D13" s="33" t="s">
@@ -6370,8 +6389,8 @@
       </c>
     </row>
     <row r="14" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B14" s="234"/>
-      <c r="C14" s="225"/>
+      <c r="B14" s="239"/>
+      <c r="C14" s="230"/>
       <c r="D14" s="26" t="s">
         <v>103</v>
       </c>
@@ -6422,8 +6441,8 @@
       <c r="AC14" s="19"/>
     </row>
     <row r="15" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B15" s="234"/>
-      <c r="C15" s="226"/>
+      <c r="B15" s="239"/>
+      <c r="C15" s="231"/>
       <c r="D15" s="83" t="s">
         <v>71</v>
       </c>
@@ -6474,7 +6493,7 @@
       <c r="AC15" s="19"/>
     </row>
     <row r="16" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B16" s="235"/>
+      <c r="B16" s="240"/>
       <c r="C16" s="32" t="s">
         <v>92</v>
       </c>
@@ -6540,40 +6559,40 @@
       <c r="Q17" s="12"/>
     </row>
     <row r="18" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B18" s="227" t="s">
+      <c r="B18" s="232" t="s">
         <v>53</v>
       </c>
-      <c r="C18" s="228"/>
-      <c r="D18" s="236" t="s">
+      <c r="C18" s="233"/>
+      <c r="D18" s="241" t="s">
         <v>54</v>
       </c>
-      <c r="E18" s="244" t="s">
+      <c r="E18" s="249" t="s">
         <v>55</v>
       </c>
-      <c r="F18" s="245"/>
-      <c r="G18" s="246"/>
-      <c r="H18" s="250" t="s">
+      <c r="F18" s="250"/>
+      <c r="G18" s="251"/>
+      <c r="H18" s="255" t="s">
         <v>56</v>
       </c>
-      <c r="I18" s="251"/>
-      <c r="J18" s="251"/>
-      <c r="K18" s="251"/>
-      <c r="L18" s="251"/>
-      <c r="M18" s="251"/>
-      <c r="N18" s="251"/>
-      <c r="O18" s="251"/>
-      <c r="P18" s="251"/>
-      <c r="Q18" s="252"/>
+      <c r="I18" s="256"/>
+      <c r="J18" s="256"/>
+      <c r="K18" s="256"/>
+      <c r="L18" s="256"/>
+      <c r="M18" s="256"/>
+      <c r="N18" s="256"/>
+      <c r="O18" s="256"/>
+      <c r="P18" s="256"/>
+      <c r="Q18" s="257"/>
     </row>
     <row r="19" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B19" s="229"/>
-      <c r="C19" s="230"/>
-      <c r="D19" s="237"/>
-      <c r="E19" s="241" t="s">
+      <c r="B19" s="234"/>
+      <c r="C19" s="235"/>
+      <c r="D19" s="242"/>
+      <c r="E19" s="246" t="s">
         <v>97</v>
       </c>
-      <c r="F19" s="242"/>
-      <c r="G19" s="243"/>
+      <c r="F19" s="247"/>
+      <c r="G19" s="248"/>
       <c r="H19" s="67"/>
       <c r="I19" s="68"/>
       <c r="J19" s="68"/>
@@ -6586,9 +6605,9 @@
       <c r="Q19" s="69"/>
     </row>
     <row r="20" spans="2:28" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B20" s="231"/>
-      <c r="C20" s="232"/>
-      <c r="D20" s="237"/>
+      <c r="B20" s="236"/>
+      <c r="C20" s="237"/>
+      <c r="D20" s="242"/>
       <c r="E20" s="85" t="s">
         <v>141</v>
       </c>
@@ -6630,10 +6649,10 @@
       </c>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B21" s="233" t="s">
+      <c r="B21" s="238" t="s">
         <v>101</v>
       </c>
-      <c r="C21" s="224" t="s">
+      <c r="C21" s="229" t="s">
         <v>100</v>
       </c>
       <c r="D21" s="33" t="s">
@@ -6693,8 +6712,8 @@
       </c>
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B22" s="234"/>
-      <c r="C22" s="225"/>
+      <c r="B22" s="239"/>
+      <c r="C22" s="230"/>
       <c r="D22" s="26" t="s">
         <v>103</v>
       </c>
@@ -6748,8 +6767,8 @@
       <c r="AB22" s="19"/>
     </row>
     <row r="23" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B23" s="234"/>
-      <c r="C23" s="226"/>
+      <c r="B23" s="239"/>
+      <c r="C23" s="231"/>
       <c r="D23" s="83" t="s">
         <v>71</v>
       </c>
@@ -6803,7 +6822,7 @@
       <c r="AB23" s="19"/>
     </row>
     <row r="24" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B24" s="234"/>
+      <c r="B24" s="239"/>
       <c r="C24" s="36" t="s">
         <v>92</v>
       </c>
@@ -6859,8 +6878,8 @@
       </c>
     </row>
     <row r="25" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B25" s="234"/>
-      <c r="C25" s="224" t="s">
+      <c r="B25" s="239"/>
+      <c r="C25" s="229" t="s">
         <v>99</v>
       </c>
       <c r="D25" s="33" t="s">
@@ -6920,8 +6939,8 @@
       </c>
     </row>
     <row r="26" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B26" s="234"/>
-      <c r="C26" s="225"/>
+      <c r="B26" s="239"/>
+      <c r="C26" s="230"/>
       <c r="D26" s="26" t="s">
         <v>103</v>
       </c>
@@ -6975,8 +6994,8 @@
       <c r="AB26" s="19"/>
     </row>
     <row r="27" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B27" s="234"/>
-      <c r="C27" s="226"/>
+      <c r="B27" s="239"/>
+      <c r="C27" s="231"/>
       <c r="D27" s="83" t="s">
         <v>71</v>
       </c>
@@ -7030,7 +7049,7 @@
       <c r="AB27" s="19"/>
     </row>
     <row r="28" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B28" s="234"/>
+      <c r="B28" s="239"/>
       <c r="C28" s="36" t="s">
         <v>92</v>
       </c>
@@ -7086,8 +7105,8 @@
       </c>
     </row>
     <row r="29" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B29" s="234"/>
-      <c r="C29" s="224" t="s">
+      <c r="B29" s="239"/>
+      <c r="C29" s="229" t="s">
         <v>98</v>
       </c>
       <c r="D29" s="33" t="s">
@@ -7147,8 +7166,8 @@
       </c>
     </row>
     <row r="30" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B30" s="234"/>
-      <c r="C30" s="225"/>
+      <c r="B30" s="239"/>
+      <c r="C30" s="230"/>
       <c r="D30" s="26" t="s">
         <v>103</v>
       </c>
@@ -7202,8 +7221,8 @@
       <c r="AB30" s="19"/>
     </row>
     <row r="31" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B31" s="234"/>
-      <c r="C31" s="226"/>
+      <c r="B31" s="239"/>
+      <c r="C31" s="231"/>
       <c r="D31" s="83" t="s">
         <v>71</v>
       </c>
@@ -7257,7 +7276,7 @@
       <c r="AB31" s="19"/>
     </row>
     <row r="32" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B32" s="235"/>
+      <c r="B32" s="240"/>
       <c r="C32" s="32" t="s">
         <v>92</v>
       </c>
@@ -7325,40 +7344,40 @@
       <c r="Q33" s="12"/>
     </row>
     <row r="34" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B34" s="227" t="s">
+      <c r="B34" s="232" t="s">
         <v>53</v>
       </c>
-      <c r="C34" s="228"/>
-      <c r="D34" s="236" t="s">
+      <c r="C34" s="233"/>
+      <c r="D34" s="241" t="s">
         <v>54</v>
       </c>
-      <c r="E34" s="244" t="s">
+      <c r="E34" s="249" t="s">
         <v>55</v>
       </c>
-      <c r="F34" s="245"/>
-      <c r="G34" s="246"/>
-      <c r="H34" s="250" t="s">
+      <c r="F34" s="250"/>
+      <c r="G34" s="251"/>
+      <c r="H34" s="255" t="s">
         <v>56</v>
       </c>
-      <c r="I34" s="251"/>
-      <c r="J34" s="251"/>
-      <c r="K34" s="251"/>
-      <c r="L34" s="251"/>
-      <c r="M34" s="251"/>
-      <c r="N34" s="251"/>
-      <c r="O34" s="251"/>
-      <c r="P34" s="251"/>
-      <c r="Q34" s="252"/>
+      <c r="I34" s="256"/>
+      <c r="J34" s="256"/>
+      <c r="K34" s="256"/>
+      <c r="L34" s="256"/>
+      <c r="M34" s="256"/>
+      <c r="N34" s="256"/>
+      <c r="O34" s="256"/>
+      <c r="P34" s="256"/>
+      <c r="Q34" s="257"/>
     </row>
     <row r="35" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B35" s="229"/>
-      <c r="C35" s="230"/>
-      <c r="D35" s="237"/>
-      <c r="E35" s="241" t="s">
+      <c r="B35" s="234"/>
+      <c r="C35" s="235"/>
+      <c r="D35" s="242"/>
+      <c r="E35" s="246" t="s">
         <v>97</v>
       </c>
-      <c r="F35" s="242"/>
-      <c r="G35" s="243"/>
+      <c r="F35" s="247"/>
+      <c r="G35" s="248"/>
       <c r="H35" s="67"/>
       <c r="I35" s="68"/>
       <c r="J35" s="68"/>
@@ -7371,9 +7390,9 @@
       <c r="Q35" s="69"/>
     </row>
     <row r="36" spans="2:28" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B36" s="231"/>
-      <c r="C36" s="232"/>
-      <c r="D36" s="237"/>
+      <c r="B36" s="236"/>
+      <c r="C36" s="237"/>
+      <c r="D36" s="242"/>
       <c r="E36" s="85" t="s">
         <v>141</v>
       </c>
@@ -7415,10 +7434,10 @@
       </c>
     </row>
     <row r="37" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B37" s="233" t="s">
+      <c r="B37" s="238" t="s">
         <v>96</v>
       </c>
-      <c r="C37" s="224" t="s">
+      <c r="C37" s="229" t="s">
         <v>95</v>
       </c>
       <c r="D37" s="33" t="s">
@@ -7478,8 +7497,8 @@
       </c>
     </row>
     <row r="38" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B38" s="234"/>
-      <c r="C38" s="225"/>
+      <c r="B38" s="239"/>
+      <c r="C38" s="230"/>
       <c r="D38" s="26" t="s">
         <v>103</v>
       </c>
@@ -7533,8 +7552,8 @@
       <c r="AB38" s="19"/>
     </row>
     <row r="39" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B39" s="234"/>
-      <c r="C39" s="226"/>
+      <c r="B39" s="239"/>
+      <c r="C39" s="231"/>
       <c r="D39" s="83" t="s">
         <v>71</v>
       </c>
@@ -7588,7 +7607,7 @@
       <c r="AB39" s="19"/>
     </row>
     <row r="40" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B40" s="234"/>
+      <c r="B40" s="239"/>
       <c r="C40" s="36" t="s">
         <v>92</v>
       </c>
@@ -7644,8 +7663,8 @@
       </c>
     </row>
     <row r="41" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B41" s="234"/>
-      <c r="C41" s="224" t="s">
+      <c r="B41" s="239"/>
+      <c r="C41" s="229" t="s">
         <v>80</v>
       </c>
       <c r="D41" s="33" t="s">
@@ -7705,8 +7724,8 @@
       </c>
     </row>
     <row r="42" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B42" s="234"/>
-      <c r="C42" s="225"/>
+      <c r="B42" s="239"/>
+      <c r="C42" s="230"/>
       <c r="D42" s="26" t="s">
         <v>103</v>
       </c>
@@ -7760,8 +7779,8 @@
       <c r="AB42" s="19"/>
     </row>
     <row r="43" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B43" s="234"/>
-      <c r="C43" s="226"/>
+      <c r="B43" s="239"/>
+      <c r="C43" s="231"/>
       <c r="D43" s="83" t="s">
         <v>71</v>
       </c>
@@ -7815,7 +7834,7 @@
       <c r="AB43" s="19"/>
     </row>
     <row r="44" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B44" s="234"/>
+      <c r="B44" s="239"/>
       <c r="C44" s="36" t="s">
         <v>92</v>
       </c>
@@ -7871,8 +7890,8 @@
       </c>
     </row>
     <row r="45" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B45" s="234"/>
-      <c r="C45" s="224" t="s">
+      <c r="B45" s="239"/>
+      <c r="C45" s="229" t="s">
         <v>94</v>
       </c>
       <c r="D45" s="33" t="s">
@@ -7932,8 +7951,8 @@
       </c>
     </row>
     <row r="46" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B46" s="234"/>
-      <c r="C46" s="225"/>
+      <c r="B46" s="239"/>
+      <c r="C46" s="230"/>
       <c r="D46" s="26" t="s">
         <v>103</v>
       </c>
@@ -7987,8 +8006,8 @@
       <c r="AB46" s="19"/>
     </row>
     <row r="47" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B47" s="234"/>
-      <c r="C47" s="226"/>
+      <c r="B47" s="239"/>
+      <c r="C47" s="231"/>
       <c r="D47" s="83" t="s">
         <v>71</v>
       </c>
@@ -8042,7 +8061,7 @@
       <c r="AB47" s="19"/>
     </row>
     <row r="48" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B48" s="234"/>
+      <c r="B48" s="239"/>
       <c r="C48" s="36" t="s">
         <v>92</v>
       </c>
@@ -8098,14 +8117,14 @@
       </c>
     </row>
     <row r="49" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B49" s="234"/>
-      <c r="C49" s="224" t="s">
+      <c r="B49" s="239"/>
+      <c r="C49" s="229" t="s">
         <v>93</v>
       </c>
       <c r="D49" s="33" t="s">
         <v>144</v>
       </c>
-      <c r="E49" s="247"/>
+      <c r="E49" s="252"/>
       <c r="F49" s="87"/>
       <c r="G49" s="31"/>
       <c r="H49" s="64" t="e">
@@ -8150,12 +8169,12 @@
       </c>
     </row>
     <row r="50" spans="2:28" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B50" s="234"/>
-      <c r="C50" s="225"/>
+      <c r="B50" s="239"/>
+      <c r="C50" s="230"/>
       <c r="D50" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="E50" s="248"/>
+      <c r="E50" s="253"/>
       <c r="F50" s="88"/>
       <c r="G50" s="28"/>
       <c r="H50" s="73">
@@ -8201,12 +8220,12 @@
       <c r="AB50" s="19"/>
     </row>
     <row r="51" spans="2:28" ht="18.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B51" s="234"/>
-      <c r="C51" s="226"/>
+      <c r="B51" s="239"/>
+      <c r="C51" s="231"/>
       <c r="D51" s="83" t="s">
         <v>71</v>
       </c>
-      <c r="E51" s="249"/>
+      <c r="E51" s="254"/>
       <c r="F51" s="89"/>
       <c r="G51" s="54"/>
       <c r="H51" s="75">
@@ -8252,7 +8271,7 @@
       <c r="AB51" s="19"/>
     </row>
     <row r="52" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B52" s="235"/>
+      <c r="B52" s="240"/>
       <c r="C52" s="32" t="s">
         <v>92</v>
       </c>
@@ -8736,77 +8755,77 @@
   </mergeCells>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="H5:Q7">
-    <cfRule type="cellIs" dxfId="14" priority="11" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="16" priority="11" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H9:Q9">
-    <cfRule type="cellIs" dxfId="13" priority="10" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="15" priority="10" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H10:Q10">
-    <cfRule type="cellIs" dxfId="12" priority="12" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="14" priority="12" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11:Q11">
-    <cfRule type="cellIs" dxfId="11" priority="14" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="13" priority="14" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13:Q13">
-    <cfRule type="cellIs" dxfId="10" priority="9" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="12" priority="9" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H14:Q14 H22:Q22 H26:Q26 H30:Q30 H38:Q38 H42:Q42 H46:Q46 H50:Q50">
-    <cfRule type="cellIs" dxfId="9" priority="16" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="11" priority="16" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:Q15 H23:Q23 H31:Q31 H39:Q39 H43:Q43">
-    <cfRule type="cellIs" dxfId="8" priority="18" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="10" priority="18" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H21:Q21">
-    <cfRule type="cellIs" dxfId="7" priority="8" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="9" priority="8" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H25:Q25">
-    <cfRule type="cellIs" dxfId="6" priority="7" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="8" priority="7" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27:Q27 H47:Q47 H51:Q51">
-    <cfRule type="cellIs" dxfId="5" priority="15" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="7" priority="15" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H29:Q29">
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="6" priority="6" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H37:Q37">
-    <cfRule type="cellIs" dxfId="3" priority="5" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H41:Q41">
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H45:Q45">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H49:Q49">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>

--- a/tool/track-aggregator/template/統合結果.xlsx
+++ b/tool/track-aggregator/template/統合結果.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ishid\Desktop\project_management\tool\track-aggregator\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{539EFA6E-7336-4585-87A8-66293D6FD7C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3C9D5F9-D95F-4B1D-9C0F-735C06B6C9CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">サマリ!$B$2:$O$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">経年比較!$B$2:$Q$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'経年比較（前年同じFMT）'!$B$2:$Q$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">実施状況!$A$3:$F$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">実施状況!$A$6:$F$6</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="171">
   <si>
     <t>目的達成</t>
     <rPh sb="0" eb="2">
@@ -967,6 +967,28 @@
     <t>テスト</t>
     <phoneticPr fontId="3"/>
   </si>
+  <si>
+    <t>※メッセージ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>運営事務局です。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストが未実施となっております。</t>
+    <rPh sb="5" eb="7">
+      <t>ジッシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>お手数ですが、実施をお願いいたします。</t>
+    <rPh sb="7" eb="9">
+      <t>ジッシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -978,7 +1000,7 @@
     <numFmt numFmtId="178" formatCode="0.00_ "/>
     <numFmt numFmtId="179" formatCode="0.0_ "/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1084,6 +1106,15 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="11">
     <fill>
@@ -1147,7 +1178,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="53">
+  <borders count="54">
     <border>
       <left/>
       <right/>
@@ -1799,6 +1830,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1812,7 +1852,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="258">
+  <cellXfs count="265">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2437,13 +2477,13 @@
     <xf numFmtId="0" fontId="10" fillId="9" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="10" fillId="8" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="10" fillId="8" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="10" fillId="8" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="9" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2491,13 +2531,31 @@
     <xf numFmtId="0" fontId="10" fillId="7" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="10" fillId="8" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="8" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="8" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2509,24 +2567,6 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -2586,6 +2626,27 @@
     </xf>
     <xf numFmtId="179" fontId="5" fillId="8" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="51" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2594,21 +2655,7 @@
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準 2" xfId="2" xr:uid="{35DECEAB-A874-4A31-B6F5-75B712B64A43}"/>
   </cellStyles>
-  <dxfs count="34">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="33">
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -2910,6 +2957,13 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -3194,7 +3248,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3C1958A-33FA-4C4A-B3B4-B13C570E4EA1}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="19.296875" style="186" customWidth="1"/>
@@ -3206,63 +3260,83 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A1" s="185"/>
-      <c r="B1" s="185"/>
-      <c r="C1" s="185"/>
-      <c r="D1" s="185"/>
-      <c r="E1" s="185"/>
+      <c r="B1" s="258" t="s">
+        <v>167</v>
+      </c>
+      <c r="C1"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A2" s="185"/>
-      <c r="B2" s="185"/>
-      <c r="C2" s="185"/>
-      <c r="D2" s="185"/>
-      <c r="E2" s="185"/>
-      <c r="F2" s="190" t="s">
+      <c r="B2" s="259" t="s">
+        <v>168</v>
+      </c>
+      <c r="C2" s="260"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="B3" s="261" t="s">
+        <v>169</v>
+      </c>
+      <c r="C3" s="262"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A4" s="185"/>
+      <c r="B4" s="263" t="s">
+        <v>170</v>
+      </c>
+      <c r="C4" s="264"/>
+      <c r="D4" s="185"/>
+      <c r="E4" s="185"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A5" s="185"/>
+      <c r="B5" s="185"/>
+      <c r="C5" s="185"/>
+      <c r="D5" s="185"/>
+      <c r="E5" s="185"/>
+      <c r="F5" s="190" t="s">
         <v>164</v>
       </c>
-      <c r="G2" s="191"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A3" s="187" t="s">
+      <c r="G5" s="191"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A6" s="187" t="s">
         <v>157</v>
       </c>
-      <c r="B3" s="187" t="s">
+      <c r="B6" s="187" t="s">
         <v>158</v>
       </c>
-      <c r="C3" s="187" t="s">
+      <c r="C6" s="187" t="s">
         <v>159</v>
       </c>
-      <c r="D3" s="187" t="s">
+      <c r="D6" s="187" t="s">
         <v>160</v>
       </c>
-      <c r="E3" s="189" t="s">
+      <c r="E6" s="189" t="s">
         <v>161</v>
       </c>
-      <c r="F3" s="96" t="s">
+      <c r="F6" s="96" t="s">
         <v>166</v>
       </c>
-      <c r="G3" s="93" t="s">
+      <c r="G6" s="93" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A4" s="188" t="s">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A7" s="188" t="s">
         <v>162</v>
       </c>
-      <c r="B4" s="188"/>
-      <c r="C4" s="188"/>
-      <c r="D4" s="188"/>
-      <c r="E4" s="188"/>
-      <c r="F4" s="192" t="s">
+      <c r="B7" s="188"/>
+      <c r="C7" s="188"/>
+      <c r="D7" s="188"/>
+      <c r="E7" s="188"/>
+      <c r="F7" s="192" t="s">
         <v>163</v>
       </c>
-      <c r="G4" s="193"/>
+      <c r="G7" s="193"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="F4:G4">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+  <conditionalFormatting sqref="F7:G7">
+    <cfRule type="cellIs" dxfId="32" priority="1" operator="equal">
       <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3496,22 +3570,22 @@
   </mergeCells>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="C5:E5">
-    <cfRule type="cellIs" dxfId="33" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="1" operator="equal">
       <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:O6">
-    <cfRule type="cellIs" dxfId="32" priority="8" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="30" priority="8" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7:O7">
-    <cfRule type="cellIs" dxfId="31" priority="13" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="29" priority="13" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8:O8">
-    <cfRule type="cellIs" dxfId="30" priority="14" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="28" priority="14" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3582,18 +3656,18 @@
       </c>
       <c r="F2" s="206"/>
       <c r="G2" s="207"/>
-      <c r="H2" s="208" t="s">
+      <c r="H2" s="226" t="s">
         <v>56</v>
       </c>
-      <c r="I2" s="209"/>
-      <c r="J2" s="209"/>
-      <c r="K2" s="209"/>
-      <c r="L2" s="209"/>
-      <c r="M2" s="209"/>
-      <c r="N2" s="209"/>
-      <c r="O2" s="209"/>
-      <c r="P2" s="209"/>
-      <c r="Q2" s="210"/>
+      <c r="I2" s="227"/>
+      <c r="J2" s="227"/>
+      <c r="K2" s="227"/>
+      <c r="L2" s="227"/>
+      <c r="M2" s="227"/>
+      <c r="N2" s="227"/>
+      <c r="O2" s="227"/>
+      <c r="P2" s="227"/>
+      <c r="Q2" s="228"/>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.45">
       <c r="B3" s="220"/>
@@ -4167,18 +4241,18 @@
       </c>
       <c r="F16" s="206"/>
       <c r="G16" s="207"/>
-      <c r="H16" s="226" t="s">
+      <c r="H16" s="208" t="s">
         <v>56</v>
       </c>
-      <c r="I16" s="227"/>
-      <c r="J16" s="227"/>
-      <c r="K16" s="227"/>
-      <c r="L16" s="227"/>
-      <c r="M16" s="227"/>
-      <c r="N16" s="227"/>
-      <c r="O16" s="227"/>
-      <c r="P16" s="227"/>
-      <c r="Q16" s="228"/>
+      <c r="I16" s="209"/>
+      <c r="J16" s="209"/>
+      <c r="K16" s="209"/>
+      <c r="L16" s="209"/>
+      <c r="M16" s="209"/>
+      <c r="N16" s="209"/>
+      <c r="O16" s="209"/>
+      <c r="P16" s="209"/>
+      <c r="Q16" s="210"/>
     </row>
     <row r="17" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B17" s="220"/>
@@ -4724,18 +4798,18 @@
       </c>
       <c r="F29" s="206"/>
       <c r="G29" s="207"/>
-      <c r="H29" s="226" t="s">
+      <c r="H29" s="208" t="s">
         <v>56</v>
       </c>
-      <c r="I29" s="227"/>
-      <c r="J29" s="227"/>
-      <c r="K29" s="227"/>
-      <c r="L29" s="227"/>
-      <c r="M29" s="227"/>
-      <c r="N29" s="227"/>
-      <c r="O29" s="227"/>
-      <c r="P29" s="227"/>
-      <c r="Q29" s="228"/>
+      <c r="I29" s="209"/>
+      <c r="J29" s="209"/>
+      <c r="K29" s="209"/>
+      <c r="L29" s="209"/>
+      <c r="M29" s="209"/>
+      <c r="N29" s="209"/>
+      <c r="O29" s="209"/>
+      <c r="P29" s="209"/>
+      <c r="Q29" s="210"/>
     </row>
     <row r="30" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B30" s="220"/>
@@ -5674,6 +5748,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:Q2"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="B5:B14"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="B2:C4"/>
+    <mergeCell ref="B16:C18"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="D16:D18"/>
     <mergeCell ref="E16:G16"/>
     <mergeCell ref="H16:Q16"/>
     <mergeCell ref="E17:G17"/>
@@ -5690,82 +5776,70 @@
     <mergeCell ref="B19:B27"/>
     <mergeCell ref="C19:C20"/>
     <mergeCell ref="C22:C23"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="B2:C4"/>
-    <mergeCell ref="B16:C18"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:Q2"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="B5:B14"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="C12:C13"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="H5:Q6">
-    <cfRule type="cellIs" dxfId="29" priority="1" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="27" priority="1" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H8:Q8">
-    <cfRule type="cellIs" dxfId="28" priority="18" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="26" priority="18" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H9:Q9">
-    <cfRule type="cellIs" dxfId="27" priority="19" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="25" priority="19" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H10:Q10">
-    <cfRule type="cellIs" dxfId="26" priority="20" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="24" priority="20" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12:Q13">
-    <cfRule type="cellIs" dxfId="25" priority="4" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="23" priority="4" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H19:Q20">
-    <cfRule type="cellIs" dxfId="24" priority="16" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="22" priority="16" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H22:Q22">
-    <cfRule type="cellIs" dxfId="23" priority="10" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="21" priority="10" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H23:Q23 H39:Q39 H42:Q42">
-    <cfRule type="cellIs" dxfId="22" priority="21" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="20" priority="21" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H25:Q26">
-    <cfRule type="cellIs" dxfId="21" priority="9" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="19" priority="9" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H32:Q33">
-    <cfRule type="cellIs" dxfId="20" priority="8" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="18" priority="8" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H35:Q36">
-    <cfRule type="cellIs" dxfId="19" priority="7" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="17" priority="7" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H38:Q38">
-    <cfRule type="cellIs" dxfId="18" priority="6" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="16" priority="6" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H41:Q41">
-    <cfRule type="cellIs" dxfId="17" priority="3" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="15" priority="3" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5820,10 +5894,10 @@
   <sheetData>
     <row r="1" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="2" spans="2:29" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="232" t="s">
+      <c r="B2" s="229" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="233"/>
+      <c r="C2" s="230"/>
       <c r="D2" s="241" t="s">
         <v>54</v>
       </c>
@@ -5846,8 +5920,8 @@
       <c r="Q2" s="245"/>
     </row>
     <row r="3" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B3" s="234"/>
-      <c r="C3" s="235"/>
+      <c r="B3" s="231"/>
+      <c r="C3" s="232"/>
       <c r="D3" s="242"/>
       <c r="E3" s="246" t="s">
         <v>97</v>
@@ -5866,8 +5940,8 @@
       <c r="Q3" s="20"/>
     </row>
     <row r="4" spans="2:29" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B4" s="236"/>
-      <c r="C4" s="237"/>
+      <c r="B4" s="233"/>
+      <c r="C4" s="234"/>
       <c r="D4" s="242"/>
       <c r="E4" s="85" t="s">
         <v>141</v>
@@ -5913,7 +5987,7 @@
       <c r="B5" s="238" t="s">
         <v>90</v>
       </c>
-      <c r="C5" s="229" t="s">
+      <c r="C5" s="235" t="s">
         <v>138</v>
       </c>
       <c r="D5" s="33" t="s">
@@ -5968,7 +6042,7 @@
     </row>
     <row r="6" spans="2:29" x14ac:dyDescent="0.45">
       <c r="B6" s="239"/>
-      <c r="C6" s="230"/>
+      <c r="C6" s="236"/>
       <c r="D6" s="26" t="s">
         <v>103</v>
       </c>
@@ -6022,7 +6096,7 @@
     </row>
     <row r="7" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B7" s="239"/>
-      <c r="C7" s="231"/>
+      <c r="C7" s="237"/>
       <c r="D7" s="83" t="s">
         <v>71</v>
       </c>
@@ -6128,7 +6202,7 @@
     </row>
     <row r="9" spans="2:29" hidden="1" x14ac:dyDescent="0.45">
       <c r="B9" s="239"/>
-      <c r="C9" s="229" t="s">
+      <c r="C9" s="235" t="s">
         <v>102</v>
       </c>
       <c r="D9" s="33" t="s">
@@ -6180,7 +6254,7 @@
     </row>
     <row r="10" spans="2:29" hidden="1" x14ac:dyDescent="0.45">
       <c r="B10" s="239"/>
-      <c r="C10" s="230"/>
+      <c r="C10" s="236"/>
       <c r="D10" s="26" t="s">
         <v>103</v>
       </c>
@@ -6232,7 +6306,7 @@
     </row>
     <row r="11" spans="2:29" ht="15.6" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B11" s="239"/>
-      <c r="C11" s="231"/>
+      <c r="C11" s="237"/>
       <c r="D11" s="34" t="s">
         <v>71</v>
       </c>
@@ -6338,7 +6412,7 @@
     </row>
     <row r="13" spans="2:29" x14ac:dyDescent="0.45">
       <c r="B13" s="239"/>
-      <c r="C13" s="229" t="s">
+      <c r="C13" s="235" t="s">
         <v>143</v>
       </c>
       <c r="D13" s="33" t="s">
@@ -6390,7 +6464,7 @@
     </row>
     <row r="14" spans="2:29" x14ac:dyDescent="0.45">
       <c r="B14" s="239"/>
-      <c r="C14" s="230"/>
+      <c r="C14" s="236"/>
       <c r="D14" s="26" t="s">
         <v>103</v>
       </c>
@@ -6442,7 +6516,7 @@
     </row>
     <row r="15" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B15" s="239"/>
-      <c r="C15" s="231"/>
+      <c r="C15" s="237"/>
       <c r="D15" s="83" t="s">
         <v>71</v>
       </c>
@@ -6559,10 +6633,10 @@
       <c r="Q17" s="12"/>
     </row>
     <row r="18" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B18" s="232" t="s">
+      <c r="B18" s="229" t="s">
         <v>53</v>
       </c>
-      <c r="C18" s="233"/>
+      <c r="C18" s="230"/>
       <c r="D18" s="241" t="s">
         <v>54</v>
       </c>
@@ -6585,8 +6659,8 @@
       <c r="Q18" s="257"/>
     </row>
     <row r="19" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B19" s="234"/>
-      <c r="C19" s="235"/>
+      <c r="B19" s="231"/>
+      <c r="C19" s="232"/>
       <c r="D19" s="242"/>
       <c r="E19" s="246" t="s">
         <v>97</v>
@@ -6605,8 +6679,8 @@
       <c r="Q19" s="69"/>
     </row>
     <row r="20" spans="2:28" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B20" s="236"/>
-      <c r="C20" s="237"/>
+      <c r="B20" s="233"/>
+      <c r="C20" s="234"/>
       <c r="D20" s="242"/>
       <c r="E20" s="85" t="s">
         <v>141</v>
@@ -6652,7 +6726,7 @@
       <c r="B21" s="238" t="s">
         <v>101</v>
       </c>
-      <c r="C21" s="229" t="s">
+      <c r="C21" s="235" t="s">
         <v>100</v>
       </c>
       <c r="D21" s="33" t="s">
@@ -6713,7 +6787,7 @@
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B22" s="239"/>
-      <c r="C22" s="230"/>
+      <c r="C22" s="236"/>
       <c r="D22" s="26" t="s">
         <v>103</v>
       </c>
@@ -6768,7 +6842,7 @@
     </row>
     <row r="23" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B23" s="239"/>
-      <c r="C23" s="231"/>
+      <c r="C23" s="237"/>
       <c r="D23" s="83" t="s">
         <v>71</v>
       </c>
@@ -6879,7 +6953,7 @@
     </row>
     <row r="25" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B25" s="239"/>
-      <c r="C25" s="229" t="s">
+      <c r="C25" s="235" t="s">
         <v>99</v>
       </c>
       <c r="D25" s="33" t="s">
@@ -6940,7 +7014,7 @@
     </row>
     <row r="26" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B26" s="239"/>
-      <c r="C26" s="230"/>
+      <c r="C26" s="236"/>
       <c r="D26" s="26" t="s">
         <v>103</v>
       </c>
@@ -6995,7 +7069,7 @@
     </row>
     <row r="27" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B27" s="239"/>
-      <c r="C27" s="231"/>
+      <c r="C27" s="237"/>
       <c r="D27" s="83" t="s">
         <v>71</v>
       </c>
@@ -7106,7 +7180,7 @@
     </row>
     <row r="29" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B29" s="239"/>
-      <c r="C29" s="229" t="s">
+      <c r="C29" s="235" t="s">
         <v>98</v>
       </c>
       <c r="D29" s="33" t="s">
@@ -7167,7 +7241,7 @@
     </row>
     <row r="30" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B30" s="239"/>
-      <c r="C30" s="230"/>
+      <c r="C30" s="236"/>
       <c r="D30" s="26" t="s">
         <v>103</v>
       </c>
@@ -7222,7 +7296,7 @@
     </row>
     <row r="31" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B31" s="239"/>
-      <c r="C31" s="231"/>
+      <c r="C31" s="237"/>
       <c r="D31" s="83" t="s">
         <v>71</v>
       </c>
@@ -7344,10 +7418,10 @@
       <c r="Q33" s="12"/>
     </row>
     <row r="34" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B34" s="232" t="s">
+      <c r="B34" s="229" t="s">
         <v>53</v>
       </c>
-      <c r="C34" s="233"/>
+      <c r="C34" s="230"/>
       <c r="D34" s="241" t="s">
         <v>54</v>
       </c>
@@ -7370,8 +7444,8 @@
       <c r="Q34" s="257"/>
     </row>
     <row r="35" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B35" s="234"/>
-      <c r="C35" s="235"/>
+      <c r="B35" s="231"/>
+      <c r="C35" s="232"/>
       <c r="D35" s="242"/>
       <c r="E35" s="246" t="s">
         <v>97</v>
@@ -7390,8 +7464,8 @@
       <c r="Q35" s="69"/>
     </row>
     <row r="36" spans="2:28" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B36" s="236"/>
-      <c r="C36" s="237"/>
+      <c r="B36" s="233"/>
+      <c r="C36" s="234"/>
       <c r="D36" s="242"/>
       <c r="E36" s="85" t="s">
         <v>141</v>
@@ -7437,7 +7511,7 @@
       <c r="B37" s="238" t="s">
         <v>96</v>
       </c>
-      <c r="C37" s="229" t="s">
+      <c r="C37" s="235" t="s">
         <v>95</v>
       </c>
       <c r="D37" s="33" t="s">
@@ -7498,7 +7572,7 @@
     </row>
     <row r="38" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B38" s="239"/>
-      <c r="C38" s="230"/>
+      <c r="C38" s="236"/>
       <c r="D38" s="26" t="s">
         <v>103</v>
       </c>
@@ -7553,7 +7627,7 @@
     </row>
     <row r="39" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B39" s="239"/>
-      <c r="C39" s="231"/>
+      <c r="C39" s="237"/>
       <c r="D39" s="83" t="s">
         <v>71</v>
       </c>
@@ -7664,7 +7738,7 @@
     </row>
     <row r="41" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B41" s="239"/>
-      <c r="C41" s="229" t="s">
+      <c r="C41" s="235" t="s">
         <v>80</v>
       </c>
       <c r="D41" s="33" t="s">
@@ -7725,7 +7799,7 @@
     </row>
     <row r="42" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B42" s="239"/>
-      <c r="C42" s="230"/>
+      <c r="C42" s="236"/>
       <c r="D42" s="26" t="s">
         <v>103</v>
       </c>
@@ -7780,7 +7854,7 @@
     </row>
     <row r="43" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B43" s="239"/>
-      <c r="C43" s="231"/>
+      <c r="C43" s="237"/>
       <c r="D43" s="83" t="s">
         <v>71</v>
       </c>
@@ -7891,7 +7965,7 @@
     </row>
     <row r="45" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B45" s="239"/>
-      <c r="C45" s="229" t="s">
+      <c r="C45" s="235" t="s">
         <v>94</v>
       </c>
       <c r="D45" s="33" t="s">
@@ -7952,7 +8026,7 @@
     </row>
     <row r="46" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B46" s="239"/>
-      <c r="C46" s="230"/>
+      <c r="C46" s="236"/>
       <c r="D46" s="26" t="s">
         <v>103</v>
       </c>
@@ -8007,7 +8081,7 @@
     </row>
     <row r="47" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B47" s="239"/>
-      <c r="C47" s="231"/>
+      <c r="C47" s="237"/>
       <c r="D47" s="83" t="s">
         <v>71</v>
       </c>
@@ -8118,7 +8192,7 @@
     </row>
     <row r="49" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B49" s="239"/>
-      <c r="C49" s="229" t="s">
+      <c r="C49" s="235" t="s">
         <v>93</v>
       </c>
       <c r="D49" s="33" t="s">
@@ -8170,7 +8244,7 @@
     </row>
     <row r="50" spans="2:28" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B50" s="239"/>
-      <c r="C50" s="230"/>
+      <c r="C50" s="236"/>
       <c r="D50" s="26" t="s">
         <v>103</v>
       </c>
@@ -8221,7 +8295,7 @@
     </row>
     <row r="51" spans="2:28" ht="18.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B51" s="239"/>
-      <c r="C51" s="231"/>
+      <c r="C51" s="237"/>
       <c r="D51" s="83" t="s">
         <v>71</v>
       </c>
@@ -8723,16 +8797,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B2:C4"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="B18:C20"/>
-    <mergeCell ref="B5:B16"/>
-    <mergeCell ref="B21:B32"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="C29:C31"/>
-    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="C41:C43"/>
+    <mergeCell ref="C45:C47"/>
+    <mergeCell ref="C49:C51"/>
+    <mergeCell ref="B34:C36"/>
+    <mergeCell ref="B37:B52"/>
+    <mergeCell ref="C37:C39"/>
     <mergeCell ref="D2:D4"/>
     <mergeCell ref="H2:Q2"/>
     <mergeCell ref="E3:G3"/>
@@ -8746,86 +8816,90 @@
     <mergeCell ref="D18:D20"/>
     <mergeCell ref="E18:G18"/>
     <mergeCell ref="E19:G19"/>
-    <mergeCell ref="C41:C43"/>
-    <mergeCell ref="C45:C47"/>
-    <mergeCell ref="C49:C51"/>
-    <mergeCell ref="B34:C36"/>
-    <mergeCell ref="B37:B52"/>
-    <mergeCell ref="C37:C39"/>
+    <mergeCell ref="B2:C4"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="B18:C20"/>
+    <mergeCell ref="B5:B16"/>
+    <mergeCell ref="B21:B32"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="C25:C27"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="H5:Q7">
-    <cfRule type="cellIs" dxfId="16" priority="11" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="14" priority="11" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H9:Q9">
-    <cfRule type="cellIs" dxfId="15" priority="10" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="13" priority="10" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H10:Q10">
-    <cfRule type="cellIs" dxfId="14" priority="12" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="12" priority="12" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11:Q11">
-    <cfRule type="cellIs" dxfId="13" priority="14" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="11" priority="14" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13:Q13">
-    <cfRule type="cellIs" dxfId="12" priority="9" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="10" priority="9" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H14:Q14 H22:Q22 H26:Q26 H30:Q30 H38:Q38 H42:Q42 H46:Q46 H50:Q50">
-    <cfRule type="cellIs" dxfId="11" priority="16" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="9" priority="16" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:Q15 H23:Q23 H31:Q31 H39:Q39 H43:Q43">
-    <cfRule type="cellIs" dxfId="10" priority="18" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="8" priority="18" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H21:Q21">
-    <cfRule type="cellIs" dxfId="9" priority="8" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="7" priority="8" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H25:Q25">
-    <cfRule type="cellIs" dxfId="8" priority="7" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="6" priority="7" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27:Q27 H47:Q47 H51:Q51">
-    <cfRule type="cellIs" dxfId="7" priority="15" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="5" priority="15" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H29:Q29">
-    <cfRule type="cellIs" dxfId="6" priority="6" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H37:Q37">
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H41:Q41">
-    <cfRule type="cellIs" dxfId="4" priority="4" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H45:Q45">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H49:Q49">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>

--- a/tool/track-aggregator/template/統合結果.xlsx
+++ b/tool/track-aggregator/template/統合結果.xlsx
@@ -8,21 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ishid\Desktop\project_management\tool\track-aggregator\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3C9D5F9-D95F-4B1D-9C0F-735C06B6C9CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0175F406-8941-4253-B71B-19EA2D2172E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="実施状況" sheetId="33" r:id="rId1"/>
     <sheet name="サマリ" sheetId="32" r:id="rId2"/>
-    <sheet name="経年比較" sheetId="31" r:id="rId3"/>
-    <sheet name="経年比較（前年同じFMT）" sheetId="22" state="hidden" r:id="rId4"/>
-    <sheet name="ビジネス基礎（Day5)" sheetId="13" state="hidden" r:id="rId5"/>
+    <sheet name="経年比較（前年同じFMT）" sheetId="22" state="hidden" r:id="rId3"/>
+    <sheet name="ビジネス基礎（Day5)" sheetId="13" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">サマリ!$B$2:$O$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">経年比較!$B$2:$Q$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'経年比較（前年同じFMT）'!$B$2:$Q$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'経年比較（前年同じFMT）'!$B$2:$Q$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">実施状況!$A$6:$F$6</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -35,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="165">
   <si>
     <t>目的達成</t>
     <rPh sb="0" eb="2">
@@ -387,10 +385,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>-</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>不合格</t>
     <rPh sb="0" eb="3">
       <t>フゴウカク</t>
@@ -862,16 +856,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>社会を支えるITサービス</t>
-    <rPh sb="0" eb="2">
-      <t>シャカイ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ササ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>中央値</t>
     <rPh sb="0" eb="3">
       <t>チュウオウチ</t>
@@ -883,33 +867,11 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>FY2026</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>{結果データ}</t>
     <rPh sb="1" eb="3">
       <t>ケッカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>データベース技術入門</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>Web技術入門</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>システム開発演習</t>
-    <rPh sb="4" eb="6">
-      <t>カイハツ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>エンシュウ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> </t>
@@ -1000,7 +962,7 @@
     <numFmt numFmtId="178" formatCode="0.00_ "/>
     <numFmt numFmtId="179" formatCode="0.0_ "/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1101,14 +1063,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="游ゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="游ゴシック"/>
       <family val="3"/>
@@ -1178,7 +1132,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="54">
+  <borders count="51">
     <border>
       <left/>
       <right/>
@@ -1678,51 +1632,6 @@
         <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1852,7 +1761,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="265">
+  <cellXfs count="175">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2159,13 +2068,13 @@
     <xf numFmtId="178" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="11" fillId="0" borderId="45" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="0" borderId="46" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="42" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="43" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="11" fillId="0" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2210,204 +2119,6 @@
     <xf numFmtId="179" fontId="12" fillId="6" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="3" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="3" borderId="33" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="0" borderId="34" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="6" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="3" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="6" borderId="37" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="37" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="12" fillId="6" borderId="37" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="11" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="11" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="33" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="12" fillId="6" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="41" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="12" fillId="6" borderId="42" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="12" fillId="6" borderId="42" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="12" fillId="6" borderId="43" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="12" fillId="6" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="12" fillId="6" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="34" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="12" fillId="6" borderId="35" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="3" borderId="38" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="3" borderId="38" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="3" borderId="37" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="3" borderId="37" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="6" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="6" borderId="25" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="11" fillId="6" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="12" fillId="6" borderId="36" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="9" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="9" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="8" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="8" borderId="17" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="8" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="8" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="8" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -2417,7 +2128,7 @@
     <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2426,14 +2137,35 @@
     <xf numFmtId="0" fontId="10" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="48" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2441,7 +2173,7 @@
     <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="44" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="41" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2453,92 +2185,29 @@
     <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="44" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="46" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="47" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="48" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="49" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="50" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="51" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="39" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="8" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="8" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="8" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="40" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2558,15 +2227,6 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -2626,27 +2286,6 @@
     </xf>
     <xf numFmtId="179" fontId="5" fillId="8" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="51" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2655,7 +2294,7 @@
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準 2" xfId="2" xr:uid="{35DECEAB-A874-4A31-B6F5-75B712B64A43}"/>
   </cellStyles>
-  <dxfs count="33">
+  <dxfs count="20">
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -2752,133 +2391,6 @@
       <font>
         <color rgb="FFFF0000"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -3251,92 +2763,92 @@
   <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="19.296875" style="186" customWidth="1"/>
-    <col min="2" max="2" width="30.69921875" style="186" customWidth="1"/>
-    <col min="3" max="3" width="40.69921875" style="186" customWidth="1"/>
-    <col min="4" max="5" width="15.69921875" style="186" customWidth="1"/>
-    <col min="6" max="6" width="20.69921875" style="186" customWidth="1"/>
+    <col min="1" max="1" width="19.296875" style="120" customWidth="1"/>
+    <col min="2" max="2" width="30.69921875" style="120" customWidth="1"/>
+    <col min="3" max="3" width="40.69921875" style="120" customWidth="1"/>
+    <col min="4" max="5" width="15.69921875" style="120" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" style="120" customWidth="1"/>
     <col min="7" max="7" width="20.69921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="B1" s="258" t="s">
-        <v>167</v>
+      <c r="B1" s="128" t="s">
+        <v>161</v>
       </c>
       <c r="C1"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="B2" s="259" t="s">
-        <v>168</v>
-      </c>
-      <c r="C2" s="260"/>
+      <c r="B2" s="129" t="s">
+        <v>162</v>
+      </c>
+      <c r="C2" s="130"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="B3" s="261" t="s">
-        <v>169</v>
-      </c>
-      <c r="C3" s="262"/>
+      <c r="B3" s="131" t="s">
+        <v>163</v>
+      </c>
+      <c r="C3" s="132"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A4" s="185"/>
-      <c r="B4" s="263" t="s">
-        <v>170</v>
-      </c>
-      <c r="C4" s="264"/>
-      <c r="D4" s="185"/>
-      <c r="E4" s="185"/>
+      <c r="A4" s="119"/>
+      <c r="B4" s="133" t="s">
+        <v>164</v>
+      </c>
+      <c r="C4" s="134"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A5" s="185"/>
-      <c r="B5" s="185"/>
-      <c r="C5" s="185"/>
-      <c r="D5" s="185"/>
-      <c r="E5" s="185"/>
-      <c r="F5" s="190" t="s">
-        <v>164</v>
-      </c>
-      <c r="G5" s="191"/>
+      <c r="A5" s="119"/>
+      <c r="B5" s="119"/>
+      <c r="C5" s="119"/>
+      <c r="D5" s="119"/>
+      <c r="E5" s="119"/>
+      <c r="F5" s="124" t="s">
+        <v>158</v>
+      </c>
+      <c r="G5" s="125"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A6" s="187" t="s">
+      <c r="A6" s="121" t="s">
+        <v>151</v>
+      </c>
+      <c r="B6" s="121" t="s">
+        <v>152</v>
+      </c>
+      <c r="C6" s="121" t="s">
+        <v>153</v>
+      </c>
+      <c r="D6" s="121" t="s">
+        <v>154</v>
+      </c>
+      <c r="E6" s="123" t="s">
+        <v>155</v>
+      </c>
+      <c r="F6" s="96" t="s">
+        <v>160</v>
+      </c>
+      <c r="G6" s="93" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A7" s="122" t="s">
+        <v>156</v>
+      </c>
+      <c r="B7" s="122"/>
+      <c r="C7" s="122"/>
+      <c r="D7" s="122"/>
+      <c r="E7" s="122"/>
+      <c r="F7" s="126" t="s">
         <v>157</v>
       </c>
-      <c r="B6" s="187" t="s">
-        <v>158</v>
-      </c>
-      <c r="C6" s="187" t="s">
-        <v>159</v>
-      </c>
-      <c r="D6" s="187" t="s">
-        <v>160</v>
-      </c>
-      <c r="E6" s="189" t="s">
-        <v>161</v>
-      </c>
-      <c r="F6" s="96" t="s">
-        <v>166</v>
-      </c>
-      <c r="G6" s="93" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A7" s="188" t="s">
-        <v>162</v>
-      </c>
-      <c r="B7" s="188"/>
-      <c r="C7" s="188"/>
-      <c r="D7" s="188"/>
-      <c r="E7" s="188"/>
-      <c r="F7" s="192" t="s">
-        <v>163</v>
-      </c>
-      <c r="G7" s="193"/>
+      <c r="G7" s="127"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="F7:G7">
-    <cfRule type="cellIs" dxfId="32" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
       <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3347,9 +2859,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACF7CB32-E2DC-41F1-851C-45AF01A8E0CE}">
-  <sheetPr>
-    <tabColor rgb="FFFFFF00"/>
-  </sheetPr>
   <dimension ref="A1:AA9"/>
   <sheetFormatPr defaultColWidth="8.19921875" defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -3362,56 +2871,56 @@
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A1" s="94" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="2" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="194" t="s">
-        <v>156</v>
-      </c>
-      <c r="C2" s="195" t="s">
+      <c r="B2" s="135" t="s">
+        <v>150</v>
+      </c>
+      <c r="C2" s="136" t="s">
         <v>55</v>
       </c>
-      <c r="D2" s="195"/>
-      <c r="E2" s="195"/>
-      <c r="F2" s="199" t="s">
+      <c r="D2" s="136"/>
+      <c r="E2" s="136"/>
+      <c r="F2" s="140" t="s">
         <v>56</v>
       </c>
-      <c r="G2" s="200"/>
-      <c r="H2" s="200"/>
-      <c r="I2" s="200"/>
-      <c r="J2" s="200"/>
-      <c r="K2" s="200"/>
-      <c r="L2" s="200"/>
-      <c r="M2" s="200"/>
-      <c r="N2" s="200"/>
-      <c r="O2" s="201"/>
+      <c r="G2" s="141"/>
+      <c r="H2" s="141"/>
+      <c r="I2" s="141"/>
+      <c r="J2" s="141"/>
+      <c r="K2" s="141"/>
+      <c r="L2" s="141"/>
+      <c r="M2" s="141"/>
+      <c r="N2" s="141"/>
+      <c r="O2" s="142"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.45">
-      <c r="B3" s="194"/>
-      <c r="C3" s="195" t="s">
-        <v>97</v>
-      </c>
-      <c r="D3" s="195"/>
-      <c r="E3" s="195"/>
-      <c r="F3" s="202"/>
-      <c r="G3" s="203"/>
-      <c r="H3" s="203"/>
-      <c r="I3" s="203"/>
-      <c r="J3" s="203"/>
-      <c r="K3" s="203"/>
-      <c r="L3" s="203"/>
-      <c r="M3" s="203"/>
-      <c r="N3" s="203"/>
-      <c r="O3" s="204"/>
+      <c r="B3" s="135"/>
+      <c r="C3" s="136" t="s">
+        <v>96</v>
+      </c>
+      <c r="D3" s="136"/>
+      <c r="E3" s="136"/>
+      <c r="F3" s="143"/>
+      <c r="G3" s="144"/>
+      <c r="H3" s="144"/>
+      <c r="I3" s="144"/>
+      <c r="J3" s="144"/>
+      <c r="K3" s="144"/>
+      <c r="L3" s="144"/>
+      <c r="M3" s="144"/>
+      <c r="N3" s="144"/>
+      <c r="O3" s="145"/>
     </row>
     <row r="4" spans="1:27" ht="36" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B4" s="194"/>
+      <c r="B4" s="135"/>
       <c r="C4" s="97" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D4" s="97" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E4" s="96" t="s">
         <v>57</v>
@@ -3426,7 +2935,7 @@
         <v>60</v>
       </c>
       <c r="I4" s="93" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J4" s="93" t="s">
         <v>61</v>
@@ -3449,7 +2958,7 @@
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.45">
       <c r="B5" s="98" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C5" s="99"/>
       <c r="D5" s="99"/>
@@ -3467,8 +2976,8 @@
       <c r="Q5" s="101"/>
     </row>
     <row r="6" spans="1:27" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B6" s="196" t="s">
-        <v>102</v>
+      <c r="B6" s="137" t="s">
+        <v>101</v>
       </c>
       <c r="C6" s="102"/>
       <c r="D6" s="102"/>
@@ -3485,7 +2994,7 @@
       <c r="O6" s="104"/>
     </row>
     <row r="7" spans="1:27" ht="18.600000000000001" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B7" s="197"/>
+      <c r="B7" s="138"/>
       <c r="C7" s="105"/>
       <c r="D7" s="105"/>
       <c r="E7" s="106"/>
@@ -3513,7 +3022,7 @@
       <c r="AA7" s="108"/>
     </row>
     <row r="8" spans="1:27" ht="18.600000000000001" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B8" s="198"/>
+      <c r="B8" s="139"/>
       <c r="C8" s="109"/>
       <c r="D8" s="109"/>
       <c r="E8" s="110"/>
@@ -3542,10 +3051,10 @@
     </row>
     <row r="9" spans="1:27" ht="18.600000000000001" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B9" s="113" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C9" s="114" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D9" s="114"/>
       <c r="E9" s="115"/>
@@ -3570,22 +3079,22 @@
   </mergeCells>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="C5:E5">
-    <cfRule type="cellIs" dxfId="31" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="1" operator="equal">
       <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:O6">
-    <cfRule type="cellIs" dxfId="30" priority="8" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="17" priority="8" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7:O7">
-    <cfRule type="cellIs" dxfId="29" priority="13" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="16" priority="13" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8:O8">
-    <cfRule type="cellIs" dxfId="28" priority="14" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="15" priority="14" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3620,2260 +3129,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{738A7942-48C0-418C-A267-8ECE9048A1F1}">
-  <sheetPr>
-    <tabColor theme="7" tint="0.39997558519241921"/>
-  </sheetPr>
-  <dimension ref="A1:AC65"/>
-  <sheetFormatPr defaultColWidth="8.19921875" defaultRowHeight="18" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="2.59765625" style="94" customWidth="1"/>
-    <col min="2" max="2" width="2.796875" style="94" customWidth="1"/>
-    <col min="3" max="3" width="25.19921875" style="94" customWidth="1"/>
-    <col min="4" max="4" width="10.296875" style="94" customWidth="1"/>
-    <col min="5" max="6" width="10.69921875" style="95" customWidth="1"/>
-    <col min="7" max="7" width="10.69921875" style="94" customWidth="1"/>
-    <col min="8" max="8" width="14.19921875" style="94" bestFit="1" customWidth="1"/>
-    <col min="9" max="17" width="9.5" style="94" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="8.19921875" style="94"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:29" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="94" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="2" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="218" t="s">
-        <v>53</v>
-      </c>
-      <c r="C2" s="219"/>
-      <c r="D2" s="224" t="s">
-        <v>54</v>
-      </c>
-      <c r="E2" s="205" t="s">
-        <v>55</v>
-      </c>
-      <c r="F2" s="206"/>
-      <c r="G2" s="207"/>
-      <c r="H2" s="226" t="s">
-        <v>56</v>
-      </c>
-      <c r="I2" s="227"/>
-      <c r="J2" s="227"/>
-      <c r="K2" s="227"/>
-      <c r="L2" s="227"/>
-      <c r="M2" s="227"/>
-      <c r="N2" s="227"/>
-      <c r="O2" s="227"/>
-      <c r="P2" s="227"/>
-      <c r="Q2" s="228"/>
-    </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="B3" s="220"/>
-      <c r="C3" s="221"/>
-      <c r="D3" s="225"/>
-      <c r="E3" s="211" t="s">
-        <v>97</v>
-      </c>
-      <c r="F3" s="212"/>
-      <c r="G3" s="213"/>
-      <c r="H3" s="168"/>
-      <c r="I3" s="169"/>
-      <c r="J3" s="169"/>
-      <c r="K3" s="169"/>
-      <c r="L3" s="169"/>
-      <c r="M3" s="169"/>
-      <c r="N3" s="169"/>
-      <c r="O3" s="169"/>
-      <c r="P3" s="169"/>
-      <c r="Q3" s="170"/>
-    </row>
-    <row r="4" spans="1:29" ht="36.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B4" s="222"/>
-      <c r="C4" s="223"/>
-      <c r="D4" s="225"/>
-      <c r="E4" s="171" t="s">
-        <v>141</v>
-      </c>
-      <c r="F4" s="172" t="s">
-        <v>149</v>
-      </c>
-      <c r="G4" s="173" t="s">
-        <v>57</v>
-      </c>
-      <c r="H4" s="174" t="s">
-        <v>58</v>
-      </c>
-      <c r="I4" s="175" t="s">
-        <v>59</v>
-      </c>
-      <c r="J4" s="175" t="s">
-        <v>60</v>
-      </c>
-      <c r="K4" s="175" t="s">
-        <v>140</v>
-      </c>
-      <c r="L4" s="175" t="s">
-        <v>61</v>
-      </c>
-      <c r="M4" s="175" t="s">
-        <v>62</v>
-      </c>
-      <c r="N4" s="175" t="s">
-        <v>63</v>
-      </c>
-      <c r="O4" s="175" t="s">
-        <v>64</v>
-      </c>
-      <c r="P4" s="175" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q4" s="176" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="B5" s="214" t="s">
-        <v>90</v>
-      </c>
-      <c r="C5" s="217" t="s">
-        <v>89</v>
-      </c>
-      <c r="D5" s="119" t="s">
-        <v>150</v>
-      </c>
-      <c r="E5" s="120"/>
-      <c r="F5" s="120"/>
-      <c r="G5" s="121"/>
-      <c r="H5" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!F"&amp;MATCH(C5, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I5" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!G"&amp;MATCH(C5, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J5" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!H"&amp;MATCH(C5, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K5" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!I"&amp;MATCH(C5, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="L5" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!J"&amp;MATCH(C5, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="M5" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!K"&amp;MATCH(C5, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="N5" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!L"&amp;MATCH(C5, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="O5" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!M"&amp;MATCH(C5, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="P5" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!N"&amp;MATCH(C5, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Q5" s="123" t="e">
-        <f ca="1">INDIRECT("サマリ!O"&amp;MATCH(C5, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="S5" s="101"/>
-    </row>
-    <row r="6" spans="1:29" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B6" s="215"/>
-      <c r="C6" s="198"/>
-      <c r="D6" s="124" t="s">
-        <v>145</v>
-      </c>
-      <c r="E6" s="125"/>
-      <c r="F6" s="125"/>
-      <c r="G6" s="126"/>
-      <c r="H6" s="109"/>
-      <c r="I6" s="109"/>
-      <c r="J6" s="109"/>
-      <c r="K6" s="109"/>
-      <c r="L6" s="109"/>
-      <c r="M6" s="109"/>
-      <c r="N6" s="109"/>
-      <c r="O6" s="109"/>
-      <c r="P6" s="109"/>
-      <c r="Q6" s="127"/>
-      <c r="R6" s="108"/>
-      <c r="S6" s="108"/>
-      <c r="T6" s="108"/>
-      <c r="U6" s="108"/>
-      <c r="V6" s="108"/>
-      <c r="W6" s="108"/>
-      <c r="X6" s="108"/>
-      <c r="Y6" s="108"/>
-      <c r="Z6" s="108"/>
-      <c r="AA6" s="108"/>
-      <c r="AB6" s="108"/>
-      <c r="AC6" s="108"/>
-    </row>
-    <row r="7" spans="1:29" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B7" s="215"/>
-      <c r="C7" s="184" t="s">
-        <v>92</v>
-      </c>
-      <c r="D7" s="128"/>
-      <c r="E7" s="129" t="s">
-        <v>70</v>
-      </c>
-      <c r="F7" s="129" t="s">
-        <v>70</v>
-      </c>
-      <c r="G7" s="130" t="s">
-        <v>70</v>
-      </c>
-      <c r="H7" s="117" t="e">
-        <f ca="1">H5-H6</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I7" s="117" t="e">
-        <f ca="1">I5-I6</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J7" s="117" t="e">
-        <f ca="1">J5-J6</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K7" s="117" t="e">
-        <f ca="1">K5-K6</f>
-        <v>#N/A</v>
-      </c>
-      <c r="L7" s="117" t="e">
-        <f ca="1">L5-L6</f>
-        <v>#N/A</v>
-      </c>
-      <c r="M7" s="117" t="e">
-        <f t="shared" ref="M7:Q7" ca="1" si="0">M5-M6</f>
-        <v>#N/A</v>
-      </c>
-      <c r="N7" s="117" t="e">
-        <f t="shared" ca="1" si="0"/>
-        <v>#N/A</v>
-      </c>
-      <c r="O7" s="117" t="e">
-        <f t="shared" ca="1" si="0"/>
-        <v>#N/A</v>
-      </c>
-      <c r="P7" s="117" t="e">
-        <f t="shared" ca="1" si="0"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Q7" s="117" t="e">
-        <f t="shared" ca="1" si="0"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="8" spans="1:29" ht="18.600000000000001" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B8" s="215"/>
-      <c r="C8" s="217" t="s">
-        <v>102</v>
-      </c>
-      <c r="D8" s="119" t="s">
-        <v>144</v>
-      </c>
-      <c r="E8" s="120"/>
-      <c r="F8" s="120"/>
-      <c r="G8" s="121"/>
-      <c r="H8" s="122" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I8" s="122" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J8" s="122" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K8" s="122" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L8" s="122" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M8" s="122" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N8" s="122" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O8" s="122" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P8" s="122" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q8" s="123" t="e">
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="9" spans="1:29" ht="18.600000000000001" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B9" s="215"/>
-      <c r="C9" s="197"/>
-      <c r="D9" s="131" t="s">
-        <v>103</v>
-      </c>
-      <c r="E9" s="132"/>
-      <c r="F9" s="132"/>
-      <c r="G9" s="133"/>
-      <c r="H9" s="107" t="s">
-        <v>67</v>
-      </c>
-      <c r="I9" s="107" t="s">
-        <v>67</v>
-      </c>
-      <c r="J9" s="107" t="s">
-        <v>67</v>
-      </c>
-      <c r="K9" s="107" t="s">
-        <v>67</v>
-      </c>
-      <c r="L9" s="107" t="s">
-        <v>67</v>
-      </c>
-      <c r="M9" s="107" t="s">
-        <v>67</v>
-      </c>
-      <c r="N9" s="107" t="s">
-        <v>67</v>
-      </c>
-      <c r="O9" s="107" t="s">
-        <v>67</v>
-      </c>
-      <c r="P9" s="107" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q9" s="107" t="s">
-        <v>67</v>
-      </c>
-      <c r="R9" s="108"/>
-      <c r="S9" s="108"/>
-      <c r="T9" s="108"/>
-      <c r="U9" s="108"/>
-      <c r="V9" s="108"/>
-      <c r="W9" s="108"/>
-      <c r="X9" s="108"/>
-      <c r="Y9" s="108"/>
-      <c r="Z9" s="108"/>
-      <c r="AA9" s="108"/>
-      <c r="AB9" s="108"/>
-      <c r="AC9" s="108"/>
-    </row>
-    <row r="10" spans="1:29" ht="18.600000000000001" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B10" s="215"/>
-      <c r="C10" s="198"/>
-      <c r="D10" s="134" t="s">
-        <v>71</v>
-      </c>
-      <c r="E10" s="125"/>
-      <c r="F10" s="125"/>
-      <c r="G10" s="126"/>
-      <c r="H10" s="111">
-        <v>4.6143497757847536</v>
-      </c>
-      <c r="I10" s="111">
-        <v>4.4887892376681613</v>
-      </c>
-      <c r="J10" s="111">
-        <v>4.5784753363228701</v>
-      </c>
-      <c r="K10" s="111">
-        <v>4.5426008968609866</v>
-      </c>
-      <c r="L10" s="111">
-        <v>4.4887892376681613</v>
-      </c>
-      <c r="M10" s="111">
-        <v>4.4843049327354256</v>
-      </c>
-      <c r="N10" s="111">
-        <v>4.506726457399103</v>
-      </c>
-      <c r="O10" s="111">
-        <v>4.4977578475336326</v>
-      </c>
-      <c r="P10" s="111">
-        <v>4.3991031390134525</v>
-      </c>
-      <c r="Q10" s="112">
-        <v>4.376681614349776</v>
-      </c>
-      <c r="R10" s="108"/>
-      <c r="S10" s="108"/>
-      <c r="T10" s="108"/>
-      <c r="U10" s="108"/>
-      <c r="V10" s="108"/>
-      <c r="W10" s="108"/>
-      <c r="X10" s="108"/>
-      <c r="Y10" s="108"/>
-      <c r="Z10" s="108"/>
-      <c r="AA10" s="108"/>
-      <c r="AB10" s="108"/>
-      <c r="AC10" s="108"/>
-    </row>
-    <row r="11" spans="1:29" ht="18.600000000000001" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B11" s="215"/>
-      <c r="C11" s="113" t="s">
-        <v>92</v>
-      </c>
-      <c r="D11" s="128"/>
-      <c r="E11" s="129" t="s">
-        <v>70</v>
-      </c>
-      <c r="F11" s="129"/>
-      <c r="G11" s="130" t="s">
-        <v>70</v>
-      </c>
-      <c r="H11" s="116" t="e">
-        <f>H8-H9</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I11" s="117" t="e">
-        <f>I8-I9</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J11" s="116" t="e">
-        <f t="shared" ref="J11:Q11" si="1">J8-J9</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K11" s="117" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L11" s="116" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M11" s="117" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N11" s="116" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O11" s="117" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P11" s="116" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q11" s="118" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="B12" s="215"/>
-      <c r="C12" s="217" t="s">
-        <v>88</v>
-      </c>
-      <c r="D12" s="119" t="s">
-        <v>150</v>
-      </c>
-      <c r="E12" s="120"/>
-      <c r="F12" s="120"/>
-      <c r="G12" s="121"/>
-      <c r="H12" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!F"&amp;MATCH(C12, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I12" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!G"&amp;MATCH(C12, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J12" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!H"&amp;MATCH(C12, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K12" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!I"&amp;MATCH(C12, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="L12" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!J"&amp;MATCH(C12, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="M12" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!K"&amp;MATCH(C12, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="N12" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!L"&amp;MATCH(C12, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="O12" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!M"&amp;MATCH(C12, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="P12" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!N"&amp;MATCH(C12, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Q12" s="123" t="e">
-        <f ca="1">INDIRECT("サマリ!O"&amp;MATCH(C12, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="13" spans="1:29" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B13" s="215"/>
-      <c r="C13" s="198"/>
-      <c r="D13" s="124" t="s">
-        <v>145</v>
-      </c>
-      <c r="E13" s="125"/>
-      <c r="F13" s="125"/>
-      <c r="G13" s="126"/>
-      <c r="H13" s="109"/>
-      <c r="I13" s="109"/>
-      <c r="J13" s="109"/>
-      <c r="K13" s="109"/>
-      <c r="L13" s="109"/>
-      <c r="M13" s="109"/>
-      <c r="N13" s="109"/>
-      <c r="O13" s="109"/>
-      <c r="P13" s="109"/>
-      <c r="Q13" s="127"/>
-      <c r="R13" s="108"/>
-      <c r="S13" s="108"/>
-      <c r="T13" s="108"/>
-      <c r="U13" s="108"/>
-      <c r="V13" s="108"/>
-      <c r="W13" s="108"/>
-      <c r="X13" s="108"/>
-      <c r="Y13" s="108"/>
-      <c r="Z13" s="108"/>
-      <c r="AA13" s="108"/>
-      <c r="AB13" s="108"/>
-      <c r="AC13" s="108"/>
-    </row>
-    <row r="14" spans="1:29" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B14" s="216"/>
-      <c r="C14" s="183" t="s">
-        <v>92</v>
-      </c>
-      <c r="D14" s="135"/>
-      <c r="E14" s="136" t="s">
-        <v>70</v>
-      </c>
-      <c r="F14" s="136" t="s">
-        <v>70</v>
-      </c>
-      <c r="G14" s="137" t="s">
-        <v>70</v>
-      </c>
-      <c r="H14" s="138" t="e">
-        <f ca="1">H12-H13</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I14" s="138" t="e">
-        <f t="shared" ref="I14:Q14" ca="1" si="2">I12-I13</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J14" s="138" t="e">
-        <f t="shared" ca="1" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="K14" s="138" t="e">
-        <f t="shared" ca="1" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="L14" s="138" t="e">
-        <f t="shared" ca="1" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="M14" s="138" t="e">
-        <f t="shared" ca="1" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="N14" s="138" t="e">
-        <f t="shared" ca="1" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="O14" s="138" t="e">
-        <f t="shared" ca="1" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="P14" s="138" t="e">
-        <f t="shared" ca="1" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Q14" s="138" t="e">
-        <f t="shared" ca="1" si="2"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="15" spans="1:29" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="H15" s="95"/>
-      <c r="I15" s="95"/>
-      <c r="J15" s="95"/>
-      <c r="K15" s="95"/>
-      <c r="L15" s="95"/>
-      <c r="M15" s="95"/>
-      <c r="N15" s="95"/>
-      <c r="O15" s="95"/>
-      <c r="P15" s="95"/>
-      <c r="Q15" s="95"/>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="B16" s="218" t="s">
-        <v>53</v>
-      </c>
-      <c r="C16" s="219"/>
-      <c r="D16" s="224" t="s">
-        <v>54</v>
-      </c>
-      <c r="E16" s="205" t="s">
-        <v>55</v>
-      </c>
-      <c r="F16" s="206"/>
-      <c r="G16" s="207"/>
-      <c r="H16" s="208" t="s">
-        <v>56</v>
-      </c>
-      <c r="I16" s="209"/>
-      <c r="J16" s="209"/>
-      <c r="K16" s="209"/>
-      <c r="L16" s="209"/>
-      <c r="M16" s="209"/>
-      <c r="N16" s="209"/>
-      <c r="O16" s="209"/>
-      <c r="P16" s="209"/>
-      <c r="Q16" s="210"/>
-    </row>
-    <row r="17" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B17" s="220"/>
-      <c r="C17" s="221"/>
-      <c r="D17" s="225"/>
-      <c r="E17" s="211" t="s">
-        <v>97</v>
-      </c>
-      <c r="F17" s="212"/>
-      <c r="G17" s="213"/>
-      <c r="H17" s="177"/>
-      <c r="I17" s="178"/>
-      <c r="J17" s="178"/>
-      <c r="K17" s="178"/>
-      <c r="L17" s="178"/>
-      <c r="M17" s="178"/>
-      <c r="N17" s="178"/>
-      <c r="O17" s="178"/>
-      <c r="P17" s="178"/>
-      <c r="Q17" s="179"/>
-    </row>
-    <row r="18" spans="2:28" ht="36.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B18" s="222"/>
-      <c r="C18" s="223"/>
-      <c r="D18" s="225"/>
-      <c r="E18" s="171" t="s">
-        <v>141</v>
-      </c>
-      <c r="F18" s="172" t="s">
-        <v>149</v>
-      </c>
-      <c r="G18" s="173" t="s">
-        <v>57</v>
-      </c>
-      <c r="H18" s="180" t="s">
-        <v>58</v>
-      </c>
-      <c r="I18" s="181" t="s">
-        <v>59</v>
-      </c>
-      <c r="J18" s="181" t="s">
-        <v>60</v>
-      </c>
-      <c r="K18" s="181" t="s">
-        <v>139</v>
-      </c>
-      <c r="L18" s="181" t="s">
-        <v>61</v>
-      </c>
-      <c r="M18" s="181" t="s">
-        <v>62</v>
-      </c>
-      <c r="N18" s="181" t="s">
-        <v>63</v>
-      </c>
-      <c r="O18" s="181" t="s">
-        <v>64</v>
-      </c>
-      <c r="P18" s="181" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q18" s="182" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="19" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B19" s="214" t="s">
-        <v>101</v>
-      </c>
-      <c r="C19" s="217" t="s">
-        <v>147</v>
-      </c>
-      <c r="D19" s="119" t="s">
-        <v>150</v>
-      </c>
-      <c r="E19" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!C"&amp;MATCH(C19, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F19" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!D"&amp;MATCH(C19, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G19" s="139" t="e">
-        <f ca="1">INDIRECT("サマリ!E"&amp;MATCH(C19, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H19" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!F"&amp;MATCH(C19, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I19" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!G"&amp;MATCH(C19, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J19" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!H"&amp;MATCH(C19, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K19" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!I"&amp;MATCH(C19, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="L19" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!J"&amp;MATCH(C19, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="M19" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!K"&amp;MATCH(C19, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="N19" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!L"&amp;MATCH(C19, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="O19" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!M"&amp;MATCH(C19, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="P19" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!N"&amp;MATCH(C19, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Q19" s="123" t="e">
-        <f ca="1">INDIRECT("サマリ!O"&amp;MATCH(C19, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="20" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B20" s="215"/>
-      <c r="C20" s="198"/>
-      <c r="D20" s="124" t="s">
-        <v>145</v>
-      </c>
-      <c r="E20" s="109"/>
-      <c r="F20" s="109"/>
-      <c r="G20" s="140"/>
-      <c r="H20" s="109"/>
-      <c r="I20" s="109"/>
-      <c r="J20" s="109"/>
-      <c r="K20" s="109"/>
-      <c r="L20" s="109"/>
-      <c r="M20" s="141"/>
-      <c r="N20" s="109"/>
-      <c r="O20" s="109"/>
-      <c r="P20" s="141"/>
-      <c r="Q20" s="127"/>
-      <c r="R20" s="108"/>
-      <c r="S20" s="108"/>
-      <c r="T20" s="108"/>
-      <c r="U20" s="108"/>
-      <c r="V20" s="108"/>
-      <c r="W20" s="108"/>
-      <c r="X20" s="108"/>
-      <c r="Y20" s="108"/>
-      <c r="Z20" s="108"/>
-      <c r="AA20" s="108"/>
-      <c r="AB20" s="108"/>
-    </row>
-    <row r="21" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B21" s="215"/>
-      <c r="C21" s="184" t="s">
-        <v>92</v>
-      </c>
-      <c r="D21" s="128"/>
-      <c r="E21" s="116" t="e">
-        <f ca="1">E19-E20</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F21" s="116" t="e">
-        <f ca="1">F19-F20</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G21" s="142" t="e">
-        <f ca="1">G19-G20</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H21" s="116" t="e">
-        <f ca="1">H19-H20</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I21" s="116" t="e">
-        <f t="shared" ref="I21:Q21" ca="1" si="3">I19-I20</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J21" s="116" t="e">
-        <f t="shared" ca="1" si="3"/>
-        <v>#N/A</v>
-      </c>
-      <c r="K21" s="116" t="e">
-        <f t="shared" ca="1" si="3"/>
-        <v>#N/A</v>
-      </c>
-      <c r="L21" s="116" t="e">
-        <f t="shared" ca="1" si="3"/>
-        <v>#N/A</v>
-      </c>
-      <c r="M21" s="116" t="e">
-        <f t="shared" ca="1" si="3"/>
-        <v>#N/A</v>
-      </c>
-      <c r="N21" s="116" t="e">
-        <f t="shared" ca="1" si="3"/>
-        <v>#N/A</v>
-      </c>
-      <c r="O21" s="116" t="e">
-        <f t="shared" ca="1" si="3"/>
-        <v>#N/A</v>
-      </c>
-      <c r="P21" s="116" t="e">
-        <f t="shared" ca="1" si="3"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Q21" s="116" t="e">
-        <f t="shared" ca="1" si="3"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="22" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B22" s="215"/>
-      <c r="C22" s="217" t="s">
-        <v>152</v>
-      </c>
-      <c r="D22" s="119" t="s">
-        <v>150</v>
-      </c>
-      <c r="E22" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!C"&amp;MATCH(C22, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F22" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!D"&amp;MATCH(C22, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G22" s="139" t="e">
-        <f ca="1">INDIRECT("サマリ!E"&amp;MATCH(C22, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H22" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!F"&amp;MATCH(C22, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I22" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!G"&amp;MATCH(C22, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J22" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!H"&amp;MATCH(C22, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K22" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!I"&amp;MATCH(C22, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="L22" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!J"&amp;MATCH(C22, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="M22" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!K"&amp;MATCH(C22, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="N22" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!L"&amp;MATCH(C22, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="O22" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!M"&amp;MATCH(C22, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="P22" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!N"&amp;MATCH(C22, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Q22" s="123" t="e">
-        <f ca="1">INDIRECT("サマリ!O"&amp;MATCH(C22, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="23" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B23" s="215"/>
-      <c r="C23" s="198"/>
-      <c r="D23" s="124" t="s">
-        <v>145</v>
-      </c>
-      <c r="E23" s="109"/>
-      <c r="F23" s="109"/>
-      <c r="G23" s="140"/>
-      <c r="H23" s="109"/>
-      <c r="I23" s="109"/>
-      <c r="J23" s="109"/>
-      <c r="K23" s="109"/>
-      <c r="L23" s="109"/>
-      <c r="M23" s="109"/>
-      <c r="N23" s="109"/>
-      <c r="O23" s="109"/>
-      <c r="P23" s="109"/>
-      <c r="Q23" s="127"/>
-      <c r="R23" s="108"/>
-      <c r="S23" s="108"/>
-      <c r="T23" s="108"/>
-      <c r="U23" s="108"/>
-      <c r="V23" s="108"/>
-      <c r="W23" s="108"/>
-      <c r="X23" s="108"/>
-      <c r="Y23" s="108"/>
-      <c r="Z23" s="108"/>
-      <c r="AA23" s="108"/>
-      <c r="AB23" s="108"/>
-    </row>
-    <row r="24" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B24" s="215"/>
-      <c r="C24" s="184" t="s">
-        <v>92</v>
-      </c>
-      <c r="D24" s="128"/>
-      <c r="E24" s="116" t="e">
-        <f ca="1">E22-E23</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F24" s="116" t="e">
-        <f t="shared" ref="F24" ca="1" si="4">F22-F23</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G24" s="142" t="e">
-        <f ca="1">G22-G23</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H24" s="116" t="e">
-        <f ca="1">H22-H23</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I24" s="116" t="e">
-        <f t="shared" ref="I24:Q24" ca="1" si="5">I22-I23</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J24" s="116" t="e">
-        <f t="shared" ca="1" si="5"/>
-        <v>#N/A</v>
-      </c>
-      <c r="K24" s="116" t="e">
-        <f t="shared" ca="1" si="5"/>
-        <v>#N/A</v>
-      </c>
-      <c r="L24" s="116" t="e">
-        <f t="shared" ca="1" si="5"/>
-        <v>#N/A</v>
-      </c>
-      <c r="M24" s="116" t="e">
-        <f t="shared" ca="1" si="5"/>
-        <v>#N/A</v>
-      </c>
-      <c r="N24" s="116" t="e">
-        <f t="shared" ca="1" si="5"/>
-        <v>#N/A</v>
-      </c>
-      <c r="O24" s="116" t="e">
-        <f t="shared" ca="1" si="5"/>
-        <v>#N/A</v>
-      </c>
-      <c r="P24" s="116" t="e">
-        <f t="shared" ca="1" si="5"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Q24" s="116" t="e">
-        <f t="shared" ca="1" si="5"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="25" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B25" s="215"/>
-      <c r="C25" s="217" t="s">
-        <v>153</v>
-      </c>
-      <c r="D25" s="119" t="s">
-        <v>150</v>
-      </c>
-      <c r="E25" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!C"&amp;MATCH(C25, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F25" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!D"&amp;MATCH(C25, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G25" s="139" t="e">
-        <f ca="1">INDIRECT("サマリ!E"&amp;MATCH(C25, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H25" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!F"&amp;MATCH(C25, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I25" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!G"&amp;MATCH(C25, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J25" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!H"&amp;MATCH(C25, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K25" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!I"&amp;MATCH(C25, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="L25" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!J"&amp;MATCH(C25, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="M25" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!K"&amp;MATCH(C25, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="N25" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!L"&amp;MATCH(C25, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="O25" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!M"&amp;MATCH(C25, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="P25" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!N"&amp;MATCH(C25, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Q25" s="123" t="e">
-        <f ca="1">INDIRECT("サマリ!O"&amp;MATCH(C25, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="26" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B26" s="215"/>
-      <c r="C26" s="198"/>
-      <c r="D26" s="124" t="s">
-        <v>145</v>
-      </c>
-      <c r="E26" s="109"/>
-      <c r="F26" s="109"/>
-      <c r="G26" s="140"/>
-      <c r="H26" s="109"/>
-      <c r="I26" s="109"/>
-      <c r="J26" s="109"/>
-      <c r="K26" s="109"/>
-      <c r="L26" s="109"/>
-      <c r="M26" s="109"/>
-      <c r="N26" s="109"/>
-      <c r="O26" s="109"/>
-      <c r="P26" s="109"/>
-      <c r="Q26" s="127"/>
-      <c r="R26" s="108"/>
-      <c r="S26" s="108"/>
-      <c r="T26" s="108"/>
-      <c r="U26" s="108"/>
-      <c r="V26" s="108"/>
-      <c r="W26" s="108"/>
-      <c r="X26" s="108"/>
-      <c r="Y26" s="108"/>
-      <c r="Z26" s="108"/>
-      <c r="AA26" s="108"/>
-      <c r="AB26" s="108"/>
-    </row>
-    <row r="27" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B27" s="216"/>
-      <c r="C27" s="183" t="s">
-        <v>92</v>
-      </c>
-      <c r="D27" s="143"/>
-      <c r="E27" s="144" t="e">
-        <f ca="1">E25-E26</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F27" s="144" t="e">
-        <f t="shared" ref="F27" ca="1" si="6">F25-F26</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G27" s="145" t="e">
-        <f ca="1">G25-G26</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H27" s="144" t="e">
-        <f ca="1">H25-H26</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I27" s="144" t="e">
-        <f t="shared" ref="I27:Q27" ca="1" si="7">I25-I26</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J27" s="144" t="e">
-        <f t="shared" ca="1" si="7"/>
-        <v>#N/A</v>
-      </c>
-      <c r="K27" s="144" t="e">
-        <f t="shared" ca="1" si="7"/>
-        <v>#N/A</v>
-      </c>
-      <c r="L27" s="144" t="e">
-        <f t="shared" ca="1" si="7"/>
-        <v>#N/A</v>
-      </c>
-      <c r="M27" s="144" t="e">
-        <f t="shared" ca="1" si="7"/>
-        <v>#N/A</v>
-      </c>
-      <c r="N27" s="144" t="e">
-        <f t="shared" ca="1" si="7"/>
-        <v>#N/A</v>
-      </c>
-      <c r="O27" s="144" t="e">
-        <f t="shared" ca="1" si="7"/>
-        <v>#N/A</v>
-      </c>
-      <c r="P27" s="144" t="e">
-        <f t="shared" ca="1" si="7"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Q27" s="146" t="e">
-        <f t="shared" ca="1" si="7"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="28" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="H28" s="95"/>
-      <c r="I28" s="95"/>
-      <c r="J28" s="95"/>
-      <c r="K28" s="95"/>
-      <c r="L28" s="95"/>
-      <c r="M28" s="95"/>
-      <c r="N28" s="95"/>
-      <c r="O28" s="95"/>
-      <c r="P28" s="95"/>
-      <c r="Q28" s="95"/>
-    </row>
-    <row r="29" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B29" s="218" t="s">
-        <v>53</v>
-      </c>
-      <c r="C29" s="219"/>
-      <c r="D29" s="224" t="s">
-        <v>54</v>
-      </c>
-      <c r="E29" s="205" t="s">
-        <v>55</v>
-      </c>
-      <c r="F29" s="206"/>
-      <c r="G29" s="207"/>
-      <c r="H29" s="208" t="s">
-        <v>56</v>
-      </c>
-      <c r="I29" s="209"/>
-      <c r="J29" s="209"/>
-      <c r="K29" s="209"/>
-      <c r="L29" s="209"/>
-      <c r="M29" s="209"/>
-      <c r="N29" s="209"/>
-      <c r="O29" s="209"/>
-      <c r="P29" s="209"/>
-      <c r="Q29" s="210"/>
-    </row>
-    <row r="30" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B30" s="220"/>
-      <c r="C30" s="221"/>
-      <c r="D30" s="225"/>
-      <c r="E30" s="211" t="s">
-        <v>97</v>
-      </c>
-      <c r="F30" s="212"/>
-      <c r="G30" s="213"/>
-      <c r="H30" s="177"/>
-      <c r="I30" s="178"/>
-      <c r="J30" s="178"/>
-      <c r="K30" s="178"/>
-      <c r="L30" s="178"/>
-      <c r="M30" s="178"/>
-      <c r="N30" s="178"/>
-      <c r="O30" s="178"/>
-      <c r="P30" s="178"/>
-      <c r="Q30" s="179"/>
-    </row>
-    <row r="31" spans="2:28" ht="36.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B31" s="222"/>
-      <c r="C31" s="223"/>
-      <c r="D31" s="225"/>
-      <c r="E31" s="171" t="s">
-        <v>141</v>
-      </c>
-      <c r="F31" s="172" t="s">
-        <v>149</v>
-      </c>
-      <c r="G31" s="173" t="s">
-        <v>57</v>
-      </c>
-      <c r="H31" s="180" t="s">
-        <v>58</v>
-      </c>
-      <c r="I31" s="181" t="s">
-        <v>59</v>
-      </c>
-      <c r="J31" s="181" t="s">
-        <v>60</v>
-      </c>
-      <c r="K31" s="181" t="s">
-        <v>139</v>
-      </c>
-      <c r="L31" s="181" t="s">
-        <v>61</v>
-      </c>
-      <c r="M31" s="181" t="s">
-        <v>62</v>
-      </c>
-      <c r="N31" s="181" t="s">
-        <v>63</v>
-      </c>
-      <c r="O31" s="181" t="s">
-        <v>64</v>
-      </c>
-      <c r="P31" s="181" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q31" s="182" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="32" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B32" s="214" t="s">
-        <v>96</v>
-      </c>
-      <c r="C32" s="217" t="s">
-        <v>81</v>
-      </c>
-      <c r="D32" s="119" t="s">
-        <v>150</v>
-      </c>
-      <c r="E32" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!C"&amp;MATCH(C32, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F32" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!D"&amp;MATCH(C32, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G32" s="139" t="e">
-        <f ca="1">INDIRECT("サマリ!E"&amp;MATCH(C32, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H32" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!F"&amp;MATCH(C32, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I32" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!G"&amp;MATCH(C32, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J32" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!H"&amp;MATCH(C32, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K32" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!I"&amp;MATCH(C32, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="L32" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!J"&amp;MATCH(C32, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="M32" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!K"&amp;MATCH(C32, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="N32" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!L"&amp;MATCH(C32, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="O32" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!M"&amp;MATCH(C32, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="P32" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!N"&amp;MATCH(C32, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Q32" s="123" t="e">
-        <f ca="1">INDIRECT("サマリ!O"&amp;MATCH(C32, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="33" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B33" s="215"/>
-      <c r="C33" s="198"/>
-      <c r="D33" s="124" t="s">
-        <v>145</v>
-      </c>
-      <c r="E33" s="109"/>
-      <c r="F33" s="109"/>
-      <c r="G33" s="140"/>
-      <c r="H33" s="109"/>
-      <c r="I33" s="109"/>
-      <c r="J33" s="109"/>
-      <c r="K33" s="109"/>
-      <c r="L33" s="109"/>
-      <c r="M33" s="109"/>
-      <c r="N33" s="109"/>
-      <c r="O33" s="109"/>
-      <c r="P33" s="109"/>
-      <c r="Q33" s="127"/>
-      <c r="R33" s="108"/>
-      <c r="S33" s="108"/>
-      <c r="T33" s="108"/>
-      <c r="U33" s="108"/>
-      <c r="V33" s="108"/>
-      <c r="W33" s="108"/>
-      <c r="X33" s="108"/>
-      <c r="Y33" s="108"/>
-      <c r="Z33" s="108"/>
-      <c r="AA33" s="108"/>
-      <c r="AB33" s="108"/>
-    </row>
-    <row r="34" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B34" s="215"/>
-      <c r="C34" s="184" t="s">
-        <v>92</v>
-      </c>
-      <c r="D34" s="147"/>
-      <c r="E34" s="148" t="e">
-        <f ca="1">E32-E33</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F34" s="149" t="e">
-        <f ca="1">F32-F33</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G34" s="142" t="e">
-        <f ca="1">G32-G33</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H34" s="116" t="e">
-        <f ca="1">H32-H33</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I34" s="116" t="e">
-        <f t="shared" ref="I34:Q34" ca="1" si="8">I32-I33</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J34" s="116" t="e">
-        <f t="shared" ca="1" si="8"/>
-        <v>#N/A</v>
-      </c>
-      <c r="K34" s="116" t="e">
-        <f t="shared" ca="1" si="8"/>
-        <v>#N/A</v>
-      </c>
-      <c r="L34" s="116" t="e">
-        <f t="shared" ca="1" si="8"/>
-        <v>#N/A</v>
-      </c>
-      <c r="M34" s="116" t="e">
-        <f t="shared" ca="1" si="8"/>
-        <v>#N/A</v>
-      </c>
-      <c r="N34" s="116" t="e">
-        <f t="shared" ca="1" si="8"/>
-        <v>#N/A</v>
-      </c>
-      <c r="O34" s="116" t="e">
-        <f t="shared" ca="1" si="8"/>
-        <v>#N/A</v>
-      </c>
-      <c r="P34" s="116" t="e">
-        <f t="shared" ca="1" si="8"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Q34" s="116" t="e">
-        <f t="shared" ca="1" si="8"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B35" s="215"/>
-      <c r="C35" s="217" t="s">
-        <v>80</v>
-      </c>
-      <c r="D35" s="119" t="s">
-        <v>150</v>
-      </c>
-      <c r="E35" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!C"&amp;MATCH(C35, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F35" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!D"&amp;MATCH(C35, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G35" s="139" t="e">
-        <f ca="1">INDIRECT("サマリ!E"&amp;MATCH(C35, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H35" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!F"&amp;MATCH(C35, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I35" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!G"&amp;MATCH(C35, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J35" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!H"&amp;MATCH(C35, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K35" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!I"&amp;MATCH(C35, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="L35" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!J"&amp;MATCH(C35, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="M35" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!K"&amp;MATCH(C35, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="N35" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!L"&amp;MATCH(C35, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="O35" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!M"&amp;MATCH(C35, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="P35" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!N"&amp;MATCH(C35, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Q35" s="123" t="e">
-        <f ca="1">INDIRECT("サマリ!O"&amp;MATCH(C35, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="36" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B36" s="215"/>
-      <c r="C36" s="198"/>
-      <c r="D36" s="124" t="s">
-        <v>145</v>
-      </c>
-      <c r="E36" s="109"/>
-      <c r="F36" s="109"/>
-      <c r="G36" s="140"/>
-      <c r="H36" s="141"/>
-      <c r="I36" s="141"/>
-      <c r="J36" s="141"/>
-      <c r="K36" s="141"/>
-      <c r="L36" s="141"/>
-      <c r="M36" s="141"/>
-      <c r="N36" s="141"/>
-      <c r="O36" s="141"/>
-      <c r="P36" s="141"/>
-      <c r="Q36" s="150"/>
-      <c r="R36" s="108"/>
-      <c r="S36" s="108"/>
-      <c r="T36" s="108"/>
-      <c r="U36" s="108"/>
-      <c r="V36" s="108"/>
-      <c r="W36" s="108"/>
-      <c r="X36" s="108"/>
-      <c r="Y36" s="108"/>
-      <c r="Z36" s="108"/>
-      <c r="AA36" s="108"/>
-      <c r="AB36" s="108"/>
-    </row>
-    <row r="37" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B37" s="215"/>
-      <c r="C37" s="184" t="s">
-        <v>92</v>
-      </c>
-      <c r="D37" s="147"/>
-      <c r="E37" s="148" t="e">
-        <f ca="1">E35-E36</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F37" s="149" t="e">
-        <f ca="1">F35-F36</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G37" s="142" t="e">
-        <f ca="1">G35-G36</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H37" s="116" t="e">
-        <f ca="1">H35-H36</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I37" s="116" t="e">
-        <f t="shared" ref="I37:Q37" ca="1" si="9">I35-I36</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J37" s="116" t="e">
-        <f t="shared" ca="1" si="9"/>
-        <v>#N/A</v>
-      </c>
-      <c r="K37" s="116" t="e">
-        <f t="shared" ca="1" si="9"/>
-        <v>#N/A</v>
-      </c>
-      <c r="L37" s="116" t="e">
-        <f t="shared" ca="1" si="9"/>
-        <v>#N/A</v>
-      </c>
-      <c r="M37" s="116" t="e">
-        <f t="shared" ca="1" si="9"/>
-        <v>#N/A</v>
-      </c>
-      <c r="N37" s="116" t="e">
-        <f t="shared" ca="1" si="9"/>
-        <v>#N/A</v>
-      </c>
-      <c r="O37" s="116" t="e">
-        <f t="shared" ca="1" si="9"/>
-        <v>#N/A</v>
-      </c>
-      <c r="P37" s="116" t="e">
-        <f t="shared" ca="1" si="9"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Q37" s="116" t="e">
-        <f t="shared" ca="1" si="9"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B38" s="215"/>
-      <c r="C38" s="217" t="s">
-        <v>94</v>
-      </c>
-      <c r="D38" s="119" t="s">
-        <v>150</v>
-      </c>
-      <c r="E38" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!C"&amp;MATCH(C38, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F38" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!D"&amp;MATCH(C38, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G38" s="139" t="e">
-        <f ca="1">INDIRECT("サマリ!E"&amp;MATCH(C38, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H38" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!F"&amp;MATCH(C38, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I38" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!G"&amp;MATCH(C38, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J38" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!H"&amp;MATCH(C38, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K38" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!I"&amp;MATCH(C38, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="L38" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!J"&amp;MATCH(C38, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="M38" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!K"&amp;MATCH(C38, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="N38" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!L"&amp;MATCH(C38, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="O38" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!M"&amp;MATCH(C38, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="P38" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!N"&amp;MATCH(C38, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Q38" s="123" t="e">
-        <f ca="1">INDIRECT("サマリ!O"&amp;MATCH(C38, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="39" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B39" s="215"/>
-      <c r="C39" s="198"/>
-      <c r="D39" s="124" t="s">
-        <v>145</v>
-      </c>
-      <c r="E39" s="109"/>
-      <c r="F39" s="109"/>
-      <c r="G39" s="140"/>
-      <c r="H39" s="141"/>
-      <c r="I39" s="141"/>
-      <c r="J39" s="141"/>
-      <c r="K39" s="141"/>
-      <c r="L39" s="141"/>
-      <c r="M39" s="141"/>
-      <c r="N39" s="141"/>
-      <c r="O39" s="141"/>
-      <c r="P39" s="141"/>
-      <c r="Q39" s="150"/>
-      <c r="R39" s="108"/>
-      <c r="S39" s="108"/>
-      <c r="T39" s="108"/>
-      <c r="U39" s="108"/>
-      <c r="V39" s="108"/>
-      <c r="W39" s="108"/>
-      <c r="X39" s="108"/>
-      <c r="Y39" s="108"/>
-      <c r="Z39" s="108"/>
-      <c r="AA39" s="108"/>
-      <c r="AB39" s="108"/>
-    </row>
-    <row r="40" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B40" s="215"/>
-      <c r="C40" s="184" t="s">
-        <v>92</v>
-      </c>
-      <c r="D40" s="151"/>
-      <c r="E40" s="148" t="e">
-        <f ca="1">E38-E39</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F40" s="149" t="e">
-        <f ca="1">F38-F39</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G40" s="142" t="e">
-        <f ca="1">G38-G39</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H40" s="152" t="e">
-        <f ca="1">H38-H39</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I40" s="152" t="e">
-        <f t="shared" ref="I40:Q40" ca="1" si="10">I38-I39</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J40" s="152" t="e">
-        <f t="shared" ca="1" si="10"/>
-        <v>#N/A</v>
-      </c>
-      <c r="K40" s="152" t="e">
-        <f t="shared" ca="1" si="10"/>
-        <v>#N/A</v>
-      </c>
-      <c r="L40" s="152" t="e">
-        <f t="shared" ca="1" si="10"/>
-        <v>#N/A</v>
-      </c>
-      <c r="M40" s="152" t="e">
-        <f t="shared" ca="1" si="10"/>
-        <v>#N/A</v>
-      </c>
-      <c r="N40" s="152" t="e">
-        <f t="shared" ca="1" si="10"/>
-        <v>#N/A</v>
-      </c>
-      <c r="O40" s="152" t="e">
-        <f t="shared" ca="1" si="10"/>
-        <v>#N/A</v>
-      </c>
-      <c r="P40" s="152" t="e">
-        <f t="shared" ca="1" si="10"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Q40" s="152" t="e">
-        <f t="shared" ca="1" si="10"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B41" s="215"/>
-      <c r="C41" s="217" t="s">
-        <v>154</v>
-      </c>
-      <c r="D41" s="119" t="s">
-        <v>150</v>
-      </c>
-      <c r="E41" s="153"/>
-      <c r="F41" s="154"/>
-      <c r="G41" s="121"/>
-      <c r="H41" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!F"&amp;MATCH(C41, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I41" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!G"&amp;MATCH(C41, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J41" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!H"&amp;MATCH(C41, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K41" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!I"&amp;MATCH(C41, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="L41" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!J"&amp;MATCH(C41, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="M41" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!K"&amp;MATCH(C41, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="N41" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!L"&amp;MATCH(C41, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="O41" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!M"&amp;MATCH(C41, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="P41" s="122" t="e">
-        <f ca="1">INDIRECT("サマリ!N"&amp;MATCH(C41, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Q41" s="123" t="e">
-        <f ca="1">INDIRECT("サマリ!O"&amp;MATCH(C41, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="42" spans="2:28" ht="18.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B42" s="215"/>
-      <c r="C42" s="198"/>
-      <c r="D42" s="124" t="s">
-        <v>145</v>
-      </c>
-      <c r="E42" s="155"/>
-      <c r="F42" s="156"/>
-      <c r="G42" s="126"/>
-      <c r="H42" s="141"/>
-      <c r="I42" s="141"/>
-      <c r="J42" s="141"/>
-      <c r="K42" s="141"/>
-      <c r="L42" s="141"/>
-      <c r="M42" s="141"/>
-      <c r="N42" s="141"/>
-      <c r="O42" s="141"/>
-      <c r="P42" s="141"/>
-      <c r="Q42" s="150"/>
-      <c r="R42" s="108"/>
-      <c r="S42" s="108"/>
-      <c r="T42" s="108"/>
-      <c r="U42" s="108"/>
-      <c r="V42" s="108"/>
-      <c r="W42" s="108"/>
-      <c r="X42" s="108"/>
-      <c r="Y42" s="108"/>
-      <c r="Z42" s="108"/>
-      <c r="AA42" s="108"/>
-      <c r="AB42" s="108"/>
-    </row>
-    <row r="43" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B43" s="216"/>
-      <c r="C43" s="183" t="s">
-        <v>92</v>
-      </c>
-      <c r="D43" s="157"/>
-      <c r="E43" s="158" t="s">
-        <v>70</v>
-      </c>
-      <c r="F43" s="159" t="s">
-        <v>70</v>
-      </c>
-      <c r="G43" s="160" t="s">
-        <v>70</v>
-      </c>
-      <c r="H43" s="161" t="e">
-        <f ca="1">H41-H42</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I43" s="161" t="e">
-        <f t="shared" ref="I43:Q43" ca="1" si="11">I41-I42</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J43" s="161" t="e">
-        <f t="shared" ca="1" si="11"/>
-        <v>#N/A</v>
-      </c>
-      <c r="K43" s="161" t="e">
-        <f t="shared" ca="1" si="11"/>
-        <v>#N/A</v>
-      </c>
-      <c r="L43" s="161" t="e">
-        <f t="shared" ca="1" si="11"/>
-        <v>#N/A</v>
-      </c>
-      <c r="M43" s="161" t="e">
-        <f t="shared" ca="1" si="11"/>
-        <v>#N/A</v>
-      </c>
-      <c r="N43" s="161" t="e">
-        <f t="shared" ca="1" si="11"/>
-        <v>#N/A</v>
-      </c>
-      <c r="O43" s="161" t="e">
-        <f t="shared" ca="1" si="11"/>
-        <v>#N/A</v>
-      </c>
-      <c r="P43" s="161" t="e">
-        <f t="shared" ca="1" si="11"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Q43" s="161" t="e">
-        <f t="shared" ca="1" si="11"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="C45" s="94" t="s">
-        <v>91</v>
-      </c>
-      <c r="D45" s="162" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="C46" s="163"/>
-      <c r="D46" s="164" t="s">
-        <v>89</v>
-      </c>
-      <c r="E46" s="165"/>
-      <c r="F46" s="165"/>
-      <c r="G46" s="166"/>
-      <c r="H46" s="166" t="s">
-        <v>78</v>
-      </c>
-      <c r="I46" s="166"/>
-      <c r="J46" s="166"/>
-      <c r="K46" s="166"/>
-      <c r="L46" s="166"/>
-      <c r="M46" s="166"/>
-      <c r="N46" s="166"/>
-      <c r="O46" s="166"/>
-      <c r="P46" s="166"/>
-      <c r="Q46" s="166"/>
-      <c r="R46" s="166"/>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="D47" s="164" t="s">
-        <v>88</v>
-      </c>
-      <c r="E47" s="165"/>
-      <c r="F47" s="165"/>
-      <c r="G47" s="166"/>
-      <c r="H47" s="166" t="s">
-        <v>78</v>
-      </c>
-      <c r="I47" s="166"/>
-      <c r="J47" s="166"/>
-      <c r="K47" s="166"/>
-      <c r="L47" s="166"/>
-      <c r="M47" s="166"/>
-      <c r="N47" s="166"/>
-      <c r="O47" s="166"/>
-      <c r="P47" s="166"/>
-      <c r="Q47" s="166"/>
-      <c r="R47" s="166"/>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="D48" s="162" t="s">
-        <v>87</v>
-      </c>
-      <c r="E48" s="165"/>
-      <c r="F48" s="165"/>
-      <c r="G48" s="166"/>
-      <c r="H48" s="166" t="s">
-        <v>78</v>
-      </c>
-      <c r="I48" s="166"/>
-      <c r="L48" s="166"/>
-      <c r="M48" s="166"/>
-      <c r="N48" s="166"/>
-      <c r="O48" s="166"/>
-      <c r="P48" s="166"/>
-      <c r="Q48" s="166"/>
-      <c r="R48" s="166"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.45">
-      <c r="D49" s="164" t="s">
-        <v>86</v>
-      </c>
-      <c r="E49" s="165"/>
-      <c r="F49" s="165"/>
-      <c r="G49" s="166"/>
-      <c r="H49" s="166" t="s">
-        <v>78</v>
-      </c>
-      <c r="I49" s="166"/>
-      <c r="J49" s="166"/>
-      <c r="K49" s="166"/>
-      <c r="L49" s="166"/>
-      <c r="M49" s="166"/>
-      <c r="N49" s="166"/>
-      <c r="O49" s="166"/>
-      <c r="P49" s="166"/>
-      <c r="Q49" s="166"/>
-      <c r="R49" s="166"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.45">
-      <c r="D50" s="164" t="s">
-        <v>85</v>
-      </c>
-      <c r="E50" s="165"/>
-      <c r="F50" s="165"/>
-      <c r="G50" s="166"/>
-      <c r="H50" s="166"/>
-      <c r="I50" s="166"/>
-      <c r="J50" s="166"/>
-      <c r="K50" s="166"/>
-      <c r="L50" s="166"/>
-      <c r="M50" s="166"/>
-      <c r="N50" s="166"/>
-      <c r="O50" s="166"/>
-      <c r="P50" s="166"/>
-      <c r="Q50" s="166"/>
-      <c r="R50" s="166"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.45">
-      <c r="D51" s="164" t="s">
-        <v>84</v>
-      </c>
-      <c r="E51" s="165"/>
-      <c r="F51" s="165"/>
-      <c r="G51" s="166"/>
-      <c r="H51" s="166" t="s">
-        <v>78</v>
-      </c>
-      <c r="I51" s="166"/>
-      <c r="J51" s="166"/>
-      <c r="K51" s="166"/>
-      <c r="L51" s="166"/>
-      <c r="M51" s="166"/>
-      <c r="N51" s="166"/>
-      <c r="O51" s="166"/>
-      <c r="P51" s="166"/>
-      <c r="Q51" s="166"/>
-      <c r="R51" s="166"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.45">
-      <c r="D52" s="164" t="s">
-        <v>83</v>
-      </c>
-      <c r="E52" s="165"/>
-      <c r="F52" s="165"/>
-      <c r="G52" s="166"/>
-      <c r="H52" s="166" t="s">
-        <v>78</v>
-      </c>
-      <c r="I52" s="166"/>
-      <c r="J52" s="166"/>
-      <c r="K52" s="166"/>
-      <c r="L52" s="166"/>
-      <c r="M52" s="166"/>
-      <c r="N52" s="166"/>
-      <c r="O52" s="166"/>
-      <c r="P52" s="166"/>
-      <c r="Q52" s="166"/>
-      <c r="R52" s="166"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.45">
-      <c r="D53" s="167" t="s">
-        <v>82</v>
-      </c>
-      <c r="E53" s="165"/>
-      <c r="F53" s="165"/>
-      <c r="G53" s="166"/>
-      <c r="H53" s="166" t="s">
-        <v>78</v>
-      </c>
-      <c r="I53" s="166"/>
-      <c r="J53" s="166"/>
-      <c r="K53" s="166"/>
-      <c r="L53" s="166"/>
-      <c r="M53" s="166"/>
-      <c r="N53" s="166"/>
-      <c r="O53" s="166"/>
-      <c r="P53" s="166"/>
-      <c r="Q53" s="166"/>
-      <c r="R53" s="166"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.45">
-      <c r="D54" s="164" t="s">
-        <v>81</v>
-      </c>
-      <c r="E54" s="165"/>
-      <c r="F54" s="165"/>
-      <c r="G54" s="166"/>
-      <c r="H54" s="166" t="s">
-        <v>78</v>
-      </c>
-      <c r="I54" s="166"/>
-      <c r="J54" s="166"/>
-      <c r="K54" s="166"/>
-      <c r="L54" s="166"/>
-      <c r="M54" s="166"/>
-      <c r="N54" s="166"/>
-      <c r="O54" s="166"/>
-      <c r="P54" s="166"/>
-      <c r="Q54" s="166"/>
-      <c r="R54" s="166"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.45">
-      <c r="D55" s="164" t="s">
-        <v>80</v>
-      </c>
-      <c r="E55" s="165"/>
-      <c r="F55" s="165"/>
-      <c r="G55" s="166"/>
-      <c r="H55" s="166" t="s">
-        <v>78</v>
-      </c>
-      <c r="I55" s="166"/>
-      <c r="J55" s="166"/>
-      <c r="K55" s="166"/>
-      <c r="L55" s="166"/>
-      <c r="M55" s="166"/>
-      <c r="N55" s="166"/>
-      <c r="O55" s="166"/>
-      <c r="P55" s="166"/>
-      <c r="Q55" s="166"/>
-      <c r="R55" s="166"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.45">
-      <c r="D56" s="164" t="s">
-        <v>79</v>
-      </c>
-      <c r="E56" s="165"/>
-      <c r="F56" s="165"/>
-      <c r="G56" s="166"/>
-      <c r="H56" s="166" t="s">
-        <v>78</v>
-      </c>
-      <c r="I56" s="166"/>
-      <c r="J56" s="166"/>
-      <c r="K56" s="166"/>
-      <c r="L56" s="166"/>
-      <c r="M56" s="166"/>
-      <c r="N56" s="166"/>
-      <c r="O56" s="166"/>
-      <c r="P56" s="166"/>
-      <c r="Q56" s="166"/>
-      <c r="R56" s="166"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.45">
-      <c r="C58" s="94" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.45">
-      <c r="C59" s="94" t="s">
-        <v>76</v>
-      </c>
-      <c r="E59" s="165"/>
-      <c r="F59" s="165"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.45">
-      <c r="C60" s="94" t="s">
-        <v>75</v>
-      </c>
-      <c r="E60" s="165"/>
-      <c r="F60" s="165"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.45">
-      <c r="C61" s="94" t="s">
-        <v>142</v>
-      </c>
-      <c r="E61" s="165"/>
-      <c r="F61" s="165"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.45">
-      <c r="C63" s="94" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.45">
-      <c r="C64" s="94" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="65" spans="3:3" x14ac:dyDescent="0.45">
-      <c r="C65" s="94" t="s">
-        <v>72</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="28">
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:Q2"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="B5:B14"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="B2:C4"/>
-    <mergeCell ref="B16:C18"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="E16:G16"/>
-    <mergeCell ref="H16:Q16"/>
-    <mergeCell ref="E17:G17"/>
-    <mergeCell ref="B32:B43"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="B29:C31"/>
-    <mergeCell ref="D29:D31"/>
-    <mergeCell ref="E29:G29"/>
-    <mergeCell ref="H29:Q29"/>
-    <mergeCell ref="E30:G30"/>
-    <mergeCell ref="B19:B27"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="C22:C23"/>
-  </mergeCells>
-  <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="H5:Q6">
-    <cfRule type="cellIs" dxfId="27" priority="1" operator="lessThanOrEqual">
-      <formula>3.4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H8:Q8">
-    <cfRule type="cellIs" dxfId="26" priority="18" operator="lessThanOrEqual">
-      <formula>3.4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H9:Q9">
-    <cfRule type="cellIs" dxfId="25" priority="19" operator="lessThanOrEqual">
-      <formula>3.4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H10:Q10">
-    <cfRule type="cellIs" dxfId="24" priority="20" operator="lessThanOrEqual">
-      <formula>3.4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H12:Q13">
-    <cfRule type="cellIs" dxfId="23" priority="4" operator="lessThanOrEqual">
-      <formula>3.4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H19:Q20">
-    <cfRule type="cellIs" dxfId="22" priority="16" operator="lessThanOrEqual">
-      <formula>3.4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H22:Q22">
-    <cfRule type="cellIs" dxfId="21" priority="10" operator="lessThanOrEqual">
-      <formula>3.4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H23:Q23 H39:Q39 H42:Q42">
-    <cfRule type="cellIs" dxfId="20" priority="21" operator="lessThanOrEqual">
-      <formula>3.4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H25:Q26">
-    <cfRule type="cellIs" dxfId="19" priority="9" operator="lessThanOrEqual">
-      <formula>3.4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H32:Q33">
-    <cfRule type="cellIs" dxfId="18" priority="8" operator="lessThanOrEqual">
-      <formula>3.4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H35:Q36">
-    <cfRule type="cellIs" dxfId="17" priority="7" operator="lessThanOrEqual">
-      <formula>3.4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H38:Q38">
-    <cfRule type="cellIs" dxfId="16" priority="6" operator="lessThanOrEqual">
-      <formula>3.4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H41:Q41">
-    <cfRule type="cellIs" dxfId="15" priority="3" operator="lessThanOrEqual">
-      <formula>3.4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
-      <x14:conditionalFormattings>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="17" id="{69DAD745-8B3F-426A-85FA-E4560827F22D}">
-            <x14:iconSet iconSet="3Arrows" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>-0.25</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>0.25</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="3Arrows" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Arrows" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>H11:P11 H7:Q7 H14:Q14 H21:Q21 H24:Q24 H27:Q27 H34:Q34 H40:Q40 H37:Q37 H43:Q43</xm:sqref>
-        </x14:conditionalFormatting>
-      </x14:conditionalFormattings>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5C06947-9AD3-4764-A00F-59E09793C545}">
   <sheetPr>
     <tabColor theme="8" tint="0.39997558519241921"/>
@@ -5894,40 +3149,40 @@
   <sheetData>
     <row r="1" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="2" spans="2:29" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="229" t="s">
+      <c r="B2" s="149" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="230"/>
-      <c r="D2" s="241" t="s">
+      <c r="C2" s="150"/>
+      <c r="D2" s="158" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="249" t="s">
+      <c r="E2" s="166" t="s">
         <v>55</v>
       </c>
-      <c r="F2" s="250"/>
-      <c r="G2" s="251"/>
-      <c r="H2" s="243" t="s">
+      <c r="F2" s="167"/>
+      <c r="G2" s="168"/>
+      <c r="H2" s="160" t="s">
         <v>56</v>
       </c>
-      <c r="I2" s="244"/>
-      <c r="J2" s="244"/>
-      <c r="K2" s="244"/>
-      <c r="L2" s="244"/>
-      <c r="M2" s="244"/>
-      <c r="N2" s="244"/>
-      <c r="O2" s="244"/>
-      <c r="P2" s="244"/>
-      <c r="Q2" s="245"/>
+      <c r="I2" s="161"/>
+      <c r="J2" s="161"/>
+      <c r="K2" s="161"/>
+      <c r="L2" s="161"/>
+      <c r="M2" s="161"/>
+      <c r="N2" s="161"/>
+      <c r="O2" s="161"/>
+      <c r="P2" s="161"/>
+      <c r="Q2" s="162"/>
     </row>
     <row r="3" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B3" s="231"/>
-      <c r="C3" s="232"/>
-      <c r="D3" s="242"/>
-      <c r="E3" s="246" t="s">
-        <v>97</v>
-      </c>
-      <c r="F3" s="247"/>
-      <c r="G3" s="248"/>
+      <c r="B3" s="151"/>
+      <c r="C3" s="152"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="163" t="s">
+        <v>96</v>
+      </c>
+      <c r="F3" s="164"/>
+      <c r="G3" s="165"/>
       <c r="H3" s="22"/>
       <c r="I3" s="21"/>
       <c r="J3" s="21"/>
@@ -5940,14 +3195,14 @@
       <c r="Q3" s="20"/>
     </row>
     <row r="4" spans="2:29" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B4" s="233"/>
-      <c r="C4" s="234"/>
-      <c r="D4" s="242"/>
+      <c r="B4" s="153"/>
+      <c r="C4" s="154"/>
+      <c r="D4" s="159"/>
       <c r="E4" s="85" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F4" s="90" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G4" s="86" t="s">
         <v>57</v>
@@ -5962,7 +3217,7 @@
         <v>60</v>
       </c>
       <c r="K4" s="24" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L4" s="24" t="s">
         <v>61</v>
@@ -5984,14 +3239,14 @@
       </c>
     </row>
     <row r="5" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B5" s="238" t="s">
-        <v>90</v>
-      </c>
-      <c r="C5" s="235" t="s">
-        <v>138</v>
+      <c r="B5" s="155" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" s="146" t="s">
+        <v>137</v>
       </c>
       <c r="D5" s="33" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E5" s="30"/>
       <c r="F5" s="30"/>
@@ -6037,14 +3292,14 @@
         <v>#REF!</v>
       </c>
       <c r="S5" s="63" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B6" s="239"/>
-      <c r="C6" s="236"/>
+      <c r="B6" s="156"/>
+      <c r="C6" s="147"/>
       <c r="D6" s="26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E6" s="27"/>
       <c r="F6" s="27"/>
@@ -6081,7 +3336,7 @@
       </c>
       <c r="R6" s="19"/>
       <c r="S6" s="11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="T6" s="19"/>
       <c r="U6" s="19"/>
@@ -6095,10 +3350,10 @@
       <c r="AC6" s="19"/>
     </row>
     <row r="7" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B7" s="239"/>
-      <c r="C7" s="237"/>
+      <c r="B7" s="156"/>
+      <c r="C7" s="148"/>
       <c r="D7" s="83" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E7" s="53"/>
       <c r="F7" s="53"/>
@@ -6147,17 +3402,17 @@
       <c r="AC7" s="19"/>
     </row>
     <row r="8" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B8" s="239"/>
+      <c r="B8" s="156"/>
       <c r="C8" s="36" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D8" s="57"/>
       <c r="E8" s="61" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F8" s="61"/>
       <c r="G8" s="62" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H8" s="42" t="e">
         <f>H5-H6</f>
@@ -6201,12 +3456,12 @@
       </c>
     </row>
     <row r="9" spans="2:29" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B9" s="239"/>
-      <c r="C9" s="235" t="s">
-        <v>102</v>
+      <c r="B9" s="156"/>
+      <c r="C9" s="146" t="s">
+        <v>101</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="30"/>
@@ -6253,43 +3508,43 @@
       </c>
     </row>
     <row r="10" spans="2:29" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B10" s="239"/>
-      <c r="C10" s="236"/>
+      <c r="B10" s="156"/>
+      <c r="C10" s="147"/>
       <c r="D10" s="26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E10" s="27"/>
       <c r="F10" s="27"/>
       <c r="G10" s="28"/>
       <c r="H10" s="84" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I10" s="84" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J10" s="84" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K10" s="84" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L10" s="84" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="M10" s="84" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N10" s="84" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O10" s="84" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P10" s="84" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Q10" s="84" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="R10" s="19"/>
       <c r="S10" s="19"/>
@@ -6305,10 +3560,10 @@
       <c r="AC10" s="19"/>
     </row>
     <row r="11" spans="2:29" ht="15.6" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B11" s="239"/>
-      <c r="C11" s="237"/>
+      <c r="B11" s="156"/>
+      <c r="C11" s="148"/>
       <c r="D11" s="34" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E11" s="53"/>
       <c r="F11" s="53"/>
@@ -6357,17 +3612,17 @@
       <c r="AC11" s="19"/>
     </row>
     <row r="12" spans="2:29" ht="15.6" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B12" s="239"/>
+      <c r="B12" s="156"/>
       <c r="C12" s="36" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D12" s="57"/>
       <c r="E12" s="61" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F12" s="61"/>
       <c r="G12" s="62" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H12" s="42" t="e">
         <f>H9-H10</f>
@@ -6411,12 +3666,12 @@
       </c>
     </row>
     <row r="13" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B13" s="239"/>
-      <c r="C13" s="235" t="s">
+      <c r="B13" s="156"/>
+      <c r="C13" s="146" t="s">
+        <v>142</v>
+      </c>
+      <c r="D13" s="33" t="s">
         <v>143</v>
-      </c>
-      <c r="D13" s="33" t="s">
-        <v>144</v>
       </c>
       <c r="E13" s="30"/>
       <c r="F13" s="30"/>
@@ -6463,10 +3718,10 @@
       </c>
     </row>
     <row r="14" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B14" s="239"/>
-      <c r="C14" s="236"/>
+      <c r="B14" s="156"/>
+      <c r="C14" s="147"/>
       <c r="D14" s="26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E14" s="27"/>
       <c r="F14" s="27"/>
@@ -6515,10 +3770,10 @@
       <c r="AC14" s="19"/>
     </row>
     <row r="15" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B15" s="239"/>
-      <c r="C15" s="237"/>
+      <c r="B15" s="156"/>
+      <c r="C15" s="148"/>
       <c r="D15" s="83" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E15" s="53"/>
       <c r="F15" s="53"/>
@@ -6567,17 +3822,17 @@
       <c r="AC15" s="19"/>
     </row>
     <row r="16" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B16" s="240"/>
+      <c r="B16" s="157"/>
       <c r="C16" s="32" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D16" s="55"/>
       <c r="E16" s="59" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F16" s="59"/>
       <c r="G16" s="60" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H16" s="51" t="e">
         <f>H13-H14</f>
@@ -6633,40 +3888,40 @@
       <c r="Q17" s="12"/>
     </row>
     <row r="18" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B18" s="229" t="s">
+      <c r="B18" s="149" t="s">
         <v>53</v>
       </c>
-      <c r="C18" s="230"/>
-      <c r="D18" s="241" t="s">
+      <c r="C18" s="150"/>
+      <c r="D18" s="158" t="s">
         <v>54</v>
       </c>
-      <c r="E18" s="249" t="s">
+      <c r="E18" s="166" t="s">
         <v>55</v>
       </c>
-      <c r="F18" s="250"/>
-      <c r="G18" s="251"/>
-      <c r="H18" s="255" t="s">
+      <c r="F18" s="167"/>
+      <c r="G18" s="168"/>
+      <c r="H18" s="172" t="s">
         <v>56</v>
       </c>
-      <c r="I18" s="256"/>
-      <c r="J18" s="256"/>
-      <c r="K18" s="256"/>
-      <c r="L18" s="256"/>
-      <c r="M18" s="256"/>
-      <c r="N18" s="256"/>
-      <c r="O18" s="256"/>
-      <c r="P18" s="256"/>
-      <c r="Q18" s="257"/>
+      <c r="I18" s="173"/>
+      <c r="J18" s="173"/>
+      <c r="K18" s="173"/>
+      <c r="L18" s="173"/>
+      <c r="M18" s="173"/>
+      <c r="N18" s="173"/>
+      <c r="O18" s="173"/>
+      <c r="P18" s="173"/>
+      <c r="Q18" s="174"/>
     </row>
     <row r="19" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B19" s="231"/>
-      <c r="C19" s="232"/>
-      <c r="D19" s="242"/>
-      <c r="E19" s="246" t="s">
-        <v>97</v>
-      </c>
-      <c r="F19" s="247"/>
-      <c r="G19" s="248"/>
+      <c r="B19" s="151"/>
+      <c r="C19" s="152"/>
+      <c r="D19" s="159"/>
+      <c r="E19" s="163" t="s">
+        <v>96</v>
+      </c>
+      <c r="F19" s="164"/>
+      <c r="G19" s="165"/>
       <c r="H19" s="67"/>
       <c r="I19" s="68"/>
       <c r="J19" s="68"/>
@@ -6679,14 +3934,14 @@
       <c r="Q19" s="69"/>
     </row>
     <row r="20" spans="2:28" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B20" s="233"/>
-      <c r="C20" s="234"/>
-      <c r="D20" s="242"/>
+      <c r="B20" s="153"/>
+      <c r="C20" s="154"/>
+      <c r="D20" s="159"/>
       <c r="E20" s="85" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F20" s="90" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G20" s="86" t="s">
         <v>57</v>
@@ -6701,7 +3956,7 @@
         <v>60</v>
       </c>
       <c r="K20" s="71" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="L20" s="71" t="s">
         <v>61</v>
@@ -6723,14 +3978,14 @@
       </c>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B21" s="238" t="s">
-        <v>101</v>
-      </c>
-      <c r="C21" s="235" t="s">
+      <c r="B21" s="155" t="s">
         <v>100</v>
       </c>
+      <c r="C21" s="146" t="s">
+        <v>99</v>
+      </c>
       <c r="D21" s="33" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E21" s="64" t="e">
         <f>#REF!</f>
@@ -6786,10 +4041,10 @@
       </c>
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B22" s="239"/>
-      <c r="C22" s="236"/>
+      <c r="B22" s="156"/>
+      <c r="C22" s="147"/>
       <c r="D22" s="26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E22" s="78">
         <v>93.333333333333329</v>
@@ -6841,10 +4096,10 @@
       <c r="AB22" s="19"/>
     </row>
     <row r="23" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B23" s="239"/>
-      <c r="C23" s="237"/>
+      <c r="B23" s="156"/>
+      <c r="C23" s="148"/>
       <c r="D23" s="83" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E23" s="79">
         <v>93.706896551724142</v>
@@ -6896,9 +4151,9 @@
       <c r="AB23" s="19"/>
     </row>
     <row r="24" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B24" s="239"/>
+      <c r="B24" s="156"/>
       <c r="C24" s="36" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D24" s="57"/>
       <c r="E24" s="42" t="e">
@@ -6952,12 +4207,12 @@
       </c>
     </row>
     <row r="25" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B25" s="239"/>
-      <c r="C25" s="235" t="s">
-        <v>99</v>
+      <c r="B25" s="156"/>
+      <c r="C25" s="146" t="s">
+        <v>98</v>
       </c>
       <c r="D25" s="33" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E25" s="64" t="e">
         <f>#REF!</f>
@@ -7013,10 +4268,10 @@
       </c>
     </row>
     <row r="26" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B26" s="239"/>
-      <c r="C26" s="236"/>
+      <c r="B26" s="156"/>
+      <c r="C26" s="147"/>
       <c r="D26" s="26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E26" s="78">
         <v>90.340501792114694</v>
@@ -7068,10 +4323,10 @@
       <c r="AB26" s="19"/>
     </row>
     <row r="27" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B27" s="239"/>
-      <c r="C27" s="237"/>
+      <c r="B27" s="156"/>
+      <c r="C27" s="148"/>
       <c r="D27" s="83" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E27" s="79">
         <v>88.879310344827587</v>
@@ -7123,9 +4378,9 @@
       <c r="AB27" s="19"/>
     </row>
     <row r="28" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B28" s="239"/>
+      <c r="B28" s="156"/>
       <c r="C28" s="36" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D28" s="57"/>
       <c r="E28" s="42" t="e">
@@ -7179,12 +4434,12 @@
       </c>
     </row>
     <row r="29" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B29" s="239"/>
-      <c r="C29" s="235" t="s">
-        <v>98</v>
+      <c r="B29" s="156"/>
+      <c r="C29" s="146" t="s">
+        <v>97</v>
       </c>
       <c r="D29" s="33" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E29" s="64" t="e">
         <f>#REF!</f>
@@ -7240,10 +4495,10 @@
       </c>
     </row>
     <row r="30" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B30" s="239"/>
-      <c r="C30" s="236"/>
+      <c r="B30" s="156"/>
+      <c r="C30" s="147"/>
       <c r="D30" s="26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E30" s="78">
         <v>94.086021505376351</v>
@@ -7295,10 +4550,10 @@
       <c r="AB30" s="19"/>
     </row>
     <row r="31" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B31" s="239"/>
-      <c r="C31" s="237"/>
+      <c r="B31" s="156"/>
+      <c r="C31" s="148"/>
       <c r="D31" s="83" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E31" s="79">
         <v>94.137931034482762</v>
@@ -7350,9 +4605,9 @@
       <c r="AB31" s="19"/>
     </row>
     <row r="32" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B32" s="240"/>
+      <c r="B32" s="157"/>
       <c r="C32" s="32" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D32" s="55"/>
       <c r="E32" s="51" t="e">
@@ -7418,40 +4673,40 @@
       <c r="Q33" s="12"/>
     </row>
     <row r="34" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B34" s="229" t="s">
+      <c r="B34" s="149" t="s">
         <v>53</v>
       </c>
-      <c r="C34" s="230"/>
-      <c r="D34" s="241" t="s">
+      <c r="C34" s="150"/>
+      <c r="D34" s="158" t="s">
         <v>54</v>
       </c>
-      <c r="E34" s="249" t="s">
+      <c r="E34" s="166" t="s">
         <v>55</v>
       </c>
-      <c r="F34" s="250"/>
-      <c r="G34" s="251"/>
-      <c r="H34" s="255" t="s">
+      <c r="F34" s="167"/>
+      <c r="G34" s="168"/>
+      <c r="H34" s="172" t="s">
         <v>56</v>
       </c>
-      <c r="I34" s="256"/>
-      <c r="J34" s="256"/>
-      <c r="K34" s="256"/>
-      <c r="L34" s="256"/>
-      <c r="M34" s="256"/>
-      <c r="N34" s="256"/>
-      <c r="O34" s="256"/>
-      <c r="P34" s="256"/>
-      <c r="Q34" s="257"/>
+      <c r="I34" s="173"/>
+      <c r="J34" s="173"/>
+      <c r="K34" s="173"/>
+      <c r="L34" s="173"/>
+      <c r="M34" s="173"/>
+      <c r="N34" s="173"/>
+      <c r="O34" s="173"/>
+      <c r="P34" s="173"/>
+      <c r="Q34" s="174"/>
     </row>
     <row r="35" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B35" s="231"/>
-      <c r="C35" s="232"/>
-      <c r="D35" s="242"/>
-      <c r="E35" s="246" t="s">
-        <v>97</v>
-      </c>
-      <c r="F35" s="247"/>
-      <c r="G35" s="248"/>
+      <c r="B35" s="151"/>
+      <c r="C35" s="152"/>
+      <c r="D35" s="159"/>
+      <c r="E35" s="163" t="s">
+        <v>96</v>
+      </c>
+      <c r="F35" s="164"/>
+      <c r="G35" s="165"/>
       <c r="H35" s="67"/>
       <c r="I35" s="68"/>
       <c r="J35" s="68"/>
@@ -7464,14 +4719,14 @@
       <c r="Q35" s="69"/>
     </row>
     <row r="36" spans="2:28" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B36" s="233"/>
-      <c r="C36" s="234"/>
-      <c r="D36" s="242"/>
+      <c r="B36" s="153"/>
+      <c r="C36" s="154"/>
+      <c r="D36" s="159"/>
       <c r="E36" s="85" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F36" s="90" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G36" s="86" t="s">
         <v>57</v>
@@ -7486,7 +4741,7 @@
         <v>60</v>
       </c>
       <c r="K36" s="71" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="L36" s="71" t="s">
         <v>61</v>
@@ -7508,14 +4763,14 @@
       </c>
     </row>
     <row r="37" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B37" s="238" t="s">
-        <v>96</v>
-      </c>
-      <c r="C37" s="235" t="s">
+      <c r="B37" s="155" t="s">
         <v>95</v>
       </c>
+      <c r="C37" s="146" t="s">
+        <v>94</v>
+      </c>
       <c r="D37" s="33" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E37" s="64" t="e">
         <f>#REF!</f>
@@ -7571,10 +4826,10 @@
       </c>
     </row>
     <row r="38" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B38" s="239"/>
-      <c r="C38" s="236"/>
+      <c r="B38" s="156"/>
+      <c r="C38" s="147"/>
       <c r="D38" s="26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E38" s="78">
         <v>90.663082437275989</v>
@@ -7626,10 +4881,10 @@
       <c r="AB38" s="19"/>
     </row>
     <row r="39" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B39" s="239"/>
-      <c r="C39" s="237"/>
+      <c r="B39" s="156"/>
+      <c r="C39" s="148"/>
       <c r="D39" s="83" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E39" s="79">
         <v>90.193965517241381</v>
@@ -7681,9 +4936,9 @@
       <c r="AB39" s="19"/>
     </row>
     <row r="40" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B40" s="239"/>
+      <c r="B40" s="156"/>
       <c r="C40" s="36" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D40" s="37"/>
       <c r="E40" s="39" t="e">
@@ -7737,12 +4992,12 @@
       </c>
     </row>
     <row r="41" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B41" s="239"/>
-      <c r="C41" s="235" t="s">
-        <v>80</v>
+      <c r="B41" s="156"/>
+      <c r="C41" s="146" t="s">
+        <v>79</v>
       </c>
       <c r="D41" s="33" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E41" s="64" t="e">
         <f>#REF!</f>
@@ -7798,10 +5053,10 @@
       </c>
     </row>
     <row r="42" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B42" s="239"/>
-      <c r="C42" s="236"/>
+      <c r="B42" s="156"/>
+      <c r="C42" s="147"/>
       <c r="D42" s="26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E42" s="78">
         <v>87.354838709677423</v>
@@ -7853,10 +5108,10 @@
       <c r="AB42" s="19"/>
     </row>
     <row r="43" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B43" s="239"/>
-      <c r="C43" s="237"/>
+      <c r="B43" s="156"/>
+      <c r="C43" s="148"/>
       <c r="D43" s="83" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E43" s="79">
         <v>87.482758620689651</v>
@@ -7908,9 +5163,9 @@
       <c r="AB43" s="19"/>
     </row>
     <row r="44" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B44" s="239"/>
+      <c r="B44" s="156"/>
       <c r="C44" s="36" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D44" s="37"/>
       <c r="E44" s="39" t="e">
@@ -7964,12 +5219,12 @@
       </c>
     </row>
     <row r="45" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B45" s="239"/>
-      <c r="C45" s="235" t="s">
-        <v>94</v>
+      <c r="B45" s="156"/>
+      <c r="C45" s="146" t="s">
+        <v>93</v>
       </c>
       <c r="D45" s="33" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E45" s="64" t="e">
         <f>#REF!</f>
@@ -8025,10 +5280,10 @@
       </c>
     </row>
     <row r="46" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B46" s="239"/>
-      <c r="C46" s="236"/>
+      <c r="B46" s="156"/>
+      <c r="C46" s="147"/>
       <c r="D46" s="26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E46" s="78">
         <v>78.709677419354833</v>
@@ -8080,10 +5335,10 @@
       <c r="AB46" s="19"/>
     </row>
     <row r="47" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B47" s="239"/>
-      <c r="C47" s="237"/>
+      <c r="B47" s="156"/>
+      <c r="C47" s="148"/>
       <c r="D47" s="83" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E47" s="79">
         <v>76.681034482758619</v>
@@ -8135,9 +5390,9 @@
       <c r="AB47" s="19"/>
     </row>
     <row r="48" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B48" s="239"/>
+      <c r="B48" s="156"/>
       <c r="C48" s="36" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D48" s="44"/>
       <c r="E48" s="39" t="e">
@@ -8191,14 +5446,14 @@
       </c>
     </row>
     <row r="49" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B49" s="239"/>
-      <c r="C49" s="235" t="s">
-        <v>93</v>
+      <c r="B49" s="156"/>
+      <c r="C49" s="146" t="s">
+        <v>92</v>
       </c>
       <c r="D49" s="33" t="s">
-        <v>144</v>
-      </c>
-      <c r="E49" s="252"/>
+        <v>143</v>
+      </c>
+      <c r="E49" s="169"/>
       <c r="F49" s="87"/>
       <c r="G49" s="31"/>
       <c r="H49" s="64" t="e">
@@ -8243,12 +5498,12 @@
       </c>
     </row>
     <row r="50" spans="2:28" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B50" s="239"/>
-      <c r="C50" s="236"/>
+      <c r="B50" s="156"/>
+      <c r="C50" s="147"/>
       <c r="D50" s="26" t="s">
-        <v>103</v>
-      </c>
-      <c r="E50" s="253"/>
+        <v>102</v>
+      </c>
+      <c r="E50" s="170"/>
       <c r="F50" s="88"/>
       <c r="G50" s="28"/>
       <c r="H50" s="73">
@@ -8294,12 +5549,12 @@
       <c r="AB50" s="19"/>
     </row>
     <row r="51" spans="2:28" ht="18.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B51" s="239"/>
-      <c r="C51" s="237"/>
+      <c r="B51" s="156"/>
+      <c r="C51" s="148"/>
       <c r="D51" s="83" t="s">
-        <v>71</v>
-      </c>
-      <c r="E51" s="254"/>
+        <v>70</v>
+      </c>
+      <c r="E51" s="171"/>
       <c r="F51" s="89"/>
       <c r="G51" s="54"/>
       <c r="H51" s="75">
@@ -8345,17 +5600,17 @@
       <c r="AB51" s="19"/>
     </row>
     <row r="52" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B52" s="240"/>
+      <c r="B52" s="157"/>
       <c r="C52" s="32" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D52" s="46"/>
       <c r="E52" s="47" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F52" s="92"/>
       <c r="G52" s="48" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H52" s="49" t="e">
         <f>H49-H50</f>
@@ -8400,22 +5655,22 @@
     </row>
     <row r="54" spans="2:28" x14ac:dyDescent="0.45">
       <c r="C54" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D54" s="17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="55" spans="2:28" x14ac:dyDescent="0.45">
       <c r="C55" s="18"/>
       <c r="D55" s="15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E55" s="13"/>
       <c r="F55" s="13"/>
       <c r="G55" s="14"/>
       <c r="H55" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I55" s="14"/>
       <c r="J55" s="14"/>
@@ -8430,13 +5685,13 @@
     </row>
     <row r="56" spans="2:28" x14ac:dyDescent="0.45">
       <c r="D56" s="15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E56" s="13"/>
       <c r="F56" s="13"/>
       <c r="G56" s="14"/>
       <c r="H56" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I56" s="14"/>
       <c r="J56" s="14"/>
@@ -8451,13 +5706,13 @@
     </row>
     <row r="57" spans="2:28" x14ac:dyDescent="0.45">
       <c r="D57" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E57" s="13"/>
       <c r="F57" s="13"/>
       <c r="G57" s="14"/>
       <c r="H57" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I57" s="14"/>
       <c r="L57" s="14"/>
@@ -8470,13 +5725,13 @@
     </row>
     <row r="58" spans="2:28" x14ac:dyDescent="0.45">
       <c r="D58" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E58" s="13"/>
       <c r="F58" s="13"/>
       <c r="G58" s="14"/>
       <c r="H58" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I58" s="14"/>
       <c r="J58" s="14"/>
@@ -8491,7 +5746,7 @@
     </row>
     <row r="59" spans="2:28" x14ac:dyDescent="0.45">
       <c r="D59" s="15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E59" s="13"/>
       <c r="F59" s="13"/>
@@ -8510,13 +5765,13 @@
     </row>
     <row r="60" spans="2:28" x14ac:dyDescent="0.45">
       <c r="D60" s="15" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E60" s="13"/>
       <c r="F60" s="13"/>
       <c r="G60" s="14"/>
       <c r="H60" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I60" s="14"/>
       <c r="J60" s="14"/>
@@ -8531,13 +5786,13 @@
     </row>
     <row r="61" spans="2:28" x14ac:dyDescent="0.45">
       <c r="D61" s="15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E61" s="13"/>
       <c r="F61" s="13"/>
       <c r="G61" s="14"/>
       <c r="H61" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I61" s="14"/>
       <c r="J61" s="14"/>
@@ -8552,13 +5807,13 @@
     </row>
     <row r="62" spans="2:28" x14ac:dyDescent="0.45">
       <c r="D62" s="16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E62" s="13"/>
       <c r="F62" s="13"/>
       <c r="G62" s="14"/>
       <c r="H62" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I62" s="14"/>
       <c r="J62" s="14"/>
@@ -8573,13 +5828,13 @@
     </row>
     <row r="63" spans="2:28" x14ac:dyDescent="0.45">
       <c r="D63" s="15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E63" s="13"/>
       <c r="F63" s="13"/>
       <c r="G63" s="14"/>
       <c r="H63" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I63" s="14"/>
       <c r="J63" s="14"/>
@@ -8594,13 +5849,13 @@
     </row>
     <row r="64" spans="2:28" x14ac:dyDescent="0.45">
       <c r="D64" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E64" s="13"/>
       <c r="F64" s="13"/>
       <c r="G64" s="14"/>
       <c r="H64" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I64" s="14"/>
       <c r="J64" s="14"/>
@@ -8615,13 +5870,13 @@
     </row>
     <row r="65" spans="3:18" x14ac:dyDescent="0.45">
       <c r="D65" s="15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E65" s="13"/>
       <c r="F65" s="13"/>
       <c r="G65" s="14"/>
       <c r="H65" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I65" s="14"/>
       <c r="J65" s="14"/>
@@ -8636,51 +5891,51 @@
     </row>
     <row r="67" spans="3:18" x14ac:dyDescent="0.45">
       <c r="C67" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="68" spans="3:18" x14ac:dyDescent="0.45">
       <c r="C68" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E68" s="13"/>
       <c r="F68" s="13"/>
     </row>
     <row r="69" spans="3:18" x14ac:dyDescent="0.45">
       <c r="C69" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E69" s="13"/>
       <c r="F69" s="13"/>
     </row>
     <row r="70" spans="3:18" x14ac:dyDescent="0.45">
       <c r="C70" s="11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E70" s="13"/>
       <c r="F70" s="13"/>
     </row>
     <row r="72" spans="3:18" x14ac:dyDescent="0.45">
       <c r="C72" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="73" spans="3:18" x14ac:dyDescent="0.45">
       <c r="C73" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="74" spans="3:18" x14ac:dyDescent="0.45">
       <c r="C74" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="78" spans="3:18" x14ac:dyDescent="0.45">
       <c r="C78" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="D78" s="11" t="s">
         <v>68</v>
-      </c>
-      <c r="D78" s="11" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="79" spans="3:18" x14ac:dyDescent="0.45">
@@ -8797,12 +6052,16 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="C41:C43"/>
-    <mergeCell ref="C45:C47"/>
-    <mergeCell ref="C49:C51"/>
-    <mergeCell ref="B34:C36"/>
-    <mergeCell ref="B37:B52"/>
-    <mergeCell ref="C37:C39"/>
+    <mergeCell ref="B2:C4"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="B18:C20"/>
+    <mergeCell ref="B5:B16"/>
+    <mergeCell ref="B21:B32"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="C25:C27"/>
     <mergeCell ref="D2:D4"/>
     <mergeCell ref="H2:Q2"/>
     <mergeCell ref="E3:G3"/>
@@ -8816,16 +6075,12 @@
     <mergeCell ref="D18:D20"/>
     <mergeCell ref="E18:G18"/>
     <mergeCell ref="E19:G19"/>
-    <mergeCell ref="B2:C4"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="B18:C20"/>
-    <mergeCell ref="B5:B16"/>
-    <mergeCell ref="B21:B32"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="C29:C31"/>
-    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="C41:C43"/>
+    <mergeCell ref="C45:C47"/>
+    <mergeCell ref="C49:C51"/>
+    <mergeCell ref="B34:C36"/>
+    <mergeCell ref="B37:B52"/>
+    <mergeCell ref="C37:C39"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="H5:Q7">
@@ -8933,7 +6188,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor theme="4" tint="0.39997558519241921"/>
@@ -8955,7 +6210,7 @@
         <v>46</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>47</v>
@@ -9020,7 +6275,7 @@
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.45">
       <c r="M3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:34" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -9038,7 +6293,7 @@
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="N4" s="3" t="s">
         <v>3</v>
@@ -9281,91 +6536,91 @@
         <v>43</v>
       </c>
       <c r="F8" t="s">
+        <v>103</v>
+      </c>
+      <c r="G8" t="s">
         <v>104</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>105</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>106</v>
       </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
         <v>107</v>
       </c>
-      <c r="J8" t="s">
+      <c r="K8" t="s">
         <v>108</v>
       </c>
-      <c r="K8" t="s">
+      <c r="L8" t="s">
         <v>109</v>
       </c>
-      <c r="L8" t="s">
+      <c r="M8" t="s">
         <v>110</v>
       </c>
-      <c r="M8" t="s">
+      <c r="N8" t="s">
+        <v>130</v>
+      </c>
+      <c r="O8" t="s">
         <v>111</v>
       </c>
-      <c r="N8" t="s">
+      <c r="P8" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>113</v>
+      </c>
+      <c r="R8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S8" t="s">
+        <v>115</v>
+      </c>
+      <c r="T8" t="s">
+        <v>116</v>
+      </c>
+      <c r="U8" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="V8" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="W8" t="s">
+        <v>119</v>
+      </c>
+      <c r="X8" t="s">
+        <v>120</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>121</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>122</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>123</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>124</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>125</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>126</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>127</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>128</v>
+      </c>
+      <c r="AG8" t="s">
         <v>131</v>
       </c>
-      <c r="O8" t="s">
-        <v>112</v>
-      </c>
-      <c r="P8" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>114</v>
-      </c>
-      <c r="R8" t="s">
-        <v>115</v>
-      </c>
-      <c r="S8" t="s">
-        <v>116</v>
-      </c>
-      <c r="T8" t="s">
-        <v>117</v>
-      </c>
-      <c r="U8" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="V8" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="W8" t="s">
-        <v>120</v>
-      </c>
-      <c r="X8" t="s">
-        <v>121</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>122</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>123</v>
-      </c>
-      <c r="AA8" t="s">
-        <v>124</v>
-      </c>
-      <c r="AB8" t="s">
-        <v>125</v>
-      </c>
-      <c r="AC8" t="s">
-        <v>126</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>127</v>
-      </c>
-      <c r="AE8" t="s">
-        <v>128</v>
-      </c>
-      <c r="AF8" t="s">
+      <c r="AH8" t="s">
         <v>129</v>
-      </c>
-      <c r="AG8" t="s">
-        <v>132</v>
-      </c>
-      <c r="AH8" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="9" spans="1:34" x14ac:dyDescent="0.45">

--- a/tool/track-aggregator/template/統合結果.xlsx
+++ b/tool/track-aggregator/template/統合結果.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ishid\Desktop\project_management\tool\track-aggregator\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0175F406-8941-4253-B71B-19EA2D2172E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F8AA7AC-382A-43E1-BB69-CEB66341AA7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="166">
   <si>
     <t>目的達成</t>
     <rPh sb="0" eb="2">
@@ -949,6 +949,10 @@
     <rPh sb="7" eb="9">
       <t>ジッシ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{データ取得}</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1761,7 +1765,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="175">
+  <cellXfs count="176">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2166,6 +2170,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="48" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2782,6 +2789,9 @@
         <v>162</v>
       </c>
       <c r="C2" s="130"/>
+      <c r="E2" s="135" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B3" s="131" t="s">
@@ -2875,47 +2885,47 @@
       </c>
     </row>
     <row r="2" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="135" t="s">
+      <c r="B2" s="136" t="s">
         <v>150</v>
       </c>
-      <c r="C2" s="136" t="s">
+      <c r="C2" s="137" t="s">
         <v>55</v>
       </c>
-      <c r="D2" s="136"/>
-      <c r="E2" s="136"/>
-      <c r="F2" s="140" t="s">
+      <c r="D2" s="137"/>
+      <c r="E2" s="137"/>
+      <c r="F2" s="141" t="s">
         <v>56</v>
       </c>
-      <c r="G2" s="141"/>
-      <c r="H2" s="141"/>
-      <c r="I2" s="141"/>
-      <c r="J2" s="141"/>
-      <c r="K2" s="141"/>
-      <c r="L2" s="141"/>
-      <c r="M2" s="141"/>
-      <c r="N2" s="141"/>
-      <c r="O2" s="142"/>
+      <c r="G2" s="142"/>
+      <c r="H2" s="142"/>
+      <c r="I2" s="142"/>
+      <c r="J2" s="142"/>
+      <c r="K2" s="142"/>
+      <c r="L2" s="142"/>
+      <c r="M2" s="142"/>
+      <c r="N2" s="142"/>
+      <c r="O2" s="143"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.45">
-      <c r="B3" s="135"/>
-      <c r="C3" s="136" t="s">
+      <c r="B3" s="136"/>
+      <c r="C3" s="137" t="s">
         <v>96</v>
       </c>
-      <c r="D3" s="136"/>
-      <c r="E3" s="136"/>
-      <c r="F3" s="143"/>
-      <c r="G3" s="144"/>
-      <c r="H3" s="144"/>
-      <c r="I3" s="144"/>
-      <c r="J3" s="144"/>
-      <c r="K3" s="144"/>
-      <c r="L3" s="144"/>
-      <c r="M3" s="144"/>
-      <c r="N3" s="144"/>
-      <c r="O3" s="145"/>
+      <c r="D3" s="137"/>
+      <c r="E3" s="137"/>
+      <c r="F3" s="144"/>
+      <c r="G3" s="145"/>
+      <c r="H3" s="145"/>
+      <c r="I3" s="145"/>
+      <c r="J3" s="145"/>
+      <c r="K3" s="145"/>
+      <c r="L3" s="145"/>
+      <c r="M3" s="145"/>
+      <c r="N3" s="145"/>
+      <c r="O3" s="146"/>
     </row>
     <row r="4" spans="1:27" ht="36" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B4" s="135"/>
+      <c r="B4" s="136"/>
       <c r="C4" s="97" t="s">
         <v>140</v>
       </c>
@@ -2976,7 +2986,7 @@
       <c r="Q5" s="101"/>
     </row>
     <row r="6" spans="1:27" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B6" s="137" t="s">
+      <c r="B6" s="138" t="s">
         <v>101</v>
       </c>
       <c r="C6" s="102"/>
@@ -2994,7 +3004,7 @@
       <c r="O6" s="104"/>
     </row>
     <row r="7" spans="1:27" ht="18.600000000000001" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B7" s="138"/>
+      <c r="B7" s="139"/>
       <c r="C7" s="105"/>
       <c r="D7" s="105"/>
       <c r="E7" s="106"/>
@@ -3022,7 +3032,7 @@
       <c r="AA7" s="108"/>
     </row>
     <row r="8" spans="1:27" ht="18.600000000000001" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B8" s="139"/>
+      <c r="B8" s="140"/>
       <c r="C8" s="109"/>
       <c r="D8" s="109"/>
       <c r="E8" s="110"/>
@@ -3149,40 +3159,40 @@
   <sheetData>
     <row r="1" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="2" spans="2:29" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="149" t="s">
+      <c r="B2" s="150" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="150"/>
-      <c r="D2" s="158" t="s">
+      <c r="C2" s="151"/>
+      <c r="D2" s="159" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="166" t="s">
+      <c r="E2" s="167" t="s">
         <v>55</v>
       </c>
-      <c r="F2" s="167"/>
-      <c r="G2" s="168"/>
-      <c r="H2" s="160" t="s">
+      <c r="F2" s="168"/>
+      <c r="G2" s="169"/>
+      <c r="H2" s="161" t="s">
         <v>56</v>
       </c>
-      <c r="I2" s="161"/>
-      <c r="J2" s="161"/>
-      <c r="K2" s="161"/>
-      <c r="L2" s="161"/>
-      <c r="M2" s="161"/>
-      <c r="N2" s="161"/>
-      <c r="O2" s="161"/>
-      <c r="P2" s="161"/>
-      <c r="Q2" s="162"/>
+      <c r="I2" s="162"/>
+      <c r="J2" s="162"/>
+      <c r="K2" s="162"/>
+      <c r="L2" s="162"/>
+      <c r="M2" s="162"/>
+      <c r="N2" s="162"/>
+      <c r="O2" s="162"/>
+      <c r="P2" s="162"/>
+      <c r="Q2" s="163"/>
     </row>
     <row r="3" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B3" s="151"/>
-      <c r="C3" s="152"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="163" t="s">
+      <c r="B3" s="152"/>
+      <c r="C3" s="153"/>
+      <c r="D3" s="160"/>
+      <c r="E3" s="164" t="s">
         <v>96</v>
       </c>
-      <c r="F3" s="164"/>
-      <c r="G3" s="165"/>
+      <c r="F3" s="165"/>
+      <c r="G3" s="166"/>
       <c r="H3" s="22"/>
       <c r="I3" s="21"/>
       <c r="J3" s="21"/>
@@ -3195,9 +3205,9 @@
       <c r="Q3" s="20"/>
     </row>
     <row r="4" spans="2:29" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B4" s="153"/>
-      <c r="C4" s="154"/>
-      <c r="D4" s="159"/>
+      <c r="B4" s="154"/>
+      <c r="C4" s="155"/>
+      <c r="D4" s="160"/>
       <c r="E4" s="85" t="s">
         <v>140</v>
       </c>
@@ -3239,10 +3249,10 @@
       </c>
     </row>
     <row r="5" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B5" s="155" t="s">
+      <c r="B5" s="156" t="s">
         <v>89</v>
       </c>
-      <c r="C5" s="146" t="s">
+      <c r="C5" s="147" t="s">
         <v>137</v>
       </c>
       <c r="D5" s="33" t="s">
@@ -3296,8 +3306,8 @@
       </c>
     </row>
     <row r="6" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B6" s="156"/>
-      <c r="C6" s="147"/>
+      <c r="B6" s="157"/>
+      <c r="C6" s="148"/>
       <c r="D6" s="26" t="s">
         <v>102</v>
       </c>
@@ -3350,8 +3360,8 @@
       <c r="AC6" s="19"/>
     </row>
     <row r="7" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B7" s="156"/>
-      <c r="C7" s="148"/>
+      <c r="B7" s="157"/>
+      <c r="C7" s="149"/>
       <c r="D7" s="83" t="s">
         <v>70</v>
       </c>
@@ -3402,7 +3412,7 @@
       <c r="AC7" s="19"/>
     </row>
     <row r="8" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B8" s="156"/>
+      <c r="B8" s="157"/>
       <c r="C8" s="36" t="s">
         <v>91</v>
       </c>
@@ -3456,8 +3466,8 @@
       </c>
     </row>
     <row r="9" spans="2:29" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B9" s="156"/>
-      <c r="C9" s="146" t="s">
+      <c r="B9" s="157"/>
+      <c r="C9" s="147" t="s">
         <v>101</v>
       </c>
       <c r="D9" s="33" t="s">
@@ -3508,8 +3518,8 @@
       </c>
     </row>
     <row r="10" spans="2:29" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B10" s="156"/>
-      <c r="C10" s="147"/>
+      <c r="B10" s="157"/>
+      <c r="C10" s="148"/>
       <c r="D10" s="26" t="s">
         <v>102</v>
       </c>
@@ -3560,8 +3570,8 @@
       <c r="AC10" s="19"/>
     </row>
     <row r="11" spans="2:29" ht="15.6" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B11" s="156"/>
-      <c r="C11" s="148"/>
+      <c r="B11" s="157"/>
+      <c r="C11" s="149"/>
       <c r="D11" s="34" t="s">
         <v>70</v>
       </c>
@@ -3612,7 +3622,7 @@
       <c r="AC11" s="19"/>
     </row>
     <row r="12" spans="2:29" ht="15.6" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B12" s="156"/>
+      <c r="B12" s="157"/>
       <c r="C12" s="36" t="s">
         <v>91</v>
       </c>
@@ -3666,8 +3676,8 @@
       </c>
     </row>
     <row r="13" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B13" s="156"/>
-      <c r="C13" s="146" t="s">
+      <c r="B13" s="157"/>
+      <c r="C13" s="147" t="s">
         <v>142</v>
       </c>
       <c r="D13" s="33" t="s">
@@ -3718,8 +3728,8 @@
       </c>
     </row>
     <row r="14" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B14" s="156"/>
-      <c r="C14" s="147"/>
+      <c r="B14" s="157"/>
+      <c r="C14" s="148"/>
       <c r="D14" s="26" t="s">
         <v>102</v>
       </c>
@@ -3770,8 +3780,8 @@
       <c r="AC14" s="19"/>
     </row>
     <row r="15" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B15" s="156"/>
-      <c r="C15" s="148"/>
+      <c r="B15" s="157"/>
+      <c r="C15" s="149"/>
       <c r="D15" s="83" t="s">
         <v>70</v>
       </c>
@@ -3822,7 +3832,7 @@
       <c r="AC15" s="19"/>
     </row>
     <row r="16" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B16" s="157"/>
+      <c r="B16" s="158"/>
       <c r="C16" s="32" t="s">
         <v>91</v>
       </c>
@@ -3888,40 +3898,40 @@
       <c r="Q17" s="12"/>
     </row>
     <row r="18" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B18" s="149" t="s">
+      <c r="B18" s="150" t="s">
         <v>53</v>
       </c>
-      <c r="C18" s="150"/>
-      <c r="D18" s="158" t="s">
+      <c r="C18" s="151"/>
+      <c r="D18" s="159" t="s">
         <v>54</v>
       </c>
-      <c r="E18" s="166" t="s">
+      <c r="E18" s="167" t="s">
         <v>55</v>
       </c>
-      <c r="F18" s="167"/>
-      <c r="G18" s="168"/>
-      <c r="H18" s="172" t="s">
+      <c r="F18" s="168"/>
+      <c r="G18" s="169"/>
+      <c r="H18" s="173" t="s">
         <v>56</v>
       </c>
-      <c r="I18" s="173"/>
-      <c r="J18" s="173"/>
-      <c r="K18" s="173"/>
-      <c r="L18" s="173"/>
-      <c r="M18" s="173"/>
-      <c r="N18" s="173"/>
-      <c r="O18" s="173"/>
-      <c r="P18" s="173"/>
-      <c r="Q18" s="174"/>
+      <c r="I18" s="174"/>
+      <c r="J18" s="174"/>
+      <c r="K18" s="174"/>
+      <c r="L18" s="174"/>
+      <c r="M18" s="174"/>
+      <c r="N18" s="174"/>
+      <c r="O18" s="174"/>
+      <c r="P18" s="174"/>
+      <c r="Q18" s="175"/>
     </row>
     <row r="19" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B19" s="151"/>
-      <c r="C19" s="152"/>
-      <c r="D19" s="159"/>
-      <c r="E19" s="163" t="s">
+      <c r="B19" s="152"/>
+      <c r="C19" s="153"/>
+      <c r="D19" s="160"/>
+      <c r="E19" s="164" t="s">
         <v>96</v>
       </c>
-      <c r="F19" s="164"/>
-      <c r="G19" s="165"/>
+      <c r="F19" s="165"/>
+      <c r="G19" s="166"/>
       <c r="H19" s="67"/>
       <c r="I19" s="68"/>
       <c r="J19" s="68"/>
@@ -3934,9 +3944,9 @@
       <c r="Q19" s="69"/>
     </row>
     <row r="20" spans="2:28" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B20" s="153"/>
-      <c r="C20" s="154"/>
-      <c r="D20" s="159"/>
+      <c r="B20" s="154"/>
+      <c r="C20" s="155"/>
+      <c r="D20" s="160"/>
       <c r="E20" s="85" t="s">
         <v>140</v>
       </c>
@@ -3978,10 +3988,10 @@
       </c>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B21" s="155" t="s">
+      <c r="B21" s="156" t="s">
         <v>100</v>
       </c>
-      <c r="C21" s="146" t="s">
+      <c r="C21" s="147" t="s">
         <v>99</v>
       </c>
       <c r="D21" s="33" t="s">
@@ -4041,8 +4051,8 @@
       </c>
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B22" s="156"/>
-      <c r="C22" s="147"/>
+      <c r="B22" s="157"/>
+      <c r="C22" s="148"/>
       <c r="D22" s="26" t="s">
         <v>102</v>
       </c>
@@ -4096,8 +4106,8 @@
       <c r="AB22" s="19"/>
     </row>
     <row r="23" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B23" s="156"/>
-      <c r="C23" s="148"/>
+      <c r="B23" s="157"/>
+      <c r="C23" s="149"/>
       <c r="D23" s="83" t="s">
         <v>70</v>
       </c>
@@ -4151,7 +4161,7 @@
       <c r="AB23" s="19"/>
     </row>
     <row r="24" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B24" s="156"/>
+      <c r="B24" s="157"/>
       <c r="C24" s="36" t="s">
         <v>91</v>
       </c>
@@ -4207,8 +4217,8 @@
       </c>
     </row>
     <row r="25" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B25" s="156"/>
-      <c r="C25" s="146" t="s">
+      <c r="B25" s="157"/>
+      <c r="C25" s="147" t="s">
         <v>98</v>
       </c>
       <c r="D25" s="33" t="s">
@@ -4268,8 +4278,8 @@
       </c>
     </row>
     <row r="26" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B26" s="156"/>
-      <c r="C26" s="147"/>
+      <c r="B26" s="157"/>
+      <c r="C26" s="148"/>
       <c r="D26" s="26" t="s">
         <v>102</v>
       </c>
@@ -4323,8 +4333,8 @@
       <c r="AB26" s="19"/>
     </row>
     <row r="27" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B27" s="156"/>
-      <c r="C27" s="148"/>
+      <c r="B27" s="157"/>
+      <c r="C27" s="149"/>
       <c r="D27" s="83" t="s">
         <v>70</v>
       </c>
@@ -4378,7 +4388,7 @@
       <c r="AB27" s="19"/>
     </row>
     <row r="28" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B28" s="156"/>
+      <c r="B28" s="157"/>
       <c r="C28" s="36" t="s">
         <v>91</v>
       </c>
@@ -4434,8 +4444,8 @@
       </c>
     </row>
     <row r="29" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B29" s="156"/>
-      <c r="C29" s="146" t="s">
+      <c r="B29" s="157"/>
+      <c r="C29" s="147" t="s">
         <v>97</v>
       </c>
       <c r="D29" s="33" t="s">
@@ -4495,8 +4505,8 @@
       </c>
     </row>
     <row r="30" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B30" s="156"/>
-      <c r="C30" s="147"/>
+      <c r="B30" s="157"/>
+      <c r="C30" s="148"/>
       <c r="D30" s="26" t="s">
         <v>102</v>
       </c>
@@ -4550,8 +4560,8 @@
       <c r="AB30" s="19"/>
     </row>
     <row r="31" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B31" s="156"/>
-      <c r="C31" s="148"/>
+      <c r="B31" s="157"/>
+      <c r="C31" s="149"/>
       <c r="D31" s="83" t="s">
         <v>70</v>
       </c>
@@ -4605,7 +4615,7 @@
       <c r="AB31" s="19"/>
     </row>
     <row r="32" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B32" s="157"/>
+      <c r="B32" s="158"/>
       <c r="C32" s="32" t="s">
         <v>91</v>
       </c>
@@ -4673,40 +4683,40 @@
       <c r="Q33" s="12"/>
     </row>
     <row r="34" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B34" s="149" t="s">
+      <c r="B34" s="150" t="s">
         <v>53</v>
       </c>
-      <c r="C34" s="150"/>
-      <c r="D34" s="158" t="s">
+      <c r="C34" s="151"/>
+      <c r="D34" s="159" t="s">
         <v>54</v>
       </c>
-      <c r="E34" s="166" t="s">
+      <c r="E34" s="167" t="s">
         <v>55</v>
       </c>
-      <c r="F34" s="167"/>
-      <c r="G34" s="168"/>
-      <c r="H34" s="172" t="s">
+      <c r="F34" s="168"/>
+      <c r="G34" s="169"/>
+      <c r="H34" s="173" t="s">
         <v>56</v>
       </c>
-      <c r="I34" s="173"/>
-      <c r="J34" s="173"/>
-      <c r="K34" s="173"/>
-      <c r="L34" s="173"/>
-      <c r="M34" s="173"/>
-      <c r="N34" s="173"/>
-      <c r="O34" s="173"/>
-      <c r="P34" s="173"/>
-      <c r="Q34" s="174"/>
+      <c r="I34" s="174"/>
+      <c r="J34" s="174"/>
+      <c r="K34" s="174"/>
+      <c r="L34" s="174"/>
+      <c r="M34" s="174"/>
+      <c r="N34" s="174"/>
+      <c r="O34" s="174"/>
+      <c r="P34" s="174"/>
+      <c r="Q34" s="175"/>
     </row>
     <row r="35" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B35" s="151"/>
-      <c r="C35" s="152"/>
-      <c r="D35" s="159"/>
-      <c r="E35" s="163" t="s">
+      <c r="B35" s="152"/>
+      <c r="C35" s="153"/>
+      <c r="D35" s="160"/>
+      <c r="E35" s="164" t="s">
         <v>96</v>
       </c>
-      <c r="F35" s="164"/>
-      <c r="G35" s="165"/>
+      <c r="F35" s="165"/>
+      <c r="G35" s="166"/>
       <c r="H35" s="67"/>
       <c r="I35" s="68"/>
       <c r="J35" s="68"/>
@@ -4719,9 +4729,9 @@
       <c r="Q35" s="69"/>
     </row>
     <row r="36" spans="2:28" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B36" s="153"/>
-      <c r="C36" s="154"/>
-      <c r="D36" s="159"/>
+      <c r="B36" s="154"/>
+      <c r="C36" s="155"/>
+      <c r="D36" s="160"/>
       <c r="E36" s="85" t="s">
         <v>140</v>
       </c>
@@ -4763,10 +4773,10 @@
       </c>
     </row>
     <row r="37" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B37" s="155" t="s">
+      <c r="B37" s="156" t="s">
         <v>95</v>
       </c>
-      <c r="C37" s="146" t="s">
+      <c r="C37" s="147" t="s">
         <v>94</v>
       </c>
       <c r="D37" s="33" t="s">
@@ -4826,8 +4836,8 @@
       </c>
     </row>
     <row r="38" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B38" s="156"/>
-      <c r="C38" s="147"/>
+      <c r="B38" s="157"/>
+      <c r="C38" s="148"/>
       <c r="D38" s="26" t="s">
         <v>102</v>
       </c>
@@ -4881,8 +4891,8 @@
       <c r="AB38" s="19"/>
     </row>
     <row r="39" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B39" s="156"/>
-      <c r="C39" s="148"/>
+      <c r="B39" s="157"/>
+      <c r="C39" s="149"/>
       <c r="D39" s="83" t="s">
         <v>70</v>
       </c>
@@ -4936,7 +4946,7 @@
       <c r="AB39" s="19"/>
     </row>
     <row r="40" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B40" s="156"/>
+      <c r="B40" s="157"/>
       <c r="C40" s="36" t="s">
         <v>91</v>
       </c>
@@ -4992,8 +5002,8 @@
       </c>
     </row>
     <row r="41" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B41" s="156"/>
-      <c r="C41" s="146" t="s">
+      <c r="B41" s="157"/>
+      <c r="C41" s="147" t="s">
         <v>79</v>
       </c>
       <c r="D41" s="33" t="s">
@@ -5053,8 +5063,8 @@
       </c>
     </row>
     <row r="42" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B42" s="156"/>
-      <c r="C42" s="147"/>
+      <c r="B42" s="157"/>
+      <c r="C42" s="148"/>
       <c r="D42" s="26" t="s">
         <v>102</v>
       </c>
@@ -5108,8 +5118,8 @@
       <c r="AB42" s="19"/>
     </row>
     <row r="43" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B43" s="156"/>
-      <c r="C43" s="148"/>
+      <c r="B43" s="157"/>
+      <c r="C43" s="149"/>
       <c r="D43" s="83" t="s">
         <v>70</v>
       </c>
@@ -5163,7 +5173,7 @@
       <c r="AB43" s="19"/>
     </row>
     <row r="44" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B44" s="156"/>
+      <c r="B44" s="157"/>
       <c r="C44" s="36" t="s">
         <v>91</v>
       </c>
@@ -5219,8 +5229,8 @@
       </c>
     </row>
     <row r="45" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B45" s="156"/>
-      <c r="C45" s="146" t="s">
+      <c r="B45" s="157"/>
+      <c r="C45" s="147" t="s">
         <v>93</v>
       </c>
       <c r="D45" s="33" t="s">
@@ -5280,8 +5290,8 @@
       </c>
     </row>
     <row r="46" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B46" s="156"/>
-      <c r="C46" s="147"/>
+      <c r="B46" s="157"/>
+      <c r="C46" s="148"/>
       <c r="D46" s="26" t="s">
         <v>102</v>
       </c>
@@ -5335,8 +5345,8 @@
       <c r="AB46" s="19"/>
     </row>
     <row r="47" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B47" s="156"/>
-      <c r="C47" s="148"/>
+      <c r="B47" s="157"/>
+      <c r="C47" s="149"/>
       <c r="D47" s="83" t="s">
         <v>70</v>
       </c>
@@ -5390,7 +5400,7 @@
       <c r="AB47" s="19"/>
     </row>
     <row r="48" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B48" s="156"/>
+      <c r="B48" s="157"/>
       <c r="C48" s="36" t="s">
         <v>91</v>
       </c>
@@ -5446,14 +5456,14 @@
       </c>
     </row>
     <row r="49" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B49" s="156"/>
-      <c r="C49" s="146" t="s">
+      <c r="B49" s="157"/>
+      <c r="C49" s="147" t="s">
         <v>92</v>
       </c>
       <c r="D49" s="33" t="s">
         <v>143</v>
       </c>
-      <c r="E49" s="169"/>
+      <c r="E49" s="170"/>
       <c r="F49" s="87"/>
       <c r="G49" s="31"/>
       <c r="H49" s="64" t="e">
@@ -5498,12 +5508,12 @@
       </c>
     </row>
     <row r="50" spans="2:28" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B50" s="156"/>
-      <c r="C50" s="147"/>
+      <c r="B50" s="157"/>
+      <c r="C50" s="148"/>
       <c r="D50" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="E50" s="170"/>
+      <c r="E50" s="171"/>
       <c r="F50" s="88"/>
       <c r="G50" s="28"/>
       <c r="H50" s="73">
@@ -5549,12 +5559,12 @@
       <c r="AB50" s="19"/>
     </row>
     <row r="51" spans="2:28" ht="18.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B51" s="156"/>
-      <c r="C51" s="148"/>
+      <c r="B51" s="157"/>
+      <c r="C51" s="149"/>
       <c r="D51" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="E51" s="171"/>
+      <c r="E51" s="172"/>
       <c r="F51" s="89"/>
       <c r="G51" s="54"/>
       <c r="H51" s="75">
@@ -5600,7 +5610,7 @@
       <c r="AB51" s="19"/>
     </row>
     <row r="52" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B52" s="157"/>
+      <c r="B52" s="158"/>
       <c r="C52" s="32" t="s">
         <v>91</v>
       </c>

--- a/tool/track-aggregator/template/統合結果.xlsx
+++ b/tool/track-aggregator/template/統合結果.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ishid\Desktop\project_management\tool\track-aggregator\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F8AA7AC-382A-43E1-BB69-CEB66341AA7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9433D5CD-1DD7-465B-A431-EF6C16953CDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="165">
   <si>
     <t>目的達成</t>
     <rPh sb="0" eb="2">
@@ -949,10 +949,6 @@
     <rPh sb="7" eb="9">
       <t>ジッシ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>{データ取得}</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1765,7 +1761,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="176">
+  <cellXfs count="175">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2171,9 +2167,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="48" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2207,6 +2200,24 @@
     <xf numFmtId="0" fontId="10" fillId="8" borderId="48" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2215,24 +2226,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
@@ -2789,9 +2782,6 @@
         <v>162</v>
       </c>
       <c r="C2" s="130"/>
-      <c r="E2" s="135" t="s">
-        <v>165</v>
-      </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B3" s="131" t="s">
@@ -2885,47 +2875,47 @@
       </c>
     </row>
     <row r="2" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="136" t="s">
+      <c r="B2" s="135" t="s">
         <v>150</v>
       </c>
-      <c r="C2" s="137" t="s">
+      <c r="C2" s="136" t="s">
         <v>55</v>
       </c>
-      <c r="D2" s="137"/>
-      <c r="E2" s="137"/>
-      <c r="F2" s="141" t="s">
+      <c r="D2" s="136"/>
+      <c r="E2" s="136"/>
+      <c r="F2" s="140" t="s">
         <v>56</v>
       </c>
-      <c r="G2" s="142"/>
-      <c r="H2" s="142"/>
-      <c r="I2" s="142"/>
-      <c r="J2" s="142"/>
-      <c r="K2" s="142"/>
-      <c r="L2" s="142"/>
-      <c r="M2" s="142"/>
-      <c r="N2" s="142"/>
-      <c r="O2" s="143"/>
+      <c r="G2" s="141"/>
+      <c r="H2" s="141"/>
+      <c r="I2" s="141"/>
+      <c r="J2" s="141"/>
+      <c r="K2" s="141"/>
+      <c r="L2" s="141"/>
+      <c r="M2" s="141"/>
+      <c r="N2" s="141"/>
+      <c r="O2" s="142"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.45">
-      <c r="B3" s="136"/>
-      <c r="C3" s="137" t="s">
+      <c r="B3" s="135"/>
+      <c r="C3" s="136" t="s">
         <v>96</v>
       </c>
-      <c r="D3" s="137"/>
-      <c r="E3" s="137"/>
-      <c r="F3" s="144"/>
-      <c r="G3" s="145"/>
-      <c r="H3" s="145"/>
-      <c r="I3" s="145"/>
-      <c r="J3" s="145"/>
-      <c r="K3" s="145"/>
-      <c r="L3" s="145"/>
-      <c r="M3" s="145"/>
-      <c r="N3" s="145"/>
-      <c r="O3" s="146"/>
+      <c r="D3" s="136"/>
+      <c r="E3" s="136"/>
+      <c r="F3" s="143"/>
+      <c r="G3" s="144"/>
+      <c r="H3" s="144"/>
+      <c r="I3" s="144"/>
+      <c r="J3" s="144"/>
+      <c r="K3" s="144"/>
+      <c r="L3" s="144"/>
+      <c r="M3" s="144"/>
+      <c r="N3" s="144"/>
+      <c r="O3" s="145"/>
     </row>
     <row r="4" spans="1:27" ht="36" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B4" s="136"/>
+      <c r="B4" s="135"/>
       <c r="C4" s="97" t="s">
         <v>140</v>
       </c>
@@ -2986,7 +2976,7 @@
       <c r="Q5" s="101"/>
     </row>
     <row r="6" spans="1:27" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B6" s="138" t="s">
+      <c r="B6" s="137" t="s">
         <v>101</v>
       </c>
       <c r="C6" s="102"/>
@@ -3004,7 +2994,7 @@
       <c r="O6" s="104"/>
     </row>
     <row r="7" spans="1:27" ht="18.600000000000001" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B7" s="139"/>
+      <c r="B7" s="138"/>
       <c r="C7" s="105"/>
       <c r="D7" s="105"/>
       <c r="E7" s="106"/>
@@ -3032,7 +3022,7 @@
       <c r="AA7" s="108"/>
     </row>
     <row r="8" spans="1:27" ht="18.600000000000001" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B8" s="140"/>
+      <c r="B8" s="139"/>
       <c r="C8" s="109"/>
       <c r="D8" s="109"/>
       <c r="E8" s="110"/>
@@ -3159,40 +3149,40 @@
   <sheetData>
     <row r="1" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="2" spans="2:29" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="150" t="s">
+      <c r="B2" s="146" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="151"/>
-      <c r="D2" s="159" t="s">
+      <c r="C2" s="147"/>
+      <c r="D2" s="158" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="167" t="s">
+      <c r="E2" s="166" t="s">
         <v>55</v>
       </c>
-      <c r="F2" s="168"/>
-      <c r="G2" s="169"/>
-      <c r="H2" s="161" t="s">
+      <c r="F2" s="167"/>
+      <c r="G2" s="168"/>
+      <c r="H2" s="160" t="s">
         <v>56</v>
       </c>
-      <c r="I2" s="162"/>
-      <c r="J2" s="162"/>
-      <c r="K2" s="162"/>
-      <c r="L2" s="162"/>
-      <c r="M2" s="162"/>
-      <c r="N2" s="162"/>
-      <c r="O2" s="162"/>
-      <c r="P2" s="162"/>
-      <c r="Q2" s="163"/>
+      <c r="I2" s="161"/>
+      <c r="J2" s="161"/>
+      <c r="K2" s="161"/>
+      <c r="L2" s="161"/>
+      <c r="M2" s="161"/>
+      <c r="N2" s="161"/>
+      <c r="O2" s="161"/>
+      <c r="P2" s="161"/>
+      <c r="Q2" s="162"/>
     </row>
     <row r="3" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B3" s="152"/>
-      <c r="C3" s="153"/>
-      <c r="D3" s="160"/>
-      <c r="E3" s="164" t="s">
+      <c r="B3" s="148"/>
+      <c r="C3" s="149"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="163" t="s">
         <v>96</v>
       </c>
-      <c r="F3" s="165"/>
-      <c r="G3" s="166"/>
+      <c r="F3" s="164"/>
+      <c r="G3" s="165"/>
       <c r="H3" s="22"/>
       <c r="I3" s="21"/>
       <c r="J3" s="21"/>
@@ -3205,9 +3195,9 @@
       <c r="Q3" s="20"/>
     </row>
     <row r="4" spans="2:29" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B4" s="154"/>
-      <c r="C4" s="155"/>
-      <c r="D4" s="160"/>
+      <c r="B4" s="150"/>
+      <c r="C4" s="151"/>
+      <c r="D4" s="159"/>
       <c r="E4" s="85" t="s">
         <v>140</v>
       </c>
@@ -3249,10 +3239,10 @@
       </c>
     </row>
     <row r="5" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B5" s="156" t="s">
+      <c r="B5" s="155" t="s">
         <v>89</v>
       </c>
-      <c r="C5" s="147" t="s">
+      <c r="C5" s="152" t="s">
         <v>137</v>
       </c>
       <c r="D5" s="33" t="s">
@@ -3306,8 +3296,8 @@
       </c>
     </row>
     <row r="6" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B6" s="157"/>
-      <c r="C6" s="148"/>
+      <c r="B6" s="156"/>
+      <c r="C6" s="153"/>
       <c r="D6" s="26" t="s">
         <v>102</v>
       </c>
@@ -3360,8 +3350,8 @@
       <c r="AC6" s="19"/>
     </row>
     <row r="7" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B7" s="157"/>
-      <c r="C7" s="149"/>
+      <c r="B7" s="156"/>
+      <c r="C7" s="154"/>
       <c r="D7" s="83" t="s">
         <v>70</v>
       </c>
@@ -3412,7 +3402,7 @@
       <c r="AC7" s="19"/>
     </row>
     <row r="8" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B8" s="157"/>
+      <c r="B8" s="156"/>
       <c r="C8" s="36" t="s">
         <v>91</v>
       </c>
@@ -3466,8 +3456,8 @@
       </c>
     </row>
     <row r="9" spans="2:29" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B9" s="157"/>
-      <c r="C9" s="147" t="s">
+      <c r="B9" s="156"/>
+      <c r="C9" s="152" t="s">
         <v>101</v>
       </c>
       <c r="D9" s="33" t="s">
@@ -3518,8 +3508,8 @@
       </c>
     </row>
     <row r="10" spans="2:29" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B10" s="157"/>
-      <c r="C10" s="148"/>
+      <c r="B10" s="156"/>
+      <c r="C10" s="153"/>
       <c r="D10" s="26" t="s">
         <v>102</v>
       </c>
@@ -3570,8 +3560,8 @@
       <c r="AC10" s="19"/>
     </row>
     <row r="11" spans="2:29" ht="15.6" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B11" s="157"/>
-      <c r="C11" s="149"/>
+      <c r="B11" s="156"/>
+      <c r="C11" s="154"/>
       <c r="D11" s="34" t="s">
         <v>70</v>
       </c>
@@ -3622,7 +3612,7 @@
       <c r="AC11" s="19"/>
     </row>
     <row r="12" spans="2:29" ht="15.6" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B12" s="157"/>
+      <c r="B12" s="156"/>
       <c r="C12" s="36" t="s">
         <v>91</v>
       </c>
@@ -3676,8 +3666,8 @@
       </c>
     </row>
     <row r="13" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B13" s="157"/>
-      <c r="C13" s="147" t="s">
+      <c r="B13" s="156"/>
+      <c r="C13" s="152" t="s">
         <v>142</v>
       </c>
       <c r="D13" s="33" t="s">
@@ -3728,8 +3718,8 @@
       </c>
     </row>
     <row r="14" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B14" s="157"/>
-      <c r="C14" s="148"/>
+      <c r="B14" s="156"/>
+      <c r="C14" s="153"/>
       <c r="D14" s="26" t="s">
         <v>102</v>
       </c>
@@ -3780,8 +3770,8 @@
       <c r="AC14" s="19"/>
     </row>
     <row r="15" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B15" s="157"/>
-      <c r="C15" s="149"/>
+      <c r="B15" s="156"/>
+      <c r="C15" s="154"/>
       <c r="D15" s="83" t="s">
         <v>70</v>
       </c>
@@ -3832,7 +3822,7 @@
       <c r="AC15" s="19"/>
     </row>
     <row r="16" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B16" s="158"/>
+      <c r="B16" s="157"/>
       <c r="C16" s="32" t="s">
         <v>91</v>
       </c>
@@ -3898,40 +3888,40 @@
       <c r="Q17" s="12"/>
     </row>
     <row r="18" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B18" s="150" t="s">
+      <c r="B18" s="146" t="s">
         <v>53</v>
       </c>
-      <c r="C18" s="151"/>
-      <c r="D18" s="159" t="s">
+      <c r="C18" s="147"/>
+      <c r="D18" s="158" t="s">
         <v>54</v>
       </c>
-      <c r="E18" s="167" t="s">
+      <c r="E18" s="166" t="s">
         <v>55</v>
       </c>
-      <c r="F18" s="168"/>
-      <c r="G18" s="169"/>
-      <c r="H18" s="173" t="s">
+      <c r="F18" s="167"/>
+      <c r="G18" s="168"/>
+      <c r="H18" s="172" t="s">
         <v>56</v>
       </c>
-      <c r="I18" s="174"/>
-      <c r="J18" s="174"/>
-      <c r="K18" s="174"/>
-      <c r="L18" s="174"/>
-      <c r="M18" s="174"/>
-      <c r="N18" s="174"/>
-      <c r="O18" s="174"/>
-      <c r="P18" s="174"/>
-      <c r="Q18" s="175"/>
+      <c r="I18" s="173"/>
+      <c r="J18" s="173"/>
+      <c r="K18" s="173"/>
+      <c r="L18" s="173"/>
+      <c r="M18" s="173"/>
+      <c r="N18" s="173"/>
+      <c r="O18" s="173"/>
+      <c r="P18" s="173"/>
+      <c r="Q18" s="174"/>
     </row>
     <row r="19" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B19" s="152"/>
-      <c r="C19" s="153"/>
-      <c r="D19" s="160"/>
-      <c r="E19" s="164" t="s">
+      <c r="B19" s="148"/>
+      <c r="C19" s="149"/>
+      <c r="D19" s="159"/>
+      <c r="E19" s="163" t="s">
         <v>96</v>
       </c>
-      <c r="F19" s="165"/>
-      <c r="G19" s="166"/>
+      <c r="F19" s="164"/>
+      <c r="G19" s="165"/>
       <c r="H19" s="67"/>
       <c r="I19" s="68"/>
       <c r="J19" s="68"/>
@@ -3944,9 +3934,9 @@
       <c r="Q19" s="69"/>
     </row>
     <row r="20" spans="2:28" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B20" s="154"/>
-      <c r="C20" s="155"/>
-      <c r="D20" s="160"/>
+      <c r="B20" s="150"/>
+      <c r="C20" s="151"/>
+      <c r="D20" s="159"/>
       <c r="E20" s="85" t="s">
         <v>140</v>
       </c>
@@ -3988,10 +3978,10 @@
       </c>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B21" s="156" t="s">
+      <c r="B21" s="155" t="s">
         <v>100</v>
       </c>
-      <c r="C21" s="147" t="s">
+      <c r="C21" s="152" t="s">
         <v>99</v>
       </c>
       <c r="D21" s="33" t="s">
@@ -4051,8 +4041,8 @@
       </c>
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B22" s="157"/>
-      <c r="C22" s="148"/>
+      <c r="B22" s="156"/>
+      <c r="C22" s="153"/>
       <c r="D22" s="26" t="s">
         <v>102</v>
       </c>
@@ -4106,8 +4096,8 @@
       <c r="AB22" s="19"/>
     </row>
     <row r="23" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B23" s="157"/>
-      <c r="C23" s="149"/>
+      <c r="B23" s="156"/>
+      <c r="C23" s="154"/>
       <c r="D23" s="83" t="s">
         <v>70</v>
       </c>
@@ -4161,7 +4151,7 @@
       <c r="AB23" s="19"/>
     </row>
     <row r="24" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B24" s="157"/>
+      <c r="B24" s="156"/>
       <c r="C24" s="36" t="s">
         <v>91</v>
       </c>
@@ -4217,8 +4207,8 @@
       </c>
     </row>
     <row r="25" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B25" s="157"/>
-      <c r="C25" s="147" t="s">
+      <c r="B25" s="156"/>
+      <c r="C25" s="152" t="s">
         <v>98</v>
       </c>
       <c r="D25" s="33" t="s">
@@ -4278,8 +4268,8 @@
       </c>
     </row>
     <row r="26" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B26" s="157"/>
-      <c r="C26" s="148"/>
+      <c r="B26" s="156"/>
+      <c r="C26" s="153"/>
       <c r="D26" s="26" t="s">
         <v>102</v>
       </c>
@@ -4333,8 +4323,8 @@
       <c r="AB26" s="19"/>
     </row>
     <row r="27" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B27" s="157"/>
-      <c r="C27" s="149"/>
+      <c r="B27" s="156"/>
+      <c r="C27" s="154"/>
       <c r="D27" s="83" t="s">
         <v>70</v>
       </c>
@@ -4388,7 +4378,7 @@
       <c r="AB27" s="19"/>
     </row>
     <row r="28" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B28" s="157"/>
+      <c r="B28" s="156"/>
       <c r="C28" s="36" t="s">
         <v>91</v>
       </c>
@@ -4444,8 +4434,8 @@
       </c>
     </row>
     <row r="29" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B29" s="157"/>
-      <c r="C29" s="147" t="s">
+      <c r="B29" s="156"/>
+      <c r="C29" s="152" t="s">
         <v>97</v>
       </c>
       <c r="D29" s="33" t="s">
@@ -4505,8 +4495,8 @@
       </c>
     </row>
     <row r="30" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B30" s="157"/>
-      <c r="C30" s="148"/>
+      <c r="B30" s="156"/>
+      <c r="C30" s="153"/>
       <c r="D30" s="26" t="s">
         <v>102</v>
       </c>
@@ -4560,8 +4550,8 @@
       <c r="AB30" s="19"/>
     </row>
     <row r="31" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B31" s="157"/>
-      <c r="C31" s="149"/>
+      <c r="B31" s="156"/>
+      <c r="C31" s="154"/>
       <c r="D31" s="83" t="s">
         <v>70</v>
       </c>
@@ -4615,7 +4605,7 @@
       <c r="AB31" s="19"/>
     </row>
     <row r="32" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B32" s="158"/>
+      <c r="B32" s="157"/>
       <c r="C32" s="32" t="s">
         <v>91</v>
       </c>
@@ -4683,40 +4673,40 @@
       <c r="Q33" s="12"/>
     </row>
     <row r="34" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B34" s="150" t="s">
+      <c r="B34" s="146" t="s">
         <v>53</v>
       </c>
-      <c r="C34" s="151"/>
-      <c r="D34" s="159" t="s">
+      <c r="C34" s="147"/>
+      <c r="D34" s="158" t="s">
         <v>54</v>
       </c>
-      <c r="E34" s="167" t="s">
+      <c r="E34" s="166" t="s">
         <v>55</v>
       </c>
-      <c r="F34" s="168"/>
-      <c r="G34" s="169"/>
-      <c r="H34" s="173" t="s">
+      <c r="F34" s="167"/>
+      <c r="G34" s="168"/>
+      <c r="H34" s="172" t="s">
         <v>56</v>
       </c>
-      <c r="I34" s="174"/>
-      <c r="J34" s="174"/>
-      <c r="K34" s="174"/>
-      <c r="L34" s="174"/>
-      <c r="M34" s="174"/>
-      <c r="N34" s="174"/>
-      <c r="O34" s="174"/>
-      <c r="P34" s="174"/>
-      <c r="Q34" s="175"/>
+      <c r="I34" s="173"/>
+      <c r="J34" s="173"/>
+      <c r="K34" s="173"/>
+      <c r="L34" s="173"/>
+      <c r="M34" s="173"/>
+      <c r="N34" s="173"/>
+      <c r="O34" s="173"/>
+      <c r="P34" s="173"/>
+      <c r="Q34" s="174"/>
     </row>
     <row r="35" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B35" s="152"/>
-      <c r="C35" s="153"/>
-      <c r="D35" s="160"/>
-      <c r="E35" s="164" t="s">
+      <c r="B35" s="148"/>
+      <c r="C35" s="149"/>
+      <c r="D35" s="159"/>
+      <c r="E35" s="163" t="s">
         <v>96</v>
       </c>
-      <c r="F35" s="165"/>
-      <c r="G35" s="166"/>
+      <c r="F35" s="164"/>
+      <c r="G35" s="165"/>
       <c r="H35" s="67"/>
       <c r="I35" s="68"/>
       <c r="J35" s="68"/>
@@ -4729,9 +4719,9 @@
       <c r="Q35" s="69"/>
     </row>
     <row r="36" spans="2:28" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B36" s="154"/>
-      <c r="C36" s="155"/>
-      <c r="D36" s="160"/>
+      <c r="B36" s="150"/>
+      <c r="C36" s="151"/>
+      <c r="D36" s="159"/>
       <c r="E36" s="85" t="s">
         <v>140</v>
       </c>
@@ -4773,10 +4763,10 @@
       </c>
     </row>
     <row r="37" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B37" s="156" t="s">
+      <c r="B37" s="155" t="s">
         <v>95</v>
       </c>
-      <c r="C37" s="147" t="s">
+      <c r="C37" s="152" t="s">
         <v>94</v>
       </c>
       <c r="D37" s="33" t="s">
@@ -4836,8 +4826,8 @@
       </c>
     </row>
     <row r="38" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B38" s="157"/>
-      <c r="C38" s="148"/>
+      <c r="B38" s="156"/>
+      <c r="C38" s="153"/>
       <c r="D38" s="26" t="s">
         <v>102</v>
       </c>
@@ -4891,8 +4881,8 @@
       <c r="AB38" s="19"/>
     </row>
     <row r="39" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B39" s="157"/>
-      <c r="C39" s="149"/>
+      <c r="B39" s="156"/>
+      <c r="C39" s="154"/>
       <c r="D39" s="83" t="s">
         <v>70</v>
       </c>
@@ -4946,7 +4936,7 @@
       <c r="AB39" s="19"/>
     </row>
     <row r="40" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B40" s="157"/>
+      <c r="B40" s="156"/>
       <c r="C40" s="36" t="s">
         <v>91</v>
       </c>
@@ -5002,8 +4992,8 @@
       </c>
     </row>
     <row r="41" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B41" s="157"/>
-      <c r="C41" s="147" t="s">
+      <c r="B41" s="156"/>
+      <c r="C41" s="152" t="s">
         <v>79</v>
       </c>
       <c r="D41" s="33" t="s">
@@ -5063,8 +5053,8 @@
       </c>
     </row>
     <row r="42" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B42" s="157"/>
-      <c r="C42" s="148"/>
+      <c r="B42" s="156"/>
+      <c r="C42" s="153"/>
       <c r="D42" s="26" t="s">
         <v>102</v>
       </c>
@@ -5118,8 +5108,8 @@
       <c r="AB42" s="19"/>
     </row>
     <row r="43" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B43" s="157"/>
-      <c r="C43" s="149"/>
+      <c r="B43" s="156"/>
+      <c r="C43" s="154"/>
       <c r="D43" s="83" t="s">
         <v>70</v>
       </c>
@@ -5173,7 +5163,7 @@
       <c r="AB43" s="19"/>
     </row>
     <row r="44" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B44" s="157"/>
+      <c r="B44" s="156"/>
       <c r="C44" s="36" t="s">
         <v>91</v>
       </c>
@@ -5229,8 +5219,8 @@
       </c>
     </row>
     <row r="45" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B45" s="157"/>
-      <c r="C45" s="147" t="s">
+      <c r="B45" s="156"/>
+      <c r="C45" s="152" t="s">
         <v>93</v>
       </c>
       <c r="D45" s="33" t="s">
@@ -5290,8 +5280,8 @@
       </c>
     </row>
     <row r="46" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B46" s="157"/>
-      <c r="C46" s="148"/>
+      <c r="B46" s="156"/>
+      <c r="C46" s="153"/>
       <c r="D46" s="26" t="s">
         <v>102</v>
       </c>
@@ -5345,8 +5335,8 @@
       <c r="AB46" s="19"/>
     </row>
     <row r="47" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B47" s="157"/>
-      <c r="C47" s="149"/>
+      <c r="B47" s="156"/>
+      <c r="C47" s="154"/>
       <c r="D47" s="83" t="s">
         <v>70</v>
       </c>
@@ -5400,7 +5390,7 @@
       <c r="AB47" s="19"/>
     </row>
     <row r="48" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B48" s="157"/>
+      <c r="B48" s="156"/>
       <c r="C48" s="36" t="s">
         <v>91</v>
       </c>
@@ -5456,14 +5446,14 @@
       </c>
     </row>
     <row r="49" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B49" s="157"/>
-      <c r="C49" s="147" t="s">
+      <c r="B49" s="156"/>
+      <c r="C49" s="152" t="s">
         <v>92</v>
       </c>
       <c r="D49" s="33" t="s">
         <v>143</v>
       </c>
-      <c r="E49" s="170"/>
+      <c r="E49" s="169"/>
       <c r="F49" s="87"/>
       <c r="G49" s="31"/>
       <c r="H49" s="64" t="e">
@@ -5508,12 +5498,12 @@
       </c>
     </row>
     <row r="50" spans="2:28" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B50" s="157"/>
-      <c r="C50" s="148"/>
+      <c r="B50" s="156"/>
+      <c r="C50" s="153"/>
       <c r="D50" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="E50" s="171"/>
+      <c r="E50" s="170"/>
       <c r="F50" s="88"/>
       <c r="G50" s="28"/>
       <c r="H50" s="73">
@@ -5559,12 +5549,12 @@
       <c r="AB50" s="19"/>
     </row>
     <row r="51" spans="2:28" ht="18.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B51" s="157"/>
-      <c r="C51" s="149"/>
+      <c r="B51" s="156"/>
+      <c r="C51" s="154"/>
       <c r="D51" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="E51" s="172"/>
+      <c r="E51" s="171"/>
       <c r="F51" s="89"/>
       <c r="G51" s="54"/>
       <c r="H51" s="75">
@@ -5610,7 +5600,7 @@
       <c r="AB51" s="19"/>
     </row>
     <row r="52" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B52" s="158"/>
+      <c r="B52" s="157"/>
       <c r="C52" s="32" t="s">
         <v>91</v>
       </c>
@@ -6062,16 +6052,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B2:C4"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="B18:C20"/>
-    <mergeCell ref="B5:B16"/>
-    <mergeCell ref="B21:B32"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="C29:C31"/>
-    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="C41:C43"/>
+    <mergeCell ref="C45:C47"/>
+    <mergeCell ref="C49:C51"/>
+    <mergeCell ref="B34:C36"/>
+    <mergeCell ref="B37:B52"/>
+    <mergeCell ref="C37:C39"/>
     <mergeCell ref="D2:D4"/>
     <mergeCell ref="H2:Q2"/>
     <mergeCell ref="E3:G3"/>
@@ -6085,12 +6071,16 @@
     <mergeCell ref="D18:D20"/>
     <mergeCell ref="E18:G18"/>
     <mergeCell ref="E19:G19"/>
-    <mergeCell ref="C41:C43"/>
-    <mergeCell ref="C45:C47"/>
-    <mergeCell ref="C49:C51"/>
-    <mergeCell ref="B34:C36"/>
-    <mergeCell ref="B37:B52"/>
-    <mergeCell ref="C37:C39"/>
+    <mergeCell ref="B2:C4"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="B18:C20"/>
+    <mergeCell ref="B5:B16"/>
+    <mergeCell ref="B21:B32"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="C25:C27"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="H5:Q7">
